--- a/Recordings/SavedData/v2_no_low_sampled/60s_resampled[analysis].xlsx
+++ b/Recordings/SavedData/v2_no_low_sampled/60s_resampled[analysis].xlsx
@@ -8,16 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dobregeo\Documents\GitHub\vilearn_ml\Recordings\SavedData\v2_no_low_sampled\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D61C261-AA9C-4ACC-9DE3-7AE8BA1024DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{366B12A7-9ECB-448A-A137-96937BA20BFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="All Data" sheetId="5" r:id="rId1"/>
-    <sheet name="1d_DG" sheetId="1" r:id="rId2"/>
-    <sheet name="MG" sheetId="2" r:id="rId3"/>
-    <sheet name="TE" sheetId="3" r:id="rId4"/>
-    <sheet name="Blinks" sheetId="4" r:id="rId5"/>
+    <sheet name="ExtraDyads" sheetId="6" r:id="rId2"/>
+    <sheet name="1d_DG" sheetId="1" r:id="rId3"/>
+    <sheet name="MG" sheetId="2" r:id="rId4"/>
+    <sheet name="TE" sheetId="3" r:id="rId5"/>
+    <sheet name="Blinks" sheetId="4" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1368" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1689" uniqueCount="343">
   <si>
     <t>seconds_interaction_window</t>
   </si>
@@ -1063,6 +1064,12 @@
   </si>
   <si>
     <t>L</t>
+  </si>
+  <si>
+    <t>blink_durations</t>
+  </si>
+  <si>
+    <t>dyad_01_0_D1</t>
   </si>
 </sst>
 </file>
@@ -1423,6 +1430,9 @@
       <c r="H1" t="s">
         <v>311</v>
       </c>
+      <c r="I1" t="s">
+        <v>341</v>
+      </c>
       <c r="M1" s="1"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.35">
@@ -1449,6 +1459,9 @@
       </c>
       <c r="H2">
         <v>4</v>
+      </c>
+      <c r="I2">
+        <v>153</v>
       </c>
       <c r="M2" s="1"/>
     </row>
@@ -1477,6 +1490,9 @@
       <c r="H3">
         <v>17</v>
       </c>
+      <c r="I3">
+        <v>149.041666666666</v>
+      </c>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
@@ -1504,6 +1520,9 @@
       <c r="H4">
         <v>17.5</v>
       </c>
+      <c r="I4">
+        <v>134.63333333333301</v>
+      </c>
       <c r="M4" s="1"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.35">
@@ -1531,6 +1550,9 @@
       <c r="H5">
         <v>15</v>
       </c>
+      <c r="I5">
+        <v>179.05172413793099</v>
+      </c>
       <c r="M5" s="1"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.35">
@@ -1558,6 +1580,9 @@
       <c r="H6">
         <v>15.5</v>
       </c>
+      <c r="I6">
+        <v>162.291666666666</v>
+      </c>
       <c r="M6" s="1"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.35">
@@ -1585,6 +1610,9 @@
       <c r="H7">
         <v>13.5</v>
       </c>
+      <c r="I7">
+        <v>170.26923076923001</v>
+      </c>
       <c r="M7" s="1"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.35">
@@ -1612,6 +1640,9 @@
       <c r="H8">
         <v>21.5</v>
       </c>
+      <c r="I8">
+        <v>138.987804878048</v>
+      </c>
       <c r="M8" s="1"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.35">
@@ -1639,6 +1670,9 @@
       <c r="H9">
         <v>16</v>
       </c>
+      <c r="I9">
+        <v>186.875</v>
+      </c>
       <c r="M9" s="1"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.35">
@@ -1666,6 +1700,9 @@
       <c r="H10">
         <v>18.5</v>
       </c>
+      <c r="I10">
+        <v>150.50757575757501</v>
+      </c>
       <c r="M10" s="1"/>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.35">
@@ -1693,6 +1730,9 @@
       <c r="H11">
         <v>14</v>
       </c>
+      <c r="I11">
+        <v>214.166666666666</v>
+      </c>
       <c r="M11" s="1"/>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.35">
@@ -1720,6 +1760,9 @@
       <c r="H12">
         <v>16.5</v>
       </c>
+      <c r="I12">
+        <v>136.21875</v>
+      </c>
       <c r="M12" s="1"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.35">
@@ -1746,6 +1789,9 @@
       </c>
       <c r="H13">
         <v>10</v>
+      </c>
+      <c r="I13">
+        <v>222.81313131313101</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.35">
@@ -1773,6 +1819,9 @@
       <c r="H14">
         <v>38</v>
       </c>
+      <c r="I14">
+        <v>221.72473867595801</v>
+      </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A15">
@@ -1799,6 +1848,9 @@
       <c r="H15">
         <v>53.5</v>
       </c>
+      <c r="I15">
+        <v>250.35350678732999</v>
+      </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A16">
@@ -1825,8 +1877,11 @@
       <c r="H16">
         <v>21.5</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I16">
+        <v>236.42105263157799</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>240</v>
       </c>
@@ -1851,8 +1906,11 @@
       <c r="H17">
         <v>35</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I17">
+        <v>232.10457516339801</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>300</v>
       </c>
@@ -1877,8 +1935,11 @@
       <c r="H18">
         <v>21.5</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I18">
+        <v>242.429802955665</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>360</v>
       </c>
@@ -1903,8 +1964,11 @@
       <c r="H19">
         <v>35.5</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I19">
+        <v>261.363672496025</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>420</v>
       </c>
@@ -1929,8 +1993,11 @@
       <c r="H20">
         <v>24.5</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I20">
+        <v>247.67807017543799</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>480</v>
       </c>
@@ -1955,8 +2022,11 @@
       <c r="H21">
         <v>25</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I21">
+        <v>252.6875</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>0</v>
       </c>
@@ -1981,8 +2051,11 @@
       <c r="H22">
         <v>15</v>
       </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I22">
+        <v>170.39140271493201</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>60</v>
       </c>
@@ -2007,8 +2080,11 @@
       <c r="H23">
         <v>32.5</v>
       </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I23">
+        <v>173.71732954545399</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>120</v>
       </c>
@@ -2033,8 +2109,11 @@
       <c r="H24">
         <v>32.5</v>
       </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I24">
+        <v>190.16555977229601</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>180</v>
       </c>
@@ -2059,8 +2138,11 @@
       <c r="H25">
         <v>34.5</v>
       </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I25">
+        <v>189.70694444444399</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>240</v>
       </c>
@@ -2085,8 +2167,11 @@
       <c r="H26">
         <v>31</v>
       </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I26">
+        <v>200.771929824561</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>300</v>
       </c>
@@ -2111,8 +2196,11 @@
       <c r="H27">
         <v>35.5</v>
       </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I27">
+        <v>183.240322580645</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>360</v>
       </c>
@@ -2137,8 +2225,11 @@
       <c r="H28">
         <v>37</v>
       </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I28">
+        <v>183.81501831501799</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>420</v>
       </c>
@@ -2163,8 +2254,11 @@
       <c r="H29">
         <v>37.5</v>
       </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I29">
+        <v>186.213773314203</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>480</v>
       </c>
@@ -2189,8 +2283,11 @@
       <c r="H30">
         <v>35</v>
       </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I30">
+        <v>185.77124183006501</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>540</v>
       </c>
@@ -2215,8 +2312,11 @@
       <c r="H31">
         <v>31.5</v>
       </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I31">
+        <v>190.40927419354799</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>600</v>
       </c>
@@ -2241,8 +2341,11 @@
       <c r="H32">
         <v>30</v>
       </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I32">
+        <v>170.860859728506</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>660</v>
       </c>
@@ -2267,8 +2370,11 @@
       <c r="H33">
         <v>36</v>
       </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I33">
+        <v>180.575851393188</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>0</v>
       </c>
@@ -2293,8 +2399,11 @@
       <c r="H35">
         <v>21.5</v>
       </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I35">
+        <v>182.258695652173</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>60</v>
       </c>
@@ -2319,8 +2428,11 @@
       <c r="H36">
         <v>42.5</v>
       </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I36">
+        <v>154.708333333333</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>120</v>
       </c>
@@ -2345,8 +2457,11 @@
       <c r="H37">
         <v>42</v>
       </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I37">
+        <v>164.20238095238</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>180</v>
       </c>
@@ -2371,8 +2486,11 @@
       <c r="H38">
         <v>42.5</v>
       </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I38">
+        <v>166.42433481152901</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>240</v>
       </c>
@@ -2397,8 +2515,11 @@
       <c r="H39">
         <v>45.5</v>
       </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I39">
+        <v>165.88502415458899</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>300</v>
       </c>
@@ -2423,8 +2544,11 @@
       <c r="H40">
         <v>40.5</v>
       </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I40">
+        <v>167.91400491400401</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>360</v>
       </c>
@@ -2449,8 +2573,11 @@
       <c r="H41">
         <v>35</v>
       </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I41">
+        <v>172.229166666666</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>420</v>
       </c>
@@ -2475,8 +2602,11 @@
       <c r="H42">
         <v>33.5</v>
       </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I42">
+        <v>162.682142857142</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>480</v>
       </c>
@@ -2501,8 +2631,11 @@
       <c r="H43">
         <v>41</v>
       </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I43">
+        <v>166.311602870813</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>540</v>
       </c>
@@ -2527,8 +2660,11 @@
       <c r="H44">
         <v>36.5</v>
       </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I44">
+        <v>155.146396396396</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>600</v>
       </c>
@@ -2553,8 +2689,11 @@
       <c r="H45">
         <v>31.5</v>
       </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I45">
+        <v>180.40606060606001</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>660</v>
       </c>
@@ -2579,8 +2718,11 @@
       <c r="H46">
         <v>13.5</v>
       </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I46">
+        <v>145.88235294117601</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>0</v>
       </c>
@@ -2605,8 +2747,11 @@
       <c r="H47">
         <v>3.5</v>
       </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I47">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>60</v>
       </c>
@@ -2631,8 +2776,11 @@
       <c r="H48">
         <v>23.5</v>
       </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I48">
+        <v>210.42090909090899</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>120</v>
       </c>
@@ -2657,8 +2805,11 @@
       <c r="H49">
         <v>21.5</v>
       </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I49">
+        <v>223.72261904761899</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>180</v>
       </c>
@@ -2683,8 +2834,11 @@
       <c r="H50">
         <v>18.5</v>
       </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I50">
+        <v>243.00730994151999</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>240</v>
       </c>
@@ -2709,8 +2863,11 @@
       <c r="H51">
         <v>30.5</v>
       </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I51">
+        <v>225.52976190476099</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>300</v>
       </c>
@@ -2735,8 +2892,11 @@
       <c r="H52">
         <v>23.5</v>
       </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I52">
+        <v>213.51296296296201</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>360</v>
       </c>
@@ -2761,8 +2921,11 @@
       <c r="H53">
         <v>23.5</v>
       </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I53">
+        <v>208.41035353535301</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>420</v>
       </c>
@@ -2787,8 +2950,11 @@
       <c r="H54">
         <v>26.5</v>
       </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I54">
+        <v>219.39955357142799</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>480</v>
       </c>
@@ -2813,8 +2979,11 @@
       <c r="H55">
         <v>27.5</v>
       </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I55">
+        <v>203.78173374612999</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>540</v>
       </c>
@@ -2839,8 +3008,11 @@
       <c r="H56">
         <v>23.5</v>
       </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I56">
+        <v>222.64559386973099</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>600</v>
       </c>
@@ -2865,8 +3037,11 @@
       <c r="H57">
         <v>25</v>
       </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I57">
+        <v>220.942708333333</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>0</v>
       </c>
@@ -2891,8 +3066,11 @@
       <c r="H58">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I58">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>60</v>
       </c>
@@ -2917,8 +3095,11 @@
       <c r="H59">
         <v>20.5</v>
       </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I59">
+        <v>190.12575757575701</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>120</v>
       </c>
@@ -2943,8 +3124,11 @@
       <c r="H60">
         <v>27</v>
       </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I60">
+        <v>205.017857142857</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>180</v>
       </c>
@@ -2969,8 +3153,11 @@
       <c r="H61">
         <v>24</v>
       </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I61">
+        <v>197.088235294117</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>240</v>
       </c>
@@ -2995,8 +3182,11 @@
       <c r="H62">
         <v>22</v>
       </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I62">
+        <v>187.619791666666</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>300</v>
       </c>
@@ -3021,8 +3211,11 @@
       <c r="H63">
         <v>23</v>
       </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I63">
+        <v>192.063063063063</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>360</v>
       </c>
@@ -3047,8 +3240,11 @@
       <c r="H64">
         <v>27</v>
       </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I64">
+        <v>209.943589743589</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>420</v>
       </c>
@@ -3073,8 +3269,11 @@
       <c r="H65">
         <v>33.5</v>
       </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I65">
+        <v>204.85826210826201</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>480</v>
       </c>
@@ -3099,8 +3298,11 @@
       <c r="H66">
         <v>29</v>
       </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I66">
+        <v>209.492109038737</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>0</v>
       </c>
@@ -3125,8 +3327,11 @@
       <c r="H68">
         <v>28</v>
       </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I68">
+        <v>158.69374999999999</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>60</v>
       </c>
@@ -3151,8 +3356,11 @@
       <c r="H69">
         <v>29</v>
       </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I69">
+        <v>169.32230392156799</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>120</v>
       </c>
@@ -3177,8 +3385,11 @@
       <c r="H70">
         <v>37.5</v>
       </c>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I70">
+        <v>158.72606382978699</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>180</v>
       </c>
@@ -3203,8 +3414,11 @@
       <c r="H71">
         <v>34</v>
       </c>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I71">
+        <v>167.50980392156799</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>240</v>
       </c>
@@ -3229,8 +3443,11 @@
       <c r="H72">
         <v>35.5</v>
       </c>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I72">
+        <v>181.04081632653001</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>300</v>
       </c>
@@ -3255,8 +3472,11 @@
       <c r="H73">
         <v>31</v>
       </c>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I73">
+        <v>185.40425531914801</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>360</v>
       </c>
@@ -3281,8 +3501,11 @@
       <c r="H74">
         <v>33.5</v>
       </c>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I74">
+        <v>169.739035087719</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>420</v>
       </c>
@@ -3307,8 +3530,11 @@
       <c r="H75">
         <v>30.5</v>
       </c>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I75">
+        <v>179.041666666666</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>480</v>
       </c>
@@ -3333,8 +3559,11 @@
       <c r="H76">
         <v>34.5</v>
       </c>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I76">
+        <v>185.769949066213</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>540</v>
       </c>
@@ -3359,8 +3588,11 @@
       <c r="H77">
         <v>26</v>
       </c>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I77">
+        <v>187.52870813397101</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A78">
         <v>600</v>
       </c>
@@ -3385,8 +3617,11 @@
       <c r="H78">
         <v>27</v>
       </c>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I78">
+        <v>183.75</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A79">
         <v>0</v>
       </c>
@@ -3411,8 +3646,11 @@
       <c r="H79">
         <v>11.5</v>
       </c>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I79">
+        <v>205.32499999999999</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A80">
         <v>60</v>
       </c>
@@ -3437,8 +3675,11 @@
       <c r="H80">
         <v>41</v>
       </c>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I80">
+        <v>170.459051724137</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A81">
         <v>120</v>
       </c>
@@ -3463,8 +3704,11 @@
       <c r="H81">
         <v>48.5</v>
       </c>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I81">
+        <v>193.745845552297</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A82">
         <v>180</v>
       </c>
@@ -3489,8 +3733,11 @@
       <c r="H82">
         <v>46.5</v>
       </c>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I82">
+        <v>196.79936854190501</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A83">
         <v>240</v>
       </c>
@@ -3515,8 +3762,11 @@
       <c r="H83">
         <v>52.5</v>
       </c>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I83">
+        <v>183.696338383838</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A84">
         <v>300</v>
       </c>
@@ -3541,8 +3791,11 @@
       <c r="H84">
         <v>45</v>
       </c>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I84">
+        <v>178.07217058501899</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A85">
         <v>360</v>
       </c>
@@ -3567,8 +3820,11 @@
       <c r="H85">
         <v>42.5</v>
       </c>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I85">
+        <v>175.27833333333299</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A86">
         <v>420</v>
       </c>
@@ -3593,8 +3849,11 @@
       <c r="H86">
         <v>38</v>
       </c>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I86">
+        <v>166.167508417508</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A87">
         <v>480</v>
       </c>
@@ -3619,8 +3878,11 @@
       <c r="H87">
         <v>43.5</v>
       </c>
-    </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I87">
+        <v>181.06643356643301</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A88">
         <v>540</v>
       </c>
@@ -3645,8 +3907,11 @@
       <c r="H88">
         <v>37.5</v>
       </c>
-    </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I88">
+        <v>187.15931372548999</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A89">
         <v>600</v>
       </c>
@@ -3671,8 +3936,11 @@
       <c r="H89">
         <v>38.5</v>
       </c>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I89">
+        <v>182.459183673469</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A90">
         <v>660</v>
       </c>
@@ -3697,8 +3965,11 @@
       <c r="H90">
         <v>48</v>
       </c>
-    </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I90">
+        <v>164.229166666666</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A91">
         <v>720</v>
       </c>
@@ -3723,8 +3994,11 @@
       <c r="H91">
         <v>45</v>
       </c>
-    </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I91">
+        <v>171.388888888888</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A92">
         <v>780</v>
       </c>
@@ -3749,8 +4023,11 @@
       <c r="H92">
         <v>35.5</v>
       </c>
-    </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I92">
+        <v>159.59219858156001</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A93">
         <v>0</v>
       </c>
@@ -3775,8 +4052,11 @@
       <c r="H93">
         <v>31.5</v>
       </c>
-    </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I93">
+        <v>212.47619047619</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A94">
         <v>60</v>
       </c>
@@ -3801,8 +4081,11 @@
       <c r="H94">
         <v>26</v>
       </c>
-    </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I94">
+        <v>212.55769230769201</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A95">
         <v>120</v>
       </c>
@@ -3827,8 +4110,11 @@
       <c r="H95">
         <v>30.5</v>
       </c>
-    </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I95">
+        <v>230.16344086021499</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A96">
         <v>180</v>
       </c>
@@ -3853,8 +4139,11 @@
       <c r="H96">
         <v>14.5</v>
       </c>
-    </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I96">
+        <v>183.44473684210499</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A97">
         <v>240</v>
       </c>
@@ -3879,8 +4168,11 @@
       <c r="H97">
         <v>32</v>
       </c>
-    </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I97">
+        <v>224.864532019704</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A98">
         <v>300</v>
       </c>
@@ -3905,8 +4197,11 @@
       <c r="H98">
         <v>17</v>
       </c>
-    </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I98">
+        <v>194.810276679841</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A99">
         <v>360</v>
       </c>
@@ -3931,8 +4226,11 @@
       <c r="H99">
         <v>9.5</v>
       </c>
-    </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I99">
+        <v>209.85833333333301</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A100">
         <v>0</v>
       </c>
@@ -3957,8 +4255,11 @@
       <c r="H100">
         <v>16.5</v>
       </c>
-    </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I100">
+        <v>163.54545454545399</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A101">
         <v>60</v>
       </c>
@@ -3983,8 +4284,11 @@
       <c r="H101">
         <v>26</v>
       </c>
-    </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I101">
+        <v>184.79027113237601</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A102">
         <v>120</v>
       </c>
@@ -4009,8 +4313,11 @@
       <c r="H102">
         <v>30</v>
       </c>
-    </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I102">
+        <v>199.62857142857101</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A103">
         <v>180</v>
       </c>
@@ -4035,8 +4342,11 @@
       <c r="H103">
         <v>28</v>
       </c>
-    </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I103">
+        <v>189.458333333333</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A104">
         <v>240</v>
       </c>
@@ -4061,8 +4371,11 @@
       <c r="H104">
         <v>24</v>
       </c>
-    </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I104">
+        <v>187.661616161616</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A105">
         <v>300</v>
       </c>
@@ -4087,8 +4400,11 @@
       <c r="H105">
         <v>26.5</v>
       </c>
-    </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I105">
+        <v>179.96959459459401</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A106">
         <v>360</v>
       </c>
@@ -4113,8 +4429,11 @@
       <c r="H106">
         <v>27.5</v>
       </c>
-    </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I106">
+        <v>189.58258258258201</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A107">
         <v>420</v>
       </c>
@@ -4139,8 +4458,11 @@
       <c r="H107">
         <v>31.5</v>
       </c>
-    </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I107">
+        <v>166.11105263157799</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A108">
         <v>480</v>
       </c>
@@ -4165,8 +4487,11 @@
       <c r="H108">
         <v>27</v>
       </c>
-    </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I108">
+        <v>174.226078799249</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A109">
         <v>0</v>
       </c>
@@ -4191,8 +4516,11 @@
       <c r="H109">
         <v>13</v>
       </c>
-    </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I109">
+        <v>144.03214285714199</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A110">
         <v>60</v>
       </c>
@@ -4217,8 +4545,11 @@
       <c r="H110">
         <v>10.5</v>
       </c>
-    </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I110">
+        <v>169.944444444444</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A111">
         <v>120</v>
       </c>
@@ -4243,8 +4574,11 @@
       <c r="H111">
         <v>15</v>
       </c>
-    </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I111">
+        <v>176.70074224021499</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A112">
         <v>180</v>
       </c>
@@ -4269,8 +4603,11 @@
       <c r="H112">
         <v>14</v>
       </c>
-    </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I112">
+        <v>178.493055555555</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A113">
         <v>240</v>
       </c>
@@ -4295,8 +4632,11 @@
       <c r="H113">
         <v>30</v>
       </c>
-    </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I113">
+        <v>168.67905875800599</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A114">
         <v>300</v>
       </c>
@@ -4321,8 +4661,11 @@
       <c r="H114">
         <v>31</v>
       </c>
-    </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I114">
+        <v>182.648578048833</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A115">
         <v>360</v>
       </c>
@@ -4347,8 +4690,11 @@
       <c r="H115">
         <v>18.5</v>
       </c>
-    </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I115">
+        <v>178.25820707070699</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A116">
         <v>420</v>
       </c>
@@ -4373,8 +4719,11 @@
       <c r="H116">
         <v>9</v>
       </c>
-    </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I116">
+        <v>142.9</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A117">
         <v>480</v>
       </c>
@@ -4399,8 +4748,11 @@
       <c r="H117">
         <v>17</v>
       </c>
-    </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I117">
+        <v>177.69411764705799</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A118">
         <v>540</v>
       </c>
@@ -4425,8 +4777,11 @@
       <c r="H118">
         <v>14</v>
       </c>
-    </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I118">
+        <v>148.61216931216899</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A119">
         <v>600</v>
       </c>
@@ -4451,8 +4806,11 @@
       <c r="H119">
         <v>27</v>
       </c>
-    </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I119">
+        <v>174.50207570207499</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A120">
         <v>660</v>
       </c>
@@ -4477,8 +4835,11 @@
       <c r="H120">
         <v>28.5</v>
       </c>
-    </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I120">
+        <v>165.26580419580401</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A121">
         <v>720</v>
       </c>
@@ -4503,8 +4864,11 @@
       <c r="H121">
         <v>19.5</v>
       </c>
-    </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I121">
+        <v>170.83184789067101</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A122">
         <v>0</v>
       </c>
@@ -4529,8 +4893,11 @@
       <c r="H122">
         <v>5</v>
       </c>
-    </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I122">
+        <v>169.722222222222</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A123">
         <v>60</v>
       </c>
@@ -4555,8 +4922,11 @@
       <c r="H123">
         <v>19</v>
       </c>
-    </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I123">
+        <v>195.7</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A124">
         <v>120</v>
       </c>
@@ -4581,8 +4951,11 @@
       <c r="H124">
         <v>24</v>
       </c>
-    </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I124">
+        <v>171.611413043478</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A125">
         <v>180</v>
       </c>
@@ -4607,8 +4980,11 @@
       <c r="H125">
         <v>20</v>
       </c>
-    </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I125">
+        <v>178.39682539682499</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A126">
         <v>240</v>
       </c>
@@ -4633,8 +5009,11 @@
       <c r="H126">
         <v>21</v>
       </c>
-    </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I126">
+        <v>188.340595497458</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A127">
         <v>300</v>
       </c>
@@ -4659,8 +5038,11 @@
       <c r="H127">
         <v>24</v>
       </c>
-    </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I127">
+        <v>187.096296296296</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A128">
         <v>360</v>
       </c>
@@ -4685,8 +5067,11 @@
       <c r="H128">
         <v>21.5</v>
       </c>
-    </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I128">
+        <v>190.119262119262</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A129">
         <v>420</v>
       </c>
@@ -4711,8 +5096,11 @@
       <c r="H129">
         <v>17.5</v>
       </c>
-    </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I129">
+        <v>182.79544159544099</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A130">
         <v>0</v>
       </c>
@@ -4737,8 +5125,11 @@
       <c r="H130">
         <v>4</v>
       </c>
-    </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I130">
+        <v>199.5</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A131">
         <v>60</v>
       </c>
@@ -4763,8 +5154,11 @@
       <c r="H131">
         <v>23.5</v>
       </c>
-    </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I131">
+        <v>178.081529581529</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A132">
         <v>120</v>
       </c>
@@ -4789,8 +5183,11 @@
       <c r="H132">
         <v>26</v>
       </c>
-    </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I132">
+        <v>183.40486633249699</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A133">
         <v>180</v>
       </c>
@@ -4815,8 +5212,11 @@
       <c r="H133">
         <v>22</v>
       </c>
-    </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I133">
+        <v>167.24444444444401</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A134">
         <v>240</v>
       </c>
@@ -4841,8 +5241,11 @@
       <c r="H134">
         <v>19.5</v>
       </c>
-    </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I134">
+        <v>182.32692307692301</v>
+      </c>
+    </row>
+    <row r="135" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A135">
         <v>300</v>
       </c>
@@ -4867,8 +5270,11 @@
       <c r="H135">
         <v>27</v>
       </c>
-    </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I135">
+        <v>167.17283950617201</v>
+      </c>
+    </row>
+    <row r="136" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A136">
         <v>360</v>
       </c>
@@ -4893,8 +5299,11 @@
       <c r="H136">
         <v>26.5</v>
       </c>
-    </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I136">
+        <v>177.72898550724599</v>
+      </c>
+    </row>
+    <row r="137" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A137">
         <v>420</v>
       </c>
@@ -4919,8 +5328,11 @@
       <c r="H137">
         <v>23.5</v>
       </c>
-    </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I137">
+        <v>192.42458521870199</v>
+      </c>
+    </row>
+    <row r="138" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A138">
         <v>480</v>
       </c>
@@ -4945,8 +5357,11 @@
       <c r="H138">
         <v>27</v>
       </c>
-    </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I138">
+        <v>191.969607843137</v>
+      </c>
+    </row>
+    <row r="139" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A139">
         <v>540</v>
       </c>
@@ -4971,8 +5386,11 @@
       <c r="H139">
         <v>22</v>
       </c>
-    </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I139">
+        <v>180.059523809523</v>
+      </c>
+    </row>
+    <row r="140" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A140">
         <v>600</v>
       </c>
@@ -4997,8 +5415,11 @@
       <c r="H140">
         <v>22.5</v>
       </c>
-    </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I140">
+        <v>202.383620689655</v>
+      </c>
+    </row>
+    <row r="141" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A141">
         <v>0</v>
       </c>
@@ -5023,8 +5444,11 @@
       <c r="H141">
         <v>2</v>
       </c>
-    </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I141">
+        <v>139.555555555555</v>
+      </c>
+    </row>
+    <row r="142" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A142">
         <v>60</v>
       </c>
@@ -5049,8 +5473,11 @@
       <c r="H142">
         <v>5.5</v>
       </c>
-    </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I142">
+        <v>173.03333333333299</v>
+      </c>
+    </row>
+    <row r="143" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A143">
         <v>120</v>
       </c>
@@ -5075,8 +5502,11 @@
       <c r="H143">
         <v>9</v>
       </c>
-    </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I143">
+        <v>139.17916666666599</v>
+      </c>
+    </row>
+    <row r="144" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A144">
         <v>180</v>
       </c>
@@ -5101,8 +5531,11 @@
       <c r="H144">
         <v>7</v>
       </c>
-    </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I144">
+        <v>148.74853801169499</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A145">
         <v>240</v>
       </c>
@@ -5127,8 +5560,11 @@
       <c r="H145">
         <v>6</v>
       </c>
-    </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I145">
+        <v>143.25054466230901</v>
+      </c>
+    </row>
+    <row r="146" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A146">
         <v>300</v>
       </c>
@@ -5153,8 +5589,11 @@
       <c r="H146">
         <v>8</v>
       </c>
-    </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I146">
+        <v>163.06709956709901</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A147">
         <v>360</v>
       </c>
@@ -5179,8 +5618,11 @@
       <c r="H147">
         <v>4.5</v>
       </c>
-    </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I147">
+        <v>145.66865079364999</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A148">
         <v>420</v>
       </c>
@@ -5205,8 +5647,11 @@
       <c r="H148">
         <v>11.5</v>
       </c>
-    </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I148">
+        <v>178.324603174603</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A149">
         <v>480</v>
       </c>
@@ -5231,8 +5676,11 @@
       <c r="H149">
         <v>6.5</v>
       </c>
-    </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I149">
+        <v>191.89807692307647</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A150">
         <v>540</v>
       </c>
@@ -5257,8 +5705,11 @@
       <c r="H150">
         <v>5</v>
       </c>
-    </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I150">
+        <v>172.68</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A151">
         <v>600</v>
       </c>
@@ -5283,8 +5734,11 @@
       <c r="H151">
         <v>6</v>
       </c>
-    </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I151">
+        <v>164.388888888888</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A152">
         <v>660</v>
       </c>
@@ -5309,8 +5763,11 @@
       <c r="H152">
         <v>8</v>
       </c>
-    </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I152">
+        <v>141.768115942029</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A153">
         <v>720</v>
       </c>
@@ -5335,8 +5792,11 @@
       <c r="H153">
         <v>6.5</v>
       </c>
-    </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I153">
+        <v>163.21568627450901</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A154">
         <v>0</v>
       </c>
@@ -5361,8 +5821,11 @@
       <c r="H154">
         <v>4.5</v>
       </c>
-    </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I154">
+        <v>150.305555555555</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A155">
         <v>60</v>
       </c>
@@ -5387,8 +5850,11 @@
       <c r="H155">
         <v>13.5</v>
       </c>
-    </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I155">
+        <v>168.58899868247599</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A156">
         <v>120</v>
       </c>
@@ -5413,8 +5879,11 @@
       <c r="H156">
         <v>19.5</v>
       </c>
-    </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I156">
+        <v>177.28396854204399</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A157">
         <v>180</v>
       </c>
@@ -5439,8 +5908,11 @@
       <c r="H157">
         <v>19</v>
       </c>
-    </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I157">
+        <v>178.680518035912</v>
+      </c>
+    </row>
+    <row r="158" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A158">
         <v>240</v>
       </c>
@@ -5465,8 +5937,11 @@
       <c r="H158">
         <v>16.5</v>
       </c>
-    </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I158">
+        <v>168.73543417366901</v>
+      </c>
+    </row>
+    <row r="159" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A159">
         <v>300</v>
       </c>
@@ -5491,8 +5966,11 @@
       <c r="H159">
         <v>12</v>
       </c>
-    </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I159">
+        <v>164.15695203400099</v>
+      </c>
+    </row>
+    <row r="160" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A160">
         <v>360</v>
       </c>
@@ -5517,8 +5995,11 @@
       <c r="H160">
         <v>13</v>
       </c>
-    </row>
-    <row r="161" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I160">
+        <v>168.531746031746</v>
+      </c>
+    </row>
+    <row r="161" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A161">
         <v>420</v>
       </c>
@@ -5543,8 +6024,11 @@
       <c r="H161">
         <v>12.5</v>
       </c>
-    </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I161">
+        <v>168.17728758169901</v>
+      </c>
+    </row>
+    <row r="162" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A162">
         <v>480</v>
       </c>
@@ -5569,8 +6053,11 @@
       <c r="H162">
         <v>16.5</v>
       </c>
-    </row>
-    <row r="163" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I162">
+        <v>159.708333333333</v>
+      </c>
+    </row>
+    <row r="163" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A163">
         <v>540</v>
       </c>
@@ -5595,8 +6082,11 @@
       <c r="H163">
         <v>14</v>
       </c>
-    </row>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I163">
+        <v>166.91174603174599</v>
+      </c>
+    </row>
+    <row r="164" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A164">
         <v>600</v>
       </c>
@@ -5621,8 +6111,11 @@
       <c r="H164">
         <v>20.5</v>
       </c>
-    </row>
-    <row r="165" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I164">
+        <v>173.35542929292899</v>
+      </c>
+    </row>
+    <row r="165" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A165">
         <v>0</v>
       </c>
@@ -5647,8 +6140,11 @@
       <c r="H165">
         <v>7.5</v>
       </c>
-    </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I165">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="166" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A166">
         <v>60</v>
       </c>
@@ -5673,8 +6169,11 @@
       <c r="H166">
         <v>12</v>
       </c>
-    </row>
-    <row r="167" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I166">
+        <v>183.786231884057</v>
+      </c>
+    </row>
+    <row r="167" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A167">
         <v>120</v>
       </c>
@@ -5699,8 +6198,11 @@
       <c r="H167">
         <v>8</v>
       </c>
-    </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I167">
+        <v>171.868055555555</v>
+      </c>
+    </row>
+    <row r="168" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A168">
         <v>180</v>
       </c>
@@ -5725,8 +6227,11 @@
       <c r="H168">
         <v>9.5</v>
       </c>
-    </row>
-    <row r="169" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I168">
+        <v>184.25063131313101</v>
+      </c>
+    </row>
+    <row r="169" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A169">
         <v>240</v>
       </c>
@@ -5751,8 +6256,11 @@
       <c r="H169">
         <v>5</v>
       </c>
-    </row>
-    <row r="170" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I169">
+        <v>173.638888888888</v>
+      </c>
+    </row>
+    <row r="170" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A170">
         <v>300</v>
       </c>
@@ -5777,8 +6285,11 @@
       <c r="H170">
         <v>13.5</v>
       </c>
-    </row>
-    <row r="171" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I170">
+        <v>182.00643939393899</v>
+      </c>
+    </row>
+    <row r="171" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A171">
         <v>360</v>
       </c>
@@ -5803,8 +6314,11 @@
       <c r="H171">
         <v>13</v>
       </c>
-    </row>
-    <row r="172" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I171">
+        <v>182.64652014652</v>
+      </c>
+    </row>
+    <row r="172" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A172">
         <v>420</v>
       </c>
@@ -5829,8 +6343,11 @@
       <c r="H172">
         <v>15.5</v>
       </c>
-    </row>
-    <row r="173" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I172">
+        <v>189.98085901027</v>
+      </c>
+    </row>
+    <row r="173" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A173">
         <v>480</v>
       </c>
@@ -5855,8 +6372,11 @@
       <c r="H173">
         <v>11.5</v>
       </c>
-    </row>
-    <row r="174" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I173">
+        <v>176.39434523809501</v>
+      </c>
+    </row>
+    <row r="174" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A174">
         <v>540</v>
       </c>
@@ -5881,8 +6401,11 @@
       <c r="H174">
         <v>11.5</v>
       </c>
-    </row>
-    <row r="175" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I174">
+        <v>180.69612794612701</v>
+      </c>
+    </row>
+    <row r="175" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A175">
         <v>600</v>
       </c>
@@ -5907,8 +6430,11 @@
       <c r="H175">
         <v>7</v>
       </c>
-    </row>
-    <row r="176" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I175">
+        <v>174.87285714285701</v>
+      </c>
+    </row>
+    <row r="176" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A176">
         <v>0</v>
       </c>
@@ -5933,8 +6459,11 @@
       <c r="H176">
         <v>7</v>
       </c>
-    </row>
-    <row r="177" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I176">
+        <v>189.34632034632</v>
+      </c>
+    </row>
+    <row r="177" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A177">
         <v>60</v>
       </c>
@@ -5959,8 +6488,11 @@
       <c r="H177">
         <v>14.5</v>
       </c>
-    </row>
-    <row r="178" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I177">
+        <v>189.12843137254899</v>
+      </c>
+    </row>
+    <row r="178" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A178">
         <v>120</v>
       </c>
@@ -5985,8 +6517,11 @@
       <c r="H178">
         <v>11.5</v>
       </c>
-    </row>
-    <row r="179" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I178">
+        <v>175.02564102564099</v>
+      </c>
+    </row>
+    <row r="179" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A179">
         <v>180</v>
       </c>
@@ -6011,8 +6546,11 @@
       <c r="H179">
         <v>12</v>
       </c>
-    </row>
-    <row r="180" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I179">
+        <v>173.56736596736499</v>
+      </c>
+    </row>
+    <row r="180" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A180">
         <v>240</v>
       </c>
@@ -6037,8 +6575,11 @@
       <c r="H180">
         <v>11.5</v>
       </c>
-    </row>
-    <row r="181" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I180">
+        <v>199.128205128205</v>
+      </c>
+    </row>
+    <row r="181" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A181">
         <v>300</v>
       </c>
@@ -6063,8 +6604,11 @@
       <c r="H181">
         <v>6.5</v>
       </c>
-    </row>
-    <row r="182" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I181">
+        <v>182.655555555555</v>
+      </c>
+    </row>
+    <row r="182" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A182">
         <v>360</v>
       </c>
@@ -6089,8 +6633,11 @@
       <c r="H182">
         <v>8.5</v>
       </c>
-    </row>
-    <row r="183" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I182">
+        <v>208.39047619047599</v>
+      </c>
+    </row>
+    <row r="183" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A183">
         <v>420</v>
       </c>
@@ -6115,8 +6662,11 @@
       <c r="H183">
         <v>1.5</v>
       </c>
-    </row>
-    <row r="184" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I183">
+        <v>168.666666666666</v>
+      </c>
+    </row>
+    <row r="184" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A184">
         <v>0</v>
       </c>
@@ -6141,8 +6691,11 @@
       <c r="H184">
         <v>18.5</v>
       </c>
-    </row>
-    <row r="185" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I184">
+        <v>199.37797619047601</v>
+      </c>
+    </row>
+    <row r="185" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A185">
         <v>60</v>
       </c>
@@ -6167,8 +6720,11 @@
       <c r="H185">
         <v>31</v>
       </c>
-    </row>
-    <row r="186" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I185">
+        <v>190.980263157894</v>
+      </c>
+    </row>
+    <row r="186" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A186">
         <v>120</v>
       </c>
@@ -6193,8 +6749,11 @@
       <c r="H186">
         <v>15</v>
       </c>
-    </row>
-    <row r="187" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I186">
+        <v>165.890540831717</v>
+      </c>
+    </row>
+    <row r="187" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A187">
         <v>180</v>
       </c>
@@ -6219,8 +6778,11 @@
       <c r="H187">
         <v>12.5</v>
       </c>
-    </row>
-    <row r="188" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I187">
+        <v>166.091269841269</v>
+      </c>
+    </row>
+    <row r="188" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A188">
         <v>240</v>
       </c>
@@ -6245,8 +6807,11 @@
       <c r="H188">
         <v>12</v>
       </c>
-    </row>
-    <row r="189" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I188">
+        <v>190.29523809523801</v>
+      </c>
+    </row>
+    <row r="189" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A189">
         <v>300</v>
       </c>
@@ -6271,8 +6836,11 @@
       <c r="H189">
         <v>8.5</v>
       </c>
-    </row>
-    <row r="190" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I189">
+        <v>188.77248677248599</v>
+      </c>
+    </row>
+    <row r="190" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A190">
         <v>360</v>
       </c>
@@ -6297,8 +6865,11 @@
       <c r="H190">
         <v>7</v>
       </c>
-    </row>
-    <row r="191" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I190">
+        <v>165.738888888888</v>
+      </c>
+    </row>
+    <row r="191" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A191">
         <v>0</v>
       </c>
@@ -6323,8 +6894,11 @@
       <c r="H191">
         <v>9</v>
       </c>
-    </row>
-    <row r="192" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I191">
+        <v>173.70238095238</v>
+      </c>
+    </row>
+    <row r="192" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A192">
         <v>60</v>
       </c>
@@ -6349,8 +6923,11 @@
       <c r="H192">
         <v>17</v>
       </c>
-    </row>
-    <row r="193" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I192">
+        <v>193.73853955375199</v>
+      </c>
+    </row>
+    <row r="193" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A193">
         <v>120</v>
       </c>
@@ -6375,8 +6952,11 @@
       <c r="H193">
         <v>17</v>
       </c>
-    </row>
-    <row r="194" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I193">
+        <v>206.77167060677601</v>
+      </c>
+    </row>
+    <row r="194" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A194">
         <v>180</v>
       </c>
@@ -6401,8 +6981,11 @@
       <c r="H194">
         <v>21</v>
       </c>
-    </row>
-    <row r="195" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I194">
+        <v>189.34114353079801</v>
+      </c>
+    </row>
+    <row r="195" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A195">
         <v>240</v>
       </c>
@@ -6427,8 +7010,11 @@
       <c r="H195">
         <v>24</v>
       </c>
-    </row>
-    <row r="196" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I195">
+        <v>211.33152578415701</v>
+      </c>
+    </row>
+    <row r="196" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A196">
         <v>300</v>
       </c>
@@ -6453,8 +7039,11 @@
       <c r="H196">
         <v>21</v>
       </c>
-    </row>
-    <row r="197" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I196">
+        <v>207.09851953601901</v>
+      </c>
+    </row>
+    <row r="197" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A197">
         <v>360</v>
       </c>
@@ -6479,8 +7068,11 @@
       <c r="H197">
         <v>25.5</v>
       </c>
-    </row>
-    <row r="198" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I197">
+        <v>209.70634920634899</v>
+      </c>
+    </row>
+    <row r="198" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A198">
         <v>420</v>
       </c>
@@ -6505,8 +7097,11 @@
       <c r="H198">
         <v>14.5</v>
       </c>
-    </row>
-    <row r="199" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I198">
+        <v>194.69576719576699</v>
+      </c>
+    </row>
+    <row r="199" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A199">
         <v>0</v>
       </c>
@@ -6531,8 +7126,11 @@
       <c r="H199">
         <v>2</v>
       </c>
-    </row>
-    <row r="200" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I199">
+        <v>138.166666666666</v>
+      </c>
+    </row>
+    <row r="200" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A200">
         <v>60</v>
       </c>
@@ -6557,8 +7155,11 @@
       <c r="H200">
         <v>15</v>
       </c>
-    </row>
-    <row r="201" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I200">
+        <v>170.64831573655101</v>
+      </c>
+    </row>
+    <row r="201" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A201">
         <v>120</v>
       </c>
@@ -6583,8 +7184,11 @@
       <c r="H201">
         <v>16.5</v>
       </c>
-    </row>
-    <row r="202" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I201">
+        <v>170.40178571428501</v>
+      </c>
+    </row>
+    <row r="202" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A202">
         <v>180</v>
       </c>
@@ -6609,8 +7213,11 @@
       <c r="H202">
         <v>19.5</v>
       </c>
-    </row>
-    <row r="203" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I202">
+        <v>177.958759590792</v>
+      </c>
+    </row>
+    <row r="203" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A203">
         <v>240</v>
       </c>
@@ -6635,8 +7242,11 @@
       <c r="H203">
         <v>18</v>
       </c>
-    </row>
-    <row r="204" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I203">
+        <v>177.40159221583301</v>
+      </c>
+    </row>
+    <row r="204" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A204">
         <v>300</v>
       </c>
@@ -6661,8 +7271,11 @@
       <c r="H204">
         <v>13.5</v>
       </c>
-    </row>
-    <row r="205" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I204">
+        <v>182.85138888888801</v>
+      </c>
+    </row>
+    <row r="205" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A205">
         <v>360</v>
       </c>
@@ -6687,8 +7300,11 @@
       <c r="H205">
         <v>19</v>
       </c>
-    </row>
-    <row r="206" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I205">
+        <v>148.953159041394</v>
+      </c>
+    </row>
+    <row r="206" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A206">
         <v>0</v>
       </c>
@@ -6713,8 +7329,11 @@
       <c r="H206">
         <v>10</v>
       </c>
-    </row>
-    <row r="207" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I206">
+        <v>155.106902356902</v>
+      </c>
+    </row>
+    <row r="207" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A207">
         <v>60</v>
       </c>
@@ -6739,8 +7358,11 @@
       <c r="H207">
         <v>28.5</v>
       </c>
-    </row>
-    <row r="208" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I207">
+        <v>164.581082564778</v>
+      </c>
+    </row>
+    <row r="208" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A208">
         <v>120</v>
       </c>
@@ -6765,8 +7387,11 @@
       <c r="H208">
         <v>24.5</v>
       </c>
-    </row>
-    <row r="209" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I208">
+        <v>180.74158249158199</v>
+      </c>
+    </row>
+    <row r="209" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A209">
         <v>180</v>
       </c>
@@ -6791,8 +7416,11 @@
       <c r="H209">
         <v>25</v>
       </c>
-    </row>
-    <row r="210" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I209">
+        <v>181.14135802469099</v>
+      </c>
+    </row>
+    <row r="210" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A210">
         <v>0</v>
       </c>
@@ -6817,8 +7445,11 @@
       <c r="H210">
         <v>10.5</v>
       </c>
-    </row>
-    <row r="211" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I210">
+        <v>191.45555555555501</v>
+      </c>
+    </row>
+    <row r="211" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A211">
         <v>60</v>
       </c>
@@ -6843,8 +7474,11 @@
       <c r="H211">
         <v>24</v>
       </c>
-    </row>
-    <row r="212" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I211">
+        <v>186.00300300300299</v>
+      </c>
+    </row>
+    <row r="212" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A212">
         <v>120</v>
       </c>
@@ -6869,8 +7503,11 @@
       <c r="H212">
         <v>18</v>
       </c>
-    </row>
-    <row r="213" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I212">
+        <v>193.86361283643799</v>
+      </c>
+    </row>
+    <row r="213" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A213">
         <v>180</v>
       </c>
@@ -6895,8 +7532,11 @@
       <c r="H213">
         <v>26.5</v>
       </c>
-    </row>
-    <row r="214" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I213">
+        <v>197.473316912972</v>
+      </c>
+    </row>
+    <row r="214" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A214">
         <v>240</v>
       </c>
@@ -6921,8 +7561,11 @@
       <c r="H214">
         <v>21.5</v>
       </c>
-    </row>
-    <row r="215" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I214">
+        <v>195.775462962962</v>
+      </c>
+    </row>
+    <row r="215" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A215">
         <v>300</v>
       </c>
@@ -6947,8 +7590,11 @@
       <c r="H215">
         <v>23.5</v>
       </c>
-    </row>
-    <row r="216" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I215">
+        <v>206.46812544180901</v>
+      </c>
+    </row>
+    <row r="216" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A216">
         <v>360</v>
       </c>
@@ -6973,8 +7619,11 @@
       <c r="H216">
         <v>29</v>
       </c>
-    </row>
-    <row r="217" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I216">
+        <v>194.20634920634899</v>
+      </c>
+    </row>
+    <row r="217" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A217">
         <v>420</v>
       </c>
@@ -6999,8 +7648,11 @@
       <c r="H217">
         <v>27.5</v>
       </c>
-    </row>
-    <row r="218" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I217">
+        <v>203.59566250742699</v>
+      </c>
+    </row>
+    <row r="218" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A218">
         <v>0</v>
       </c>
@@ -7025,8 +7677,11 @@
       <c r="H218">
         <v>11.5</v>
       </c>
-    </row>
-    <row r="219" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I218">
+        <v>150.797979797979</v>
+      </c>
+    </row>
+    <row r="219" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A219">
         <v>60</v>
       </c>
@@ -7051,8 +7706,11 @@
       <c r="H219">
         <v>30.5</v>
       </c>
-    </row>
-    <row r="220" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I219">
+        <v>163.036733161733</v>
+      </c>
+    </row>
+    <row r="220" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A220">
         <v>120</v>
       </c>
@@ -7077,8 +7735,11 @@
       <c r="H220">
         <v>15.5</v>
       </c>
-    </row>
-    <row r="221" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I220">
+        <v>145.21618357487901</v>
+      </c>
+    </row>
+    <row r="221" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A221">
         <v>180</v>
       </c>
@@ -7103,8 +7764,11 @@
       <c r="H221">
         <v>31</v>
       </c>
-    </row>
-    <row r="222" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I221">
+        <v>168.892361111111</v>
+      </c>
+    </row>
+    <row r="222" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A222">
         <v>240</v>
       </c>
@@ -7129,8 +7793,11 @@
       <c r="H222">
         <v>29</v>
       </c>
-    </row>
-    <row r="223" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I222">
+        <v>169.029647435897</v>
+      </c>
+    </row>
+    <row r="223" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A223">
         <v>300</v>
       </c>
@@ -7155,8 +7822,11 @@
       <c r="H223">
         <v>25</v>
       </c>
-    </row>
-    <row r="224" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I223">
+        <v>159.931746031746</v>
+      </c>
+    </row>
+    <row r="224" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A224">
         <v>360</v>
       </c>
@@ -7181,8 +7851,11 @@
       <c r="H224">
         <v>19</v>
       </c>
-    </row>
-    <row r="225" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I224">
+        <v>163.392495126705</v>
+      </c>
+    </row>
+    <row r="225" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A225">
         <v>420</v>
       </c>
@@ -7207,8 +7880,11 @@
       <c r="H225">
         <v>31</v>
       </c>
-    </row>
-    <row r="226" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I225">
+        <v>157.90152359717499</v>
+      </c>
+    </row>
+    <row r="226" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A226">
         <v>480</v>
       </c>
@@ -7233,8 +7909,11 @@
       <c r="H226">
         <v>21.5</v>
       </c>
-    </row>
-    <row r="227" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I226">
+        <v>153.097671957671</v>
+      </c>
+    </row>
+    <row r="227" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A227">
         <v>540</v>
       </c>
@@ -7259,8 +7938,11 @@
       <c r="H227">
         <v>24</v>
       </c>
-    </row>
-    <row r="228" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I227">
+        <v>156.23753623188401</v>
+      </c>
+    </row>
+    <row r="228" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A228">
         <v>600</v>
       </c>
@@ -7285,8 +7967,11 @@
       <c r="H228">
         <v>14.5</v>
       </c>
-    </row>
-    <row r="229" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I228">
+        <v>161.846671846671</v>
+      </c>
+    </row>
+    <row r="229" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A229">
         <v>0</v>
       </c>
@@ -7311,8 +7996,11 @@
       <c r="H229">
         <v>2</v>
       </c>
-    </row>
-    <row r="230" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I229">
+        <v>195.5</v>
+      </c>
+    </row>
+    <row r="230" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A230">
         <v>60</v>
       </c>
@@ -7337,8 +8025,11 @@
       <c r="H230">
         <v>17.5</v>
       </c>
-    </row>
-    <row r="231" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I230">
+        <v>173.122420020639</v>
+      </c>
+    </row>
+    <row r="231" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A231">
         <v>120</v>
       </c>
@@ -7363,8 +8054,11 @@
       <c r="H231">
         <v>20</v>
       </c>
-    </row>
-    <row r="232" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I231">
+        <v>178.60208866155099</v>
+      </c>
+    </row>
+    <row r="232" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A232">
         <v>180</v>
       </c>
@@ -7389,8 +8083,11 @@
       <c r="H232">
         <v>14</v>
       </c>
-    </row>
-    <row r="233" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I232">
+        <v>167.701388888888</v>
+      </c>
+    </row>
+    <row r="233" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A233">
         <v>240</v>
       </c>
@@ -7415,8 +8112,11 @@
       <c r="H233">
         <v>15</v>
       </c>
-    </row>
-    <row r="234" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I233">
+        <v>162.39629629629599</v>
+      </c>
+    </row>
+    <row r="234" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A234">
         <v>300</v>
       </c>
@@ -7441,8 +8141,11 @@
       <c r="H234">
         <v>23</v>
       </c>
-    </row>
-    <row r="235" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I234">
+        <v>173.79944960440301</v>
+      </c>
+    </row>
+    <row r="235" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A235">
         <v>360</v>
       </c>
@@ -7467,8 +8170,11 @@
       <c r="H235">
         <v>25.5</v>
       </c>
-    </row>
-    <row r="236" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I235">
+        <v>182.871945488721</v>
+      </c>
+    </row>
+    <row r="236" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A236">
         <v>420</v>
       </c>
@@ -7493,8 +8199,11 @@
       <c r="H236">
         <v>17.5</v>
       </c>
-    </row>
-    <row r="237" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I236">
+        <v>181.112037037037</v>
+      </c>
+    </row>
+    <row r="237" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A237">
         <v>480</v>
       </c>
@@ -7519,8 +8228,11 @@
       <c r="H237">
         <v>18</v>
       </c>
-    </row>
-    <row r="238" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I237">
+        <v>164.293452380952</v>
+      </c>
+    </row>
+    <row r="238" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A238">
         <v>540</v>
       </c>
@@ -7544,6 +8256,9 @@
       </c>
       <c r="H238">
         <v>15</v>
+      </c>
+      <c r="I238">
+        <v>177.03748006379499</v>
       </c>
     </row>
   </sheetData>
@@ -7553,6 +8268,1563 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F126CFC9-BE8B-4DAF-AADB-1B89D72E9205}">
+  <dimension ref="A1:E108"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>305</v>
+      </c>
+      <c r="C1" t="s">
+        <v>306</v>
+      </c>
+      <c r="D1" t="s">
+        <v>307</v>
+      </c>
+      <c r="E1" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>337</v>
+      </c>
+      <c r="C2" t="s">
+        <v>338</v>
+      </c>
+      <c r="D2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E2">
+        <v>0.87554664723032005</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>60</v>
+      </c>
+      <c r="B3" t="s">
+        <v>337</v>
+      </c>
+      <c r="C3" t="s">
+        <v>338</v>
+      </c>
+      <c r="D3" t="s">
+        <v>110</v>
+      </c>
+      <c r="E3">
+        <v>0.93689936536717999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>120</v>
+      </c>
+      <c r="B4" t="s">
+        <v>337</v>
+      </c>
+      <c r="C4" t="s">
+        <v>338</v>
+      </c>
+      <c r="D4" t="s">
+        <v>110</v>
+      </c>
+      <c r="E4">
+        <v>0.94897403304884698</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>180</v>
+      </c>
+      <c r="B5" t="s">
+        <v>337</v>
+      </c>
+      <c r="C5" t="s">
+        <v>338</v>
+      </c>
+      <c r="D5" t="s">
+        <v>110</v>
+      </c>
+      <c r="E5">
+        <v>0.97681999275624698</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>240</v>
+      </c>
+      <c r="B6" t="s">
+        <v>337</v>
+      </c>
+      <c r="C6" t="s">
+        <v>338</v>
+      </c>
+      <c r="D6" t="s">
+        <v>110</v>
+      </c>
+      <c r="E6">
+        <v>0.69329710144927503</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>300</v>
+      </c>
+      <c r="B7" t="s">
+        <v>337</v>
+      </c>
+      <c r="C7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D7" t="s">
+        <v>110</v>
+      </c>
+      <c r="E7">
+        <v>0.97549909255898304</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>360</v>
+      </c>
+      <c r="B8" t="s">
+        <v>337</v>
+      </c>
+      <c r="C8" t="s">
+        <v>338</v>
+      </c>
+      <c r="D8" t="s">
+        <v>110</v>
+      </c>
+      <c r="E8">
+        <v>0.93922452660054101</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>420</v>
+      </c>
+      <c r="B9" t="s">
+        <v>337</v>
+      </c>
+      <c r="C9" t="s">
+        <v>338</v>
+      </c>
+      <c r="D9" t="s">
+        <v>110</v>
+      </c>
+      <c r="E9">
+        <v>0.99460043196544201</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>480</v>
+      </c>
+      <c r="B10" t="s">
+        <v>337</v>
+      </c>
+      <c r="C10" t="s">
+        <v>338</v>
+      </c>
+      <c r="D10" t="s">
+        <v>110</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>540</v>
+      </c>
+      <c r="B11" t="s">
+        <v>337</v>
+      </c>
+      <c r="C11" t="s">
+        <v>338</v>
+      </c>
+      <c r="D11" t="s">
+        <v>110</v>
+      </c>
+      <c r="E11">
+        <v>0.93255184851217299</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>600</v>
+      </c>
+      <c r="B12" t="s">
+        <v>337</v>
+      </c>
+      <c r="C12" t="s">
+        <v>338</v>
+      </c>
+      <c r="D12" t="s">
+        <v>110</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>0</v>
+      </c>
+      <c r="B13" t="s">
+        <v>337</v>
+      </c>
+      <c r="C13" t="s">
+        <v>338</v>
+      </c>
+      <c r="D13" t="s">
+        <v>122</v>
+      </c>
+      <c r="E13">
+        <v>0.75100461378181205</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>60</v>
+      </c>
+      <c r="B14" t="s">
+        <v>337</v>
+      </c>
+      <c r="C14" t="s">
+        <v>338</v>
+      </c>
+      <c r="D14" t="s">
+        <v>122</v>
+      </c>
+      <c r="E14">
+        <v>0.85975975975975905</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>120</v>
+      </c>
+      <c r="B15" t="s">
+        <v>337</v>
+      </c>
+      <c r="C15" t="s">
+        <v>338</v>
+      </c>
+      <c r="D15" t="s">
+        <v>122</v>
+      </c>
+      <c r="E15">
+        <v>0.93885542168674696</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>180</v>
+      </c>
+      <c r="B16" t="s">
+        <v>337</v>
+      </c>
+      <c r="C16" t="s">
+        <v>338</v>
+      </c>
+      <c r="D16" t="s">
+        <v>122</v>
+      </c>
+      <c r="E16">
+        <v>0.78962278216788395</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>240</v>
+      </c>
+      <c r="B17" t="s">
+        <v>337</v>
+      </c>
+      <c r="C17" t="s">
+        <v>338</v>
+      </c>
+      <c r="D17" t="s">
+        <v>122</v>
+      </c>
+      <c r="E17">
+        <v>0.93130799161927502</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>300</v>
+      </c>
+      <c r="B18" t="s">
+        <v>337</v>
+      </c>
+      <c r="C18" t="s">
+        <v>338</v>
+      </c>
+      <c r="D18" t="s">
+        <v>122</v>
+      </c>
+      <c r="E18">
+        <v>0.88182632050134202</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>360</v>
+      </c>
+      <c r="B19" t="s">
+        <v>337</v>
+      </c>
+      <c r="C19" t="s">
+        <v>338</v>
+      </c>
+      <c r="D19" t="s">
+        <v>122</v>
+      </c>
+      <c r="E19">
+        <v>0.65941043083900197</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>420</v>
+      </c>
+      <c r="B20" t="s">
+        <v>337</v>
+      </c>
+      <c r="C20" t="s">
+        <v>338</v>
+      </c>
+      <c r="D20" t="s">
+        <v>122</v>
+      </c>
+      <c r="E20">
+        <v>0.77470116507792397</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>480</v>
+      </c>
+      <c r="B21" t="s">
+        <v>337</v>
+      </c>
+      <c r="C21" t="s">
+        <v>338</v>
+      </c>
+      <c r="D21" t="s">
+        <v>122</v>
+      </c>
+      <c r="E21">
+        <v>0.77791718946047606</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>0</v>
+      </c>
+      <c r="B22" t="s">
+        <v>337</v>
+      </c>
+      <c r="C22" t="s">
+        <v>338</v>
+      </c>
+      <c r="D22" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>60</v>
+      </c>
+      <c r="B23" t="s">
+        <v>337</v>
+      </c>
+      <c r="C23" t="s">
+        <v>338</v>
+      </c>
+      <c r="D23" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A24">
+        <v>120</v>
+      </c>
+      <c r="B24" t="s">
+        <v>337</v>
+      </c>
+      <c r="C24" t="s">
+        <v>338</v>
+      </c>
+      <c r="D24" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A25">
+        <v>180</v>
+      </c>
+      <c r="B25" t="s">
+        <v>337</v>
+      </c>
+      <c r="C25" t="s">
+        <v>338</v>
+      </c>
+      <c r="D25" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A26">
+        <v>240</v>
+      </c>
+      <c r="B26" t="s">
+        <v>337</v>
+      </c>
+      <c r="C26" t="s">
+        <v>338</v>
+      </c>
+      <c r="D26" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A27">
+        <v>300</v>
+      </c>
+      <c r="B27" t="s">
+        <v>337</v>
+      </c>
+      <c r="C27" t="s">
+        <v>338</v>
+      </c>
+      <c r="D27" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A28">
+        <v>360</v>
+      </c>
+      <c r="B28" t="s">
+        <v>337</v>
+      </c>
+      <c r="C28" t="s">
+        <v>338</v>
+      </c>
+      <c r="D28" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A29">
+        <v>420</v>
+      </c>
+      <c r="B29" t="s">
+        <v>337</v>
+      </c>
+      <c r="C29" t="s">
+        <v>338</v>
+      </c>
+      <c r="D29" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A30">
+        <v>480</v>
+      </c>
+      <c r="B30" t="s">
+        <v>337</v>
+      </c>
+      <c r="C30" t="s">
+        <v>338</v>
+      </c>
+      <c r="D30" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A31">
+        <v>540</v>
+      </c>
+      <c r="B31" t="s">
+        <v>337</v>
+      </c>
+      <c r="C31" t="s">
+        <v>338</v>
+      </c>
+      <c r="D31" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A32">
+        <v>600</v>
+      </c>
+      <c r="B32" t="s">
+        <v>337</v>
+      </c>
+      <c r="C32" t="s">
+        <v>338</v>
+      </c>
+      <c r="D32" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A33">
+        <v>660</v>
+      </c>
+      <c r="B33" t="s">
+        <v>337</v>
+      </c>
+      <c r="C33" t="s">
+        <v>338</v>
+      </c>
+      <c r="D33" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A35">
+        <v>0</v>
+      </c>
+      <c r="B35" t="s">
+        <v>337</v>
+      </c>
+      <c r="C35" t="s">
+        <v>338</v>
+      </c>
+      <c r="D35" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A36">
+        <v>60</v>
+      </c>
+      <c r="B36" t="s">
+        <v>337</v>
+      </c>
+      <c r="C36" t="s">
+        <v>338</v>
+      </c>
+      <c r="D36" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A37">
+        <v>120</v>
+      </c>
+      <c r="B37" t="s">
+        <v>337</v>
+      </c>
+      <c r="C37" t="s">
+        <v>338</v>
+      </c>
+      <c r="D37" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A38">
+        <v>180</v>
+      </c>
+      <c r="B38" t="s">
+        <v>337</v>
+      </c>
+      <c r="C38" t="s">
+        <v>338</v>
+      </c>
+      <c r="D38" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A39">
+        <v>240</v>
+      </c>
+      <c r="B39" t="s">
+        <v>337</v>
+      </c>
+      <c r="C39" t="s">
+        <v>338</v>
+      </c>
+      <c r="D39" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A40">
+        <v>300</v>
+      </c>
+      <c r="B40" t="s">
+        <v>337</v>
+      </c>
+      <c r="C40" t="s">
+        <v>338</v>
+      </c>
+      <c r="D40" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A41">
+        <v>360</v>
+      </c>
+      <c r="B41" t="s">
+        <v>337</v>
+      </c>
+      <c r="C41" t="s">
+        <v>338</v>
+      </c>
+      <c r="D41" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A42">
+        <v>420</v>
+      </c>
+      <c r="B42" t="s">
+        <v>337</v>
+      </c>
+      <c r="C42" t="s">
+        <v>338</v>
+      </c>
+      <c r="D42" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A43">
+        <v>480</v>
+      </c>
+      <c r="B43" t="s">
+        <v>337</v>
+      </c>
+      <c r="C43" t="s">
+        <v>338</v>
+      </c>
+      <c r="D43" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A44">
+        <v>540</v>
+      </c>
+      <c r="B44" t="s">
+        <v>337</v>
+      </c>
+      <c r="C44" t="s">
+        <v>338</v>
+      </c>
+      <c r="D44" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A45">
+        <v>600</v>
+      </c>
+      <c r="B45" t="s">
+        <v>337</v>
+      </c>
+      <c r="C45" t="s">
+        <v>338</v>
+      </c>
+      <c r="D45" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A46">
+        <v>660</v>
+      </c>
+      <c r="B46" t="s">
+        <v>337</v>
+      </c>
+      <c r="C46" t="s">
+        <v>338</v>
+      </c>
+      <c r="D46" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A47">
+        <v>0</v>
+      </c>
+      <c r="B47" t="s">
+        <v>337</v>
+      </c>
+      <c r="C47" t="s">
+        <v>338</v>
+      </c>
+      <c r="D47" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A48">
+        <v>60</v>
+      </c>
+      <c r="B48" t="s">
+        <v>337</v>
+      </c>
+      <c r="C48" t="s">
+        <v>338</v>
+      </c>
+      <c r="D48" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A49">
+        <v>120</v>
+      </c>
+      <c r="B49" t="s">
+        <v>337</v>
+      </c>
+      <c r="C49" t="s">
+        <v>338</v>
+      </c>
+      <c r="D49" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A50">
+        <v>180</v>
+      </c>
+      <c r="B50" t="s">
+        <v>337</v>
+      </c>
+      <c r="C50" t="s">
+        <v>338</v>
+      </c>
+      <c r="D50" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A51">
+        <v>240</v>
+      </c>
+      <c r="B51" t="s">
+        <v>337</v>
+      </c>
+      <c r="C51" t="s">
+        <v>338</v>
+      </c>
+      <c r="D51" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A52">
+        <v>300</v>
+      </c>
+      <c r="B52" t="s">
+        <v>337</v>
+      </c>
+      <c r="C52" t="s">
+        <v>338</v>
+      </c>
+      <c r="D52" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A53">
+        <v>360</v>
+      </c>
+      <c r="B53" t="s">
+        <v>337</v>
+      </c>
+      <c r="C53" t="s">
+        <v>338</v>
+      </c>
+      <c r="D53" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A54">
+        <v>420</v>
+      </c>
+      <c r="B54" t="s">
+        <v>337</v>
+      </c>
+      <c r="C54" t="s">
+        <v>338</v>
+      </c>
+      <c r="D54" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A55">
+        <v>480</v>
+      </c>
+      <c r="B55" t="s">
+        <v>337</v>
+      </c>
+      <c r="C55" t="s">
+        <v>338</v>
+      </c>
+      <c r="D55" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A56">
+        <v>540</v>
+      </c>
+      <c r="B56" t="s">
+        <v>337</v>
+      </c>
+      <c r="C56" t="s">
+        <v>338</v>
+      </c>
+      <c r="D56" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A57">
+        <v>600</v>
+      </c>
+      <c r="B57" t="s">
+        <v>337</v>
+      </c>
+      <c r="C57" t="s">
+        <v>338</v>
+      </c>
+      <c r="D57" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A58">
+        <v>0</v>
+      </c>
+      <c r="B58" t="s">
+        <v>337</v>
+      </c>
+      <c r="C58" t="s">
+        <v>338</v>
+      </c>
+      <c r="D58" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A59">
+        <v>60</v>
+      </c>
+      <c r="B59" t="s">
+        <v>337</v>
+      </c>
+      <c r="C59" t="s">
+        <v>338</v>
+      </c>
+      <c r="D59" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A60">
+        <v>120</v>
+      </c>
+      <c r="B60" t="s">
+        <v>337</v>
+      </c>
+      <c r="C60" t="s">
+        <v>338</v>
+      </c>
+      <c r="D60" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A61">
+        <v>180</v>
+      </c>
+      <c r="B61" t="s">
+        <v>337</v>
+      </c>
+      <c r="C61" t="s">
+        <v>338</v>
+      </c>
+      <c r="D61" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A62">
+        <v>240</v>
+      </c>
+      <c r="B62" t="s">
+        <v>337</v>
+      </c>
+      <c r="C62" t="s">
+        <v>338</v>
+      </c>
+      <c r="D62" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A63">
+        <v>300</v>
+      </c>
+      <c r="B63" t="s">
+        <v>337</v>
+      </c>
+      <c r="C63" t="s">
+        <v>338</v>
+      </c>
+      <c r="D63" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A64">
+        <v>360</v>
+      </c>
+      <c r="B64" t="s">
+        <v>337</v>
+      </c>
+      <c r="C64" t="s">
+        <v>338</v>
+      </c>
+      <c r="D64" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A65">
+        <v>420</v>
+      </c>
+      <c r="B65" t="s">
+        <v>337</v>
+      </c>
+      <c r="C65" t="s">
+        <v>338</v>
+      </c>
+      <c r="D65" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A66">
+        <v>480</v>
+      </c>
+      <c r="B66" t="s">
+        <v>337</v>
+      </c>
+      <c r="C66" t="s">
+        <v>338</v>
+      </c>
+      <c r="D66" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A68">
+        <v>0</v>
+      </c>
+      <c r="B68" t="s">
+        <v>337</v>
+      </c>
+      <c r="C68" t="s">
+        <v>338</v>
+      </c>
+      <c r="D68" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A69">
+        <v>60</v>
+      </c>
+      <c r="B69" t="s">
+        <v>337</v>
+      </c>
+      <c r="C69" t="s">
+        <v>338</v>
+      </c>
+      <c r="D69" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A70">
+        <v>120</v>
+      </c>
+      <c r="B70" t="s">
+        <v>337</v>
+      </c>
+      <c r="C70" t="s">
+        <v>338</v>
+      </c>
+      <c r="D70" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A71">
+        <v>180</v>
+      </c>
+      <c r="B71" t="s">
+        <v>337</v>
+      </c>
+      <c r="C71" t="s">
+        <v>338</v>
+      </c>
+      <c r="D71" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A72">
+        <v>240</v>
+      </c>
+      <c r="B72" t="s">
+        <v>337</v>
+      </c>
+      <c r="C72" t="s">
+        <v>338</v>
+      </c>
+      <c r="D72" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A73">
+        <v>300</v>
+      </c>
+      <c r="B73" t="s">
+        <v>337</v>
+      </c>
+      <c r="C73" t="s">
+        <v>338</v>
+      </c>
+      <c r="D73" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A74">
+        <v>360</v>
+      </c>
+      <c r="B74" t="s">
+        <v>337</v>
+      </c>
+      <c r="C74" t="s">
+        <v>338</v>
+      </c>
+      <c r="D74" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A75">
+        <v>420</v>
+      </c>
+      <c r="B75" t="s">
+        <v>337</v>
+      </c>
+      <c r="C75" t="s">
+        <v>338</v>
+      </c>
+      <c r="D75" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A76">
+        <v>480</v>
+      </c>
+      <c r="B76" t="s">
+        <v>337</v>
+      </c>
+      <c r="C76" t="s">
+        <v>338</v>
+      </c>
+      <c r="D76" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A77">
+        <v>540</v>
+      </c>
+      <c r="B77" t="s">
+        <v>337</v>
+      </c>
+      <c r="C77" t="s">
+        <v>338</v>
+      </c>
+      <c r="D77" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A78">
+        <v>600</v>
+      </c>
+      <c r="B78" t="s">
+        <v>337</v>
+      </c>
+      <c r="C78" t="s">
+        <v>338</v>
+      </c>
+      <c r="D78" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A79">
+        <v>0</v>
+      </c>
+      <c r="B79" t="s">
+        <v>337</v>
+      </c>
+      <c r="C79" t="s">
+        <v>338</v>
+      </c>
+      <c r="D79" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A80">
+        <v>60</v>
+      </c>
+      <c r="B80" t="s">
+        <v>337</v>
+      </c>
+      <c r="C80" t="s">
+        <v>338</v>
+      </c>
+      <c r="D80" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A81">
+        <v>120</v>
+      </c>
+      <c r="B81" t="s">
+        <v>337</v>
+      </c>
+      <c r="C81" t="s">
+        <v>338</v>
+      </c>
+      <c r="D81" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A82">
+        <v>180</v>
+      </c>
+      <c r="B82" t="s">
+        <v>337</v>
+      </c>
+      <c r="C82" t="s">
+        <v>338</v>
+      </c>
+      <c r="D82" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A83">
+        <v>240</v>
+      </c>
+      <c r="B83" t="s">
+        <v>337</v>
+      </c>
+      <c r="C83" t="s">
+        <v>338</v>
+      </c>
+      <c r="D83" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A84">
+        <v>300</v>
+      </c>
+      <c r="B84" t="s">
+        <v>337</v>
+      </c>
+      <c r="C84" t="s">
+        <v>338</v>
+      </c>
+      <c r="D84" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A85">
+        <v>360</v>
+      </c>
+      <c r="B85" t="s">
+        <v>337</v>
+      </c>
+      <c r="C85" t="s">
+        <v>338</v>
+      </c>
+      <c r="D85" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A86">
+        <v>420</v>
+      </c>
+      <c r="B86" t="s">
+        <v>337</v>
+      </c>
+      <c r="C86" t="s">
+        <v>338</v>
+      </c>
+      <c r="D86" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A87">
+        <v>480</v>
+      </c>
+      <c r="B87" t="s">
+        <v>337</v>
+      </c>
+      <c r="C87" t="s">
+        <v>338</v>
+      </c>
+      <c r="D87" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A88">
+        <v>540</v>
+      </c>
+      <c r="B88" t="s">
+        <v>337</v>
+      </c>
+      <c r="C88" t="s">
+        <v>338</v>
+      </c>
+      <c r="D88" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A89">
+        <v>600</v>
+      </c>
+      <c r="B89" t="s">
+        <v>337</v>
+      </c>
+      <c r="C89" t="s">
+        <v>338</v>
+      </c>
+      <c r="D89" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A90">
+        <v>660</v>
+      </c>
+      <c r="B90" t="s">
+        <v>337</v>
+      </c>
+      <c r="C90" t="s">
+        <v>338</v>
+      </c>
+      <c r="D90" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A91">
+        <v>720</v>
+      </c>
+      <c r="B91" t="s">
+        <v>337</v>
+      </c>
+      <c r="C91" t="s">
+        <v>338</v>
+      </c>
+      <c r="D91" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A92">
+        <v>780</v>
+      </c>
+      <c r="B92" t="s">
+        <v>337</v>
+      </c>
+      <c r="C92" t="s">
+        <v>338</v>
+      </c>
+      <c r="D92" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A93">
+        <v>0</v>
+      </c>
+      <c r="B93" t="s">
+        <v>337</v>
+      </c>
+      <c r="C93" t="s">
+        <v>338</v>
+      </c>
+      <c r="D93" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A94">
+        <v>60</v>
+      </c>
+      <c r="B94" t="s">
+        <v>337</v>
+      </c>
+      <c r="C94" t="s">
+        <v>338</v>
+      </c>
+      <c r="D94" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A95">
+        <v>120</v>
+      </c>
+      <c r="B95" t="s">
+        <v>337</v>
+      </c>
+      <c r="C95" t="s">
+        <v>338</v>
+      </c>
+      <c r="D95" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A96">
+        <v>180</v>
+      </c>
+      <c r="B96" t="s">
+        <v>337</v>
+      </c>
+      <c r="C96" t="s">
+        <v>338</v>
+      </c>
+      <c r="D96" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A97">
+        <v>240</v>
+      </c>
+      <c r="B97" t="s">
+        <v>337</v>
+      </c>
+      <c r="C97" t="s">
+        <v>338</v>
+      </c>
+      <c r="D97" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A98">
+        <v>300</v>
+      </c>
+      <c r="B98" t="s">
+        <v>337</v>
+      </c>
+      <c r="C98" t="s">
+        <v>338</v>
+      </c>
+      <c r="D98" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A99">
+        <v>360</v>
+      </c>
+      <c r="B99" t="s">
+        <v>337</v>
+      </c>
+      <c r="C99" t="s">
+        <v>338</v>
+      </c>
+      <c r="D99" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A100">
+        <v>0</v>
+      </c>
+      <c r="B100" t="s">
+        <v>337</v>
+      </c>
+      <c r="C100" t="s">
+        <v>338</v>
+      </c>
+      <c r="D100" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A101">
+        <v>60</v>
+      </c>
+      <c r="B101" t="s">
+        <v>337</v>
+      </c>
+      <c r="C101" t="s">
+        <v>338</v>
+      </c>
+      <c r="D101" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A102">
+        <v>120</v>
+      </c>
+      <c r="B102" t="s">
+        <v>337</v>
+      </c>
+      <c r="C102" t="s">
+        <v>338</v>
+      </c>
+      <c r="D102" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A103">
+        <v>180</v>
+      </c>
+      <c r="B103" t="s">
+        <v>337</v>
+      </c>
+      <c r="C103" t="s">
+        <v>338</v>
+      </c>
+      <c r="D103" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A104">
+        <v>240</v>
+      </c>
+      <c r="B104" t="s">
+        <v>337</v>
+      </c>
+      <c r="C104" t="s">
+        <v>338</v>
+      </c>
+      <c r="D104" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A105">
+        <v>300</v>
+      </c>
+      <c r="B105" t="s">
+        <v>337</v>
+      </c>
+      <c r="C105" t="s">
+        <v>338</v>
+      </c>
+      <c r="D105" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A106">
+        <v>360</v>
+      </c>
+      <c r="B106" t="s">
+        <v>337</v>
+      </c>
+      <c r="C106" t="s">
+        <v>338</v>
+      </c>
+      <c r="D106" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A107">
+        <v>420</v>
+      </c>
+      <c r="B107" t="s">
+        <v>337</v>
+      </c>
+      <c r="C107" t="s">
+        <v>338</v>
+      </c>
+      <c r="D107" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A108">
+        <v>480</v>
+      </c>
+      <c r="B108" t="s">
+        <v>337</v>
+      </c>
+      <c r="C108" t="s">
+        <v>338</v>
+      </c>
+      <c r="D108" t="s">
+        <v>197</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:CL15"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -10766,7 +13038,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C79A2F0D-0642-4C0E-8D2C-134A58C1CED4}">
   <dimension ref="A1:O15"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -11283,7 +13555,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A29EEC2-1BB3-40E4-97B4-D8227D81F07F}">
   <dimension ref="A1:AD15"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -12355,7 +14627,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0222AAA1-4358-484C-B7F2-43704DA71319}">
   <dimension ref="A1:E259"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>

--- a/Recordings/SavedData/v2_no_low_sampled/60s_resampled[analysis].xlsx
+++ b/Recordings/SavedData/v2_no_low_sampled/60s_resampled[analysis].xlsx
@@ -8,17 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dobregeo\Documents\GitHub\vilearn_ml\Recordings\SavedData\v2_no_low_sampled\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{366B12A7-9ECB-448A-A137-96937BA20BFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1F6C7F4-4DE1-4968-A782-52BE045B8251}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="6315" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="All Data" sheetId="5" r:id="rId1"/>
-    <sheet name="ExtraDyads" sheetId="6" r:id="rId2"/>
-    <sheet name="1d_DG" sheetId="1" r:id="rId3"/>
-    <sheet name="MG" sheetId="2" r:id="rId4"/>
-    <sheet name="TE" sheetId="3" r:id="rId5"/>
-    <sheet name="Blinks" sheetId="4" r:id="rId6"/>
+    <sheet name="ExtraTriads" sheetId="7" r:id="rId2"/>
+    <sheet name="ExtraDyads" sheetId="6" r:id="rId3"/>
+    <sheet name="1d_DG" sheetId="1" r:id="rId4"/>
+    <sheet name="MG" sheetId="2" r:id="rId5"/>
+    <sheet name="TE" sheetId="3" r:id="rId6"/>
+    <sheet name="Blinks" sheetId="4" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1689" uniqueCount="343">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2102" uniqueCount="357">
   <si>
     <t>seconds_interaction_window</t>
   </si>
@@ -1070,6 +1071,48 @@
   </si>
   <si>
     <t>dyad_01_0_D1</t>
+  </si>
+  <si>
+    <t>triad_01_0_D1</t>
+  </si>
+  <si>
+    <t>triad_01_1_D1</t>
+  </si>
+  <si>
+    <t>triad_01_2_D1_same</t>
+  </si>
+  <si>
+    <t>triad_01_2_D1_different</t>
+  </si>
+  <si>
+    <t>triad_01_3_D1</t>
+  </si>
+  <si>
+    <t>triad_01_MG_D1</t>
+  </si>
+  <si>
+    <t>triad_01_MG_D0</t>
+  </si>
+  <si>
+    <t>0_D1</t>
+  </si>
+  <si>
+    <t>1_D1</t>
+  </si>
+  <si>
+    <t>2_D1_same</t>
+  </si>
+  <si>
+    <t>2_D1_different</t>
+  </si>
+  <si>
+    <t>3_D1</t>
+  </si>
+  <si>
+    <t>MG_D1</t>
+  </si>
+  <si>
+    <t>MG_D0</t>
   </si>
 </sst>
 </file>
@@ -8268,11 +8311,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F126CFC9-BE8B-4DAF-AADB-1B89D72E9205}">
-  <dimension ref="A1:E108"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B780FF01-0A38-4003-BA42-FA6B1F48FFCE}">
+  <dimension ref="A1:P131"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -8286,1537 +8329,6519 @@
         <v>307</v>
       </c>
       <c r="E1" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+        <v>308</v>
+      </c>
+      <c r="F1" t="s">
+        <v>309</v>
+      </c>
+      <c r="G1" t="s">
+        <v>310</v>
+      </c>
+      <c r="H1" t="s">
+        <v>311</v>
+      </c>
+      <c r="I1" t="s">
+        <v>341</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C2" t="s">
         <v>338</v>
       </c>
       <c r="D2" t="s">
-        <v>110</v>
+        <v>208</v>
       </c>
       <c r="E2">
-        <v>0.87554664723032005</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+        <v>0.53146061768759201</v>
+      </c>
+      <c r="F2">
+        <v>0.31603870702079401</v>
+      </c>
+      <c r="G2">
+        <v>0.23924233065678366</v>
+      </c>
+      <c r="H2">
+        <v>13</v>
+      </c>
+      <c r="I2">
+        <v>144.03214285714199</v>
+      </c>
+      <c r="J2">
+        <v>0.17376981675931599</v>
+      </c>
+      <c r="K2">
+        <v>0.391187976116944</v>
+      </c>
+      <c r="L2">
+        <v>4.9619106444307101E-2</v>
+      </c>
+      <c r="M2">
+        <v>6.9384393658636995E-2</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>8.8532015647519002E-2</v>
+      </c>
+      <c r="P2">
+        <v>0.22750669137327501</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>60</v>
       </c>
       <c r="B3" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C3" t="s">
         <v>338</v>
       </c>
       <c r="D3" t="s">
-        <v>110</v>
+        <v>208</v>
       </c>
       <c r="E3">
-        <v>0.93689936536717999</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+        <v>3.2412930139259201E-2</v>
+      </c>
+      <c r="F3">
+        <v>7.0911722141823397E-2</v>
+      </c>
+      <c r="G3">
+        <v>0.17662462959134431</v>
+      </c>
+      <c r="H3">
+        <v>10.5</v>
+      </c>
+      <c r="I3">
+        <v>169.944444444444</v>
+      </c>
+      <c r="J3">
+        <v>0.47136654951416102</v>
+      </c>
+      <c r="K3">
+        <v>0.40066156708703698</v>
+      </c>
+      <c r="L3">
+        <v>3.1631176348976602E-2</v>
+      </c>
+      <c r="M3">
+        <v>2.4808765763903201E-2</v>
+      </c>
+      <c r="N3">
+        <v>6.2021914409758096E-4</v>
+      </c>
+      <c r="O3">
+        <v>1.44717800289435E-2</v>
+      </c>
+      <c r="P3">
+        <v>5.6439942112879803E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>120</v>
       </c>
       <c r="B4" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C4" t="s">
         <v>338</v>
       </c>
       <c r="D4" t="s">
-        <v>110</v>
+        <v>208</v>
       </c>
       <c r="E4">
-        <v>0.94897403304884698</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+        <v>0.487230359482407</v>
+      </c>
+      <c r="F4">
+        <v>5.1229084899814002E-2</v>
+      </c>
+      <c r="G4">
+        <v>0.19286648764029435</v>
+      </c>
+      <c r="H4">
+        <v>15</v>
+      </c>
+      <c r="I4">
+        <v>176.70074224021499</v>
+      </c>
+      <c r="J4">
+        <v>0.47531501755835498</v>
+      </c>
+      <c r="K4">
+        <v>0.37781450113612802</v>
+      </c>
+      <c r="L4">
+        <v>3.3051022516008999E-2</v>
+      </c>
+      <c r="M4">
+        <v>6.25903738896922E-2</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>9.5021689733526104E-3</v>
+      </c>
+      <c r="P4">
+        <v>4.1726915926461397E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>180</v>
       </c>
       <c r="B5" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C5" t="s">
         <v>338</v>
       </c>
       <c r="D5" t="s">
-        <v>110</v>
+        <v>208</v>
       </c>
       <c r="E5">
-        <v>0.97681999275624698</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+        <v>0.58234169113787004</v>
+      </c>
+      <c r="F5">
+        <v>0.14679461004491601</v>
+      </c>
+      <c r="G5">
+        <v>0.29032258064516103</v>
+      </c>
+      <c r="H5">
+        <v>14</v>
+      </c>
+      <c r="I5">
+        <v>178.493055555555</v>
+      </c>
+      <c r="J5">
+        <v>0.248264597795018</v>
+      </c>
+      <c r="K5">
+        <v>0.40955492037566299</v>
+      </c>
+      <c r="L5">
+        <v>0.111882400979991</v>
+      </c>
+      <c r="M5">
+        <v>7.9216006533278802E-2</v>
+      </c>
+      <c r="N5">
+        <v>4.2874642711310702E-3</v>
+      </c>
+      <c r="O5">
+        <v>6.6353613719885601E-2</v>
+      </c>
+      <c r="P5">
+        <v>8.04409963250306E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>240</v>
       </c>
       <c r="B6" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C6" t="s">
         <v>338</v>
       </c>
       <c r="D6" t="s">
-        <v>110</v>
+        <v>208</v>
       </c>
       <c r="E6">
-        <v>0.69329710144927503</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+        <v>0.72127053801287</v>
+      </c>
+      <c r="F6">
+        <v>0.15986045557151601</v>
+      </c>
+      <c r="G6">
+        <v>0.34831383815582434</v>
+      </c>
+      <c r="H6">
+        <v>30</v>
+      </c>
+      <c r="I6">
+        <v>168.67905875800599</v>
+      </c>
+      <c r="J6">
+        <v>0.11491894110404199</v>
+      </c>
+      <c r="K6">
+        <v>0.460086189205828</v>
+      </c>
+      <c r="L6">
+        <v>0.12887338395239001</v>
+      </c>
+      <c r="M6">
+        <v>0.13400369382310601</v>
+      </c>
+      <c r="N6">
+        <v>2.2573363431151201E-3</v>
+      </c>
+      <c r="O6">
+        <v>5.2329160681305102E-2</v>
+      </c>
+      <c r="P6">
+        <v>0.107531294890211</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>300</v>
       </c>
       <c r="B7" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C7" t="s">
         <v>338</v>
       </c>
       <c r="D7" t="s">
-        <v>110</v>
+        <v>208</v>
       </c>
       <c r="E7">
-        <v>0.97549909255898304</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+        <v>0.42212739762370299</v>
+      </c>
+      <c r="F7">
+        <v>2.5420254202542E-2</v>
+      </c>
+      <c r="G7">
+        <v>0.30852808528085252</v>
+      </c>
+      <c r="H7">
+        <v>31</v>
+      </c>
+      <c r="I7">
+        <v>182.648578048833</v>
+      </c>
+      <c r="J7">
+        <v>0.2790077900779</v>
+      </c>
+      <c r="K7">
+        <v>0.47437474374743699</v>
+      </c>
+      <c r="L7">
+        <v>0.170561705617056</v>
+      </c>
+      <c r="M7">
+        <v>4.8585485854858501E-2</v>
+      </c>
+      <c r="N7">
+        <v>2.0500205002049999E-3</v>
+      </c>
+      <c r="O7">
+        <v>6.7650676506765001E-3</v>
+      </c>
+      <c r="P7">
+        <v>1.8655186551865498E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>360</v>
       </c>
       <c r="B8" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C8" t="s">
         <v>338</v>
       </c>
       <c r="D8" t="s">
-        <v>110</v>
+        <v>208</v>
       </c>
       <c r="E8">
-        <v>0.93922452660054101</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+        <v>0.321562010515833</v>
+      </c>
+      <c r="F8">
+        <v>0.10339157245632</v>
+      </c>
+      <c r="G8">
+        <v>0.33874614594038999</v>
+      </c>
+      <c r="H8">
+        <v>18.5</v>
+      </c>
+      <c r="I8">
+        <v>178.25820707070699</v>
+      </c>
+      <c r="J8">
+        <v>0.20678314491264099</v>
+      </c>
+      <c r="K8">
+        <v>0.41459403905447001</v>
+      </c>
+      <c r="L8">
+        <v>0.13299075025693699</v>
+      </c>
+      <c r="M8">
+        <v>0.132579650565262</v>
+      </c>
+      <c r="N8">
+        <v>9.6608427543679303E-3</v>
+      </c>
+      <c r="O8">
+        <v>4.1521068859198297E-2</v>
+      </c>
+      <c r="P8">
+        <v>6.1870503597122303E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>420</v>
       </c>
       <c r="B9" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C9" t="s">
         <v>338</v>
       </c>
       <c r="D9" t="s">
-        <v>110</v>
+        <v>208</v>
       </c>
       <c r="E9">
-        <v>0.99460043196544201</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+        <v>2.38613526652777E-2</v>
+      </c>
+      <c r="F9">
+        <v>8.6313193588162695E-2</v>
+      </c>
+      <c r="G9">
+        <v>0.16098095629538234</v>
+      </c>
+      <c r="H9">
+        <v>9</v>
+      </c>
+      <c r="I9">
+        <v>142.9</v>
+      </c>
+      <c r="J9">
+        <v>0.496917385943279</v>
+      </c>
+      <c r="K9">
+        <v>0.35717221537196803</v>
+      </c>
+      <c r="L9">
+        <v>1.5824085491163101E-2</v>
+      </c>
+      <c r="M9">
+        <v>4.3773119605425397E-2</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>6.57624332100287E-3</v>
+      </c>
+      <c r="P9">
+        <v>7.9736950267159795E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>480</v>
       </c>
       <c r="B10" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C10" t="s">
         <v>338</v>
       </c>
       <c r="D10" t="s">
-        <v>110</v>
+        <v>208</v>
       </c>
       <c r="E10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+        <v>2.40754035643518E-2</v>
+      </c>
+      <c r="F10">
+        <v>0.13236481033091199</v>
+      </c>
+      <c r="G10">
+        <v>0.34375840731772905</v>
+      </c>
+      <c r="H10">
+        <v>17</v>
+      </c>
+      <c r="I10">
+        <v>177.69411764705799</v>
+      </c>
+      <c r="J10">
+        <v>0.20157384987893401</v>
+      </c>
+      <c r="K10">
+        <v>0.39164648910411598</v>
+      </c>
+      <c r="L10">
+        <v>0.107949959644874</v>
+      </c>
+      <c r="M10">
+        <v>0.135189669087974</v>
+      </c>
+      <c r="N10">
+        <v>3.1275221953188E-2</v>
+      </c>
+      <c r="O10">
+        <v>5.95238095238095E-2</v>
+      </c>
+      <c r="P10">
+        <v>7.2841000807102499E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>540</v>
       </c>
       <c r="B11" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C11" t="s">
         <v>338</v>
       </c>
       <c r="D11" t="s">
-        <v>110</v>
+        <v>208</v>
       </c>
       <c r="E11">
-        <v>0.93255184851217299</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+        <v>2.6711386281110999E-2</v>
+      </c>
+      <c r="F11">
+        <v>0.05</v>
+      </c>
+      <c r="G11">
+        <v>0.24802721088435331</v>
+      </c>
+      <c r="H11">
+        <v>14</v>
+      </c>
+      <c r="I11">
+        <v>148.61216931216899</v>
+      </c>
+      <c r="J11">
+        <v>0.37734693877551001</v>
+      </c>
+      <c r="K11">
+        <v>0.43244897959183598</v>
+      </c>
+      <c r="L11">
+        <v>4.8571428571428502E-2</v>
+      </c>
+      <c r="M11">
+        <v>0.09</v>
+      </c>
+      <c r="N11">
+        <v>1.6326530612244801E-3</v>
+      </c>
+      <c r="O11">
+        <v>2.9591836734693799E-2</v>
+      </c>
+      <c r="P11">
+        <v>2.04081632653061E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>600</v>
       </c>
       <c r="B12" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C12" t="s">
         <v>338</v>
       </c>
       <c r="D12" t="s">
-        <v>110</v>
+        <v>208</v>
       </c>
       <c r="E12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+        <v>0.63890952741620299</v>
+      </c>
+      <c r="F12">
+        <v>0.25056572721662201</v>
+      </c>
+      <c r="G12">
+        <v>0.24350270863333934</v>
+      </c>
+      <c r="H12">
+        <v>27</v>
+      </c>
+      <c r="I12">
+        <v>174.50207570207499</v>
+      </c>
+      <c r="J12">
+        <v>0.193581567578687</v>
+      </c>
+      <c r="K12">
+        <v>0.43715284920798098</v>
+      </c>
+      <c r="L12">
+        <v>2.0160460810532799E-2</v>
+      </c>
+      <c r="M12">
+        <v>9.8539395186175605E-2</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <v>5.5955564698621597E-2</v>
+      </c>
+      <c r="P12">
+        <v>0.19461016251800001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A13">
-        <v>0</v>
+        <v>660</v>
       </c>
       <c r="B13" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C13" t="s">
         <v>338</v>
       </c>
       <c r="D13" t="s">
-        <v>122</v>
+        <v>208</v>
       </c>
       <c r="E13">
-        <v>0.75100461378181205</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+        <v>0.65731285226509195</v>
+      </c>
+      <c r="F13">
+        <v>0.30931677018633502</v>
+      </c>
+      <c r="G13">
+        <v>0.28219461697722553</v>
+      </c>
+      <c r="H13">
+        <v>28.5</v>
+      </c>
+      <c r="I13">
+        <v>165.26580419580401</v>
+      </c>
+      <c r="J13">
+        <v>5.3209109730848803E-2</v>
+      </c>
+      <c r="K13">
+        <v>0.45548654244306402</v>
+      </c>
+      <c r="L13">
+        <v>0.125465838509316</v>
+      </c>
+      <c r="M13">
+        <v>5.6521739130434699E-2</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13">
+        <v>2.7122153209109701E-2</v>
+      </c>
+      <c r="P13">
+        <v>0.28219461697722498</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A14">
+        <v>720</v>
+      </c>
+      <c r="B14" t="s">
+        <v>339</v>
+      </c>
+      <c r="C14" t="s">
+        <v>338</v>
+      </c>
+      <c r="D14" t="s">
+        <v>208</v>
+      </c>
+      <c r="E14">
+        <v>0.32695114584769902</v>
+      </c>
+      <c r="F14">
+        <v>9.1016548463356897E-2</v>
+      </c>
+      <c r="G14">
+        <v>0.17592592592592568</v>
+      </c>
+      <c r="H14">
+        <v>19.5</v>
+      </c>
+      <c r="I14">
+        <v>170.83184789067101</v>
+      </c>
+      <c r="J14">
+        <v>0.50118203309692599</v>
+      </c>
+      <c r="K14">
+        <v>0.32505910165484603</v>
+      </c>
+      <c r="L14">
+        <v>1.5957446808510599E-2</v>
+      </c>
+      <c r="M14">
+        <v>5.9692671394799002E-2</v>
+      </c>
+      <c r="N14">
+        <v>7.09219858156028E-3</v>
+      </c>
+      <c r="O14">
+        <v>3.0141843971631201E-2</v>
+      </c>
+      <c r="P14">
+        <v>6.0874704491725697E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>0</v>
+      </c>
+      <c r="B15" t="s">
+        <v>339</v>
+      </c>
+      <c r="C15" t="s">
+        <v>338</v>
+      </c>
+      <c r="D15" t="s">
+        <v>252</v>
+      </c>
+      <c r="E15">
+        <v>4.17101436391666E-2</v>
+      </c>
+      <c r="F15">
+        <v>7.6563164610803898E-3</v>
+      </c>
+      <c r="G15">
+        <v>0.13809726357578317</v>
+      </c>
+      <c r="H15">
+        <v>5</v>
+      </c>
+      <c r="I15">
+        <v>169.722222222222</v>
+      </c>
+      <c r="J15">
+        <v>0.59187579753296404</v>
+      </c>
+      <c r="K15">
+        <v>0.38664398128455901</v>
+      </c>
+      <c r="L15">
+        <v>1.06337728626116E-2</v>
+      </c>
+      <c r="M15">
+        <v>3.1901318587834902E-3</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <v>7.6563164610803898E-3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A16">
         <v>60</v>
       </c>
-      <c r="B14" t="s">
-        <v>337</v>
-      </c>
-      <c r="C14" t="s">
-        <v>338</v>
-      </c>
-      <c r="D14" t="s">
-        <v>122</v>
-      </c>
-      <c r="E14">
-        <v>0.85975975975975905</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A15">
+      <c r="B16" t="s">
+        <v>339</v>
+      </c>
+      <c r="C16" t="s">
+        <v>338</v>
+      </c>
+      <c r="D16" t="s">
+        <v>252</v>
+      </c>
+      <c r="E16">
+        <v>0.59111725767722201</v>
+      </c>
+      <c r="F16">
+        <v>3.2613299449385798E-2</v>
+      </c>
+      <c r="G16">
+        <v>0.11647606946209203</v>
+      </c>
+      <c r="H16">
+        <v>19</v>
+      </c>
+      <c r="I16">
+        <v>195.7</v>
+      </c>
+      <c r="J16">
+        <v>0.65353663701821196</v>
+      </c>
+      <c r="K16">
+        <v>0.288860652265989</v>
+      </c>
+      <c r="L16">
+        <v>7.6238881829733098E-3</v>
+      </c>
+      <c r="M16">
+        <v>7.4121135112240498E-3</v>
+      </c>
+      <c r="N16">
+        <v>9.9534095722151605E-3</v>
+      </c>
+      <c r="O16">
+        <v>6.3532401524777596E-4</v>
+      </c>
+      <c r="P16">
+        <v>3.1977975434138002E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A17">
         <v>120</v>
       </c>
-      <c r="B15" t="s">
-        <v>337</v>
-      </c>
-      <c r="C15" t="s">
-        <v>338</v>
-      </c>
-      <c r="D15" t="s">
-        <v>122</v>
-      </c>
-      <c r="E15">
-        <v>0.93885542168674696</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A16">
+      <c r="B17" t="s">
+        <v>339</v>
+      </c>
+      <c r="C17" t="s">
+        <v>338</v>
+      </c>
+      <c r="D17" t="s">
+        <v>252</v>
+      </c>
+      <c r="E17">
+        <v>0.74489593490564798</v>
+      </c>
+      <c r="F17">
+        <v>4.4266441821247896E-3</v>
+      </c>
+      <c r="G17">
+        <v>7.27234401349071E-2</v>
+      </c>
+      <c r="H17">
+        <v>24</v>
+      </c>
+      <c r="I17">
+        <v>171.611413043478</v>
+      </c>
+      <c r="J17">
+        <v>0.78098650927487301</v>
+      </c>
+      <c r="K17">
+        <v>0.211003372681281</v>
+      </c>
+      <c r="L17">
+        <v>2.9510961214165199E-3</v>
+      </c>
+      <c r="M17">
+        <v>6.3237774030354096E-4</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <v>4.4266441821247896E-3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A18">
         <v>180</v>
       </c>
-      <c r="B16" t="s">
-        <v>337</v>
-      </c>
-      <c r="C16" t="s">
-        <v>338</v>
-      </c>
-      <c r="D16" t="s">
-        <v>122</v>
-      </c>
-      <c r="E16">
-        <v>0.78962278216788395</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A17">
+      <c r="B18" t="s">
+        <v>339</v>
+      </c>
+      <c r="C18" t="s">
+        <v>338</v>
+      </c>
+      <c r="D18" t="s">
+        <v>252</v>
+      </c>
+      <c r="E18">
+        <v>0.74045038835777699</v>
+      </c>
+      <c r="F18">
+        <v>8.4656084656084592E-3</v>
+      </c>
+      <c r="G18">
+        <v>7.5908289241622531E-2</v>
+      </c>
+      <c r="H18">
+        <v>20</v>
+      </c>
+      <c r="I18">
+        <v>178.39682539682499</v>
+      </c>
+      <c r="J18">
+        <v>0.77015873015873004</v>
+      </c>
+      <c r="K18">
+        <v>0.21502645502645501</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <v>6.3492063492063397E-3</v>
+      </c>
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="O18">
+        <v>0</v>
+      </c>
+      <c r="P18">
+        <v>8.4656084656084592E-3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A19">
         <v>240</v>
       </c>
-      <c r="B17" t="s">
-        <v>337</v>
-      </c>
-      <c r="C17" t="s">
-        <v>338</v>
-      </c>
-      <c r="D17" t="s">
-        <v>122</v>
-      </c>
-      <c r="E17">
-        <v>0.93130799161927502</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A18">
+      <c r="B19" t="s">
+        <v>339</v>
+      </c>
+      <c r="C19" t="s">
+        <v>338</v>
+      </c>
+      <c r="D19" t="s">
+        <v>252</v>
+      </c>
+      <c r="E19">
+        <v>0.76282026927185198</v>
+      </c>
+      <c r="F19">
+        <v>6.7854113655640303E-3</v>
+      </c>
+      <c r="G19">
+        <v>0.12326830647441304</v>
+      </c>
+      <c r="H19">
+        <v>21</v>
+      </c>
+      <c r="I19">
+        <v>188.340595497458</v>
+      </c>
+      <c r="J19">
+        <v>0.63952502120441002</v>
+      </c>
+      <c r="K19">
+        <v>0.33757421543680999</v>
+      </c>
+      <c r="L19">
+        <v>1.2298558100084799E-2</v>
+      </c>
+      <c r="M19">
+        <v>3.81679389312977E-3</v>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19">
+        <v>6.7854113655640303E-3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A20">
         <v>300</v>
       </c>
-      <c r="B18" t="s">
-        <v>337</v>
-      </c>
-      <c r="C18" t="s">
-        <v>338</v>
-      </c>
-      <c r="D18" t="s">
-        <v>122</v>
-      </c>
-      <c r="E18">
-        <v>0.88182632050134202</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A19">
+      <c r="B20" t="s">
+        <v>339</v>
+      </c>
+      <c r="C20" t="s">
+        <v>338</v>
+      </c>
+      <c r="D20" t="s">
+        <v>252</v>
+      </c>
+      <c r="E20">
+        <v>0.76668677314185196</v>
+      </c>
+      <c r="F20">
+        <v>8.3194675540765295E-4</v>
+      </c>
+      <c r="G20">
+        <v>0.10323072656683295</v>
+      </c>
+      <c r="H20">
+        <v>24</v>
+      </c>
+      <c r="I20">
+        <v>187.096296296296</v>
+      </c>
+      <c r="J20">
+        <v>0.69758735440931696</v>
+      </c>
+      <c r="K20">
+        <v>0.29346921797004899</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
+        <v>8.1114808652246202E-3</v>
+      </c>
+      <c r="N20">
+        <v>0</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20">
+        <v>8.3194675540765295E-4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A21">
         <v>360</v>
       </c>
-      <c r="B19" t="s">
-        <v>337</v>
-      </c>
-      <c r="C19" t="s">
-        <v>338</v>
-      </c>
-      <c r="D19" t="s">
-        <v>122</v>
-      </c>
-      <c r="E19">
-        <v>0.65941043083900197</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A20">
+      <c r="B21" t="s">
+        <v>339</v>
+      </c>
+      <c r="C21" t="s">
+        <v>338</v>
+      </c>
+      <c r="D21" t="s">
+        <v>252</v>
+      </c>
+      <c r="E21">
+        <v>0.67676970490481403</v>
+      </c>
+      <c r="F21">
+        <v>4.0092846592107998E-3</v>
+      </c>
+      <c r="G21">
+        <v>0.1403249630723781</v>
+      </c>
+      <c r="H21">
+        <v>21.5</v>
+      </c>
+      <c r="I21">
+        <v>190.119262119262</v>
+      </c>
+      <c r="J21">
+        <v>0.61489765773369898</v>
+      </c>
+      <c r="K21">
+        <v>0.34121122599704501</v>
+      </c>
+      <c r="L21">
+        <v>2.5110782865583402E-2</v>
+      </c>
+      <c r="M21">
+        <v>1.47710487444608E-2</v>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21">
+        <v>0</v>
+      </c>
+      <c r="P21">
+        <v>4.0092846592107998E-3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A22">
         <v>420</v>
       </c>
-      <c r="B20" t="s">
-        <v>337</v>
-      </c>
-      <c r="C20" t="s">
-        <v>338</v>
-      </c>
-      <c r="D20" t="s">
-        <v>122</v>
-      </c>
-      <c r="E20">
-        <v>0.77470116507792397</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A21">
+      <c r="B22" t="s">
+        <v>339</v>
+      </c>
+      <c r="C22" t="s">
+        <v>338</v>
+      </c>
+      <c r="D22" t="s">
+        <v>252</v>
+      </c>
+      <c r="E22">
+        <v>0.567710327420343</v>
+      </c>
+      <c r="F22">
+        <v>3.6072144288577098E-3</v>
+      </c>
+      <c r="G22">
+        <v>5.4375417501669771E-2</v>
+      </c>
+      <c r="H22">
+        <v>17.5</v>
+      </c>
+      <c r="I22">
+        <v>182.79544159544099</v>
+      </c>
+      <c r="J22">
+        <v>0.84088176352705402</v>
+      </c>
+      <c r="K22">
+        <v>0.14789579158316599</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <v>7.6152304609218404E-3</v>
+      </c>
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <v>3.6072144288577098E-3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>0</v>
+      </c>
+      <c r="B23" t="s">
+        <v>339</v>
+      </c>
+      <c r="C23" t="s">
+        <v>338</v>
+      </c>
+      <c r="D23" t="s">
+        <v>221</v>
+      </c>
+      <c r="E23">
+        <v>0.46012231577120299</v>
+      </c>
+      <c r="F23">
+        <v>8.1888246628131003E-3</v>
+      </c>
+      <c r="G23">
+        <v>3.3076429030186233E-2</v>
+      </c>
+      <c r="H23">
+        <v>4</v>
+      </c>
+      <c r="I23">
+        <v>199.5</v>
+      </c>
+      <c r="J23">
+        <v>0.89258188824662799</v>
+      </c>
+      <c r="K23">
+        <v>9.9229287090558699E-2</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23">
+        <v>0</v>
+      </c>
+      <c r="P23">
+        <v>8.1888246628131003E-3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A24">
+        <v>60</v>
+      </c>
+      <c r="B24" t="s">
+        <v>339</v>
+      </c>
+      <c r="C24" t="s">
+        <v>338</v>
+      </c>
+      <c r="D24" t="s">
+        <v>221</v>
+      </c>
+      <c r="E24">
+        <v>0.65120080052092499</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>3.6824027478233032E-2</v>
+      </c>
+      <c r="H24">
+        <v>23.5</v>
+      </c>
+      <c r="I24">
+        <v>178.081529581529</v>
+      </c>
+      <c r="J24">
+        <v>0.88952791756530003</v>
+      </c>
+      <c r="K24">
+        <v>0.110472082434699</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24">
+        <v>0</v>
+      </c>
+      <c r="O24">
+        <v>0</v>
+      </c>
+      <c r="P24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A25">
+        <v>120</v>
+      </c>
+      <c r="B25" t="s">
+        <v>339</v>
+      </c>
+      <c r="C25" t="s">
+        <v>338</v>
+      </c>
+      <c r="D25" t="s">
+        <v>221</v>
+      </c>
+      <c r="E25">
+        <v>0.49674356673592501</v>
+      </c>
+      <c r="F25">
+        <v>2.1333333333333301E-2</v>
+      </c>
+      <c r="G25">
+        <v>0.11078787878787855</v>
+      </c>
+      <c r="H25">
+        <v>26</v>
+      </c>
+      <c r="I25">
+        <v>183.40486633249699</v>
+      </c>
+      <c r="J25">
+        <v>0.66787878787878696</v>
+      </c>
+      <c r="K25">
+        <v>0.28921212121212098</v>
+      </c>
+      <c r="L25">
+        <v>1.21212121212121E-3</v>
+      </c>
+      <c r="M25">
+        <v>2.0363636363636299E-2</v>
+      </c>
+      <c r="N25">
+        <v>0</v>
+      </c>
+      <c r="O25">
+        <v>0</v>
+      </c>
+      <c r="P25">
+        <v>2.1333333333333301E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A26">
+        <v>180</v>
+      </c>
+      <c r="B26" t="s">
+        <v>339</v>
+      </c>
+      <c r="C26" t="s">
+        <v>338</v>
+      </c>
+      <c r="D26" t="s">
+        <v>221</v>
+      </c>
+      <c r="E26">
+        <v>0.57479954083222196</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>2.1398578811369501E-2</v>
+      </c>
+      <c r="H26">
+        <v>22</v>
+      </c>
+      <c r="I26">
+        <v>167.24444444444401</v>
+      </c>
+      <c r="J26">
+        <v>0.93580426356589097</v>
+      </c>
+      <c r="K26">
+        <v>6.4195736434108502E-2</v>
+      </c>
+      <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26">
+        <v>0</v>
+      </c>
+      <c r="N26">
+        <v>0</v>
+      </c>
+      <c r="O26">
+        <v>0</v>
+      </c>
+      <c r="P26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A27">
+        <v>240</v>
+      </c>
+      <c r="B27" t="s">
+        <v>339</v>
+      </c>
+      <c r="C27" t="s">
+        <v>338</v>
+      </c>
+      <c r="D27" t="s">
+        <v>221</v>
+      </c>
+      <c r="E27">
+        <v>0.22791949873092501</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27">
+        <v>2.8135895564744967E-2</v>
+      </c>
+      <c r="H27">
+        <v>19.5</v>
+      </c>
+      <c r="I27">
+        <v>182.32692307692301</v>
+      </c>
+      <c r="J27">
+        <v>0.91559231330576496</v>
+      </c>
+      <c r="K27">
+        <v>8.4407686694234901E-2</v>
+      </c>
+      <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27">
+        <v>0</v>
+      </c>
+      <c r="N27">
+        <v>0</v>
+      </c>
+      <c r="O27">
+        <v>0</v>
+      </c>
+      <c r="P27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A28">
+        <v>300</v>
+      </c>
+      <c r="B28" t="s">
+        <v>339</v>
+      </c>
+      <c r="C28" t="s">
+        <v>338</v>
+      </c>
+      <c r="D28" t="s">
+        <v>221</v>
+      </c>
+      <c r="E28">
+        <v>0.36249643173250001</v>
+      </c>
+      <c r="F28">
+        <v>0</v>
+      </c>
+      <c r="G28">
+        <v>4.2440318302387169E-2</v>
+      </c>
+      <c r="H28">
+        <v>27</v>
+      </c>
+      <c r="I28">
+        <v>167.17283950617201</v>
+      </c>
+      <c r="J28">
+        <v>0.872679045092838</v>
+      </c>
+      <c r="K28">
+        <v>0.127320954907161</v>
+      </c>
+      <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="M28">
+        <v>0</v>
+      </c>
+      <c r="N28">
+        <v>0</v>
+      </c>
+      <c r="O28">
+        <v>0</v>
+      </c>
+      <c r="P28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A29">
+        <v>360</v>
+      </c>
+      <c r="B29" t="s">
+        <v>339</v>
+      </c>
+      <c r="C29" t="s">
+        <v>338</v>
+      </c>
+      <c r="D29" t="s">
+        <v>221</v>
+      </c>
+      <c r="E29">
+        <v>0.664064733666203</v>
+      </c>
+      <c r="F29">
+        <v>0</v>
+      </c>
+      <c r="G29">
+        <v>2.8398058252427166E-2</v>
+      </c>
+      <c r="H29">
+        <v>26.5</v>
+      </c>
+      <c r="I29">
+        <v>177.72898550724599</v>
+      </c>
+      <c r="J29">
+        <v>0.91480582524271803</v>
+      </c>
+      <c r="K29">
+        <v>8.5194174757281499E-2</v>
+      </c>
+      <c r="L29">
+        <v>0</v>
+      </c>
+      <c r="M29">
+        <v>0</v>
+      </c>
+      <c r="N29">
+        <v>0</v>
+      </c>
+      <c r="O29">
+        <v>0</v>
+      </c>
+      <c r="P29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A30">
+        <v>420</v>
+      </c>
+      <c r="B30" t="s">
+        <v>339</v>
+      </c>
+      <c r="C30" t="s">
+        <v>338</v>
+      </c>
+      <c r="D30" t="s">
+        <v>221</v>
+      </c>
+      <c r="E30">
+        <v>0.35336908102981401</v>
+      </c>
+      <c r="F30">
+        <v>4.7619047619047597E-4</v>
+      </c>
+      <c r="G30">
+        <v>5.9841269841269772E-2</v>
+      </c>
+      <c r="H30">
+        <v>23.5</v>
+      </c>
+      <c r="I30">
+        <v>192.42458521870199</v>
+      </c>
+      <c r="J30">
+        <v>0.83142857142857096</v>
+      </c>
+      <c r="K30">
+        <v>0.15666666666666601</v>
+      </c>
+      <c r="L30">
+        <v>2.6190476190476098E-3</v>
+      </c>
+      <c r="M30">
+        <v>8.8095238095238001E-3</v>
+      </c>
+      <c r="N30">
+        <v>0</v>
+      </c>
+      <c r="O30">
+        <v>0</v>
+      </c>
+      <c r="P30">
+        <v>4.7619047619047597E-4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A31">
         <v>480</v>
       </c>
-      <c r="B21" t="s">
-        <v>337</v>
-      </c>
-      <c r="C21" t="s">
-        <v>338</v>
-      </c>
-      <c r="D21" t="s">
-        <v>122</v>
-      </c>
-      <c r="E21">
-        <v>0.77791718946047606</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A22">
-        <v>0</v>
-      </c>
-      <c r="B22" t="s">
-        <v>337</v>
-      </c>
-      <c r="C22" t="s">
-        <v>338</v>
-      </c>
-      <c r="D22" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A23">
+      <c r="B31" t="s">
+        <v>339</v>
+      </c>
+      <c r="C31" t="s">
+        <v>338</v>
+      </c>
+      <c r="D31" t="s">
+        <v>221</v>
+      </c>
+      <c r="E31">
+        <v>0.33091328855027702</v>
+      </c>
+      <c r="F31">
+        <v>0</v>
+      </c>
+      <c r="G31">
+        <v>3.3817594834543975E-2</v>
+      </c>
+      <c r="H31">
+        <v>27</v>
+      </c>
+      <c r="I31">
+        <v>191.969607843137</v>
+      </c>
+      <c r="J31">
+        <v>0.89854721549636796</v>
+      </c>
+      <c r="K31">
+        <v>0.101452784503631</v>
+      </c>
+      <c r="L31">
+        <v>0</v>
+      </c>
+      <c r="M31">
+        <v>0</v>
+      </c>
+      <c r="N31">
+        <v>0</v>
+      </c>
+      <c r="O31">
+        <v>0</v>
+      </c>
+      <c r="P31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A32">
+        <v>540</v>
+      </c>
+      <c r="B32" t="s">
+        <v>339</v>
+      </c>
+      <c r="C32" t="s">
+        <v>338</v>
+      </c>
+      <c r="D32" t="s">
+        <v>221</v>
+      </c>
+      <c r="E32">
+        <v>0.54873259226009197</v>
+      </c>
+      <c r="F32">
+        <v>0</v>
+      </c>
+      <c r="G32">
+        <v>2.4187089540285117E-2</v>
+      </c>
+      <c r="H32">
+        <v>22</v>
+      </c>
+      <c r="I32">
+        <v>180.059523809523</v>
+      </c>
+      <c r="J32">
+        <v>0.92743873137914401</v>
+      </c>
+      <c r="K32">
+        <v>7.2561268620855296E-2</v>
+      </c>
+      <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32">
+        <v>0</v>
+      </c>
+      <c r="N32">
+        <v>0</v>
+      </c>
+      <c r="O32">
+        <v>0</v>
+      </c>
+      <c r="P32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A33">
+        <v>600</v>
+      </c>
+      <c r="B33" t="s">
+        <v>339</v>
+      </c>
+      <c r="C33" t="s">
+        <v>338</v>
+      </c>
+      <c r="D33" t="s">
+        <v>221</v>
+      </c>
+      <c r="E33">
+        <v>0.41040564839955601</v>
+      </c>
+      <c r="F33">
+        <v>0</v>
+      </c>
+      <c r="G33">
+        <v>4.9400479616306926E-2</v>
+      </c>
+      <c r="H33">
+        <v>22.5</v>
+      </c>
+      <c r="I33">
+        <v>202.383620689655</v>
+      </c>
+      <c r="J33">
+        <v>0.85179856115107899</v>
+      </c>
+      <c r="K33">
+        <v>0.14820143884892001</v>
+      </c>
+      <c r="L33">
+        <v>0</v>
+      </c>
+      <c r="M33">
+        <v>0</v>
+      </c>
+      <c r="N33">
+        <v>0</v>
+      </c>
+      <c r="O33">
+        <v>0</v>
+      </c>
+      <c r="P33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A34">
+        <v>0</v>
+      </c>
+      <c r="B34" t="s">
+        <v>339</v>
+      </c>
+      <c r="C34" t="s">
+        <v>338</v>
+      </c>
+      <c r="D34" t="s">
+        <v>223</v>
+      </c>
+      <c r="E34">
+        <v>0.48420072937444403</v>
+      </c>
+      <c r="F34">
+        <v>0</v>
+      </c>
+      <c r="G34">
+        <v>0.15805976834965102</v>
+      </c>
+      <c r="H34">
+        <v>2</v>
+      </c>
+      <c r="I34">
+        <v>139.555555555555</v>
+      </c>
+      <c r="J34">
+        <v>0.53311576118256798</v>
+      </c>
+      <c r="K34">
+        <v>0.45958917258590898</v>
+      </c>
+      <c r="L34">
+        <v>3.2635822614705298E-3</v>
+      </c>
+      <c r="M34">
+        <v>4.0314839700518303E-3</v>
+      </c>
+      <c r="N34">
+        <v>0</v>
+      </c>
+      <c r="O34">
+        <v>0</v>
+      </c>
+      <c r="P34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A35">
         <v>60</v>
       </c>
-      <c r="B23" t="s">
-        <v>337</v>
-      </c>
-      <c r="C23" t="s">
-        <v>338</v>
-      </c>
-      <c r="D23" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A24">
+      <c r="B35" t="s">
+        <v>339</v>
+      </c>
+      <c r="C35" t="s">
+        <v>338</v>
+      </c>
+      <c r="D35" t="s">
+        <v>223</v>
+      </c>
+      <c r="E35">
+        <v>0.51610955136453696</v>
+      </c>
+      <c r="F35">
+        <v>3.8381937911570997E-2</v>
+      </c>
+      <c r="G35">
+        <v>0.11545939165882664</v>
+      </c>
+      <c r="H35">
+        <v>5.5</v>
+      </c>
+      <c r="I35">
+        <v>173.03333333333299</v>
+      </c>
+      <c r="J35">
+        <v>0.63367826904985802</v>
+      </c>
+      <c r="K35">
+        <v>0.30950141110065799</v>
+      </c>
+      <c r="L35">
+        <v>9.2191909689557806E-3</v>
+      </c>
+      <c r="M35">
+        <v>9.2191909689557806E-3</v>
+      </c>
+      <c r="N35">
+        <v>0</v>
+      </c>
+      <c r="O35">
+        <v>0</v>
+      </c>
+      <c r="P35">
+        <v>3.8381937911570997E-2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A36">
         <v>120</v>
       </c>
-      <c r="B24" t="s">
-        <v>337</v>
-      </c>
-      <c r="C24" t="s">
-        <v>338</v>
-      </c>
-      <c r="D24" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A25">
+      <c r="B36" t="s">
+        <v>339</v>
+      </c>
+      <c r="C36" t="s">
+        <v>338</v>
+      </c>
+      <c r="D36" t="s">
+        <v>223</v>
+      </c>
+      <c r="E36">
+        <v>0.60986177301768496</v>
+      </c>
+      <c r="F36">
+        <v>1.7870302137067001E-2</v>
+      </c>
+      <c r="G36">
+        <v>0.12748710390567405</v>
+      </c>
+      <c r="H36">
+        <v>9</v>
+      </c>
+      <c r="I36">
+        <v>139.17916666666599</v>
+      </c>
+      <c r="J36">
+        <v>0.606484893146647</v>
+      </c>
+      <c r="K36">
+        <v>0.36882829771554898</v>
+      </c>
+      <c r="L36">
+        <v>4.97420781134856E-3</v>
+      </c>
+      <c r="M36">
+        <v>1.84229918938835E-3</v>
+      </c>
+      <c r="N36">
+        <v>0</v>
+      </c>
+      <c r="O36">
+        <v>0</v>
+      </c>
+      <c r="P36">
+        <v>1.7870302137067001E-2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A37">
         <v>180</v>
       </c>
-      <c r="B25" t="s">
-        <v>337</v>
-      </c>
-      <c r="C25" t="s">
-        <v>338</v>
-      </c>
-      <c r="D25" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A26">
+      <c r="B37" t="s">
+        <v>339</v>
+      </c>
+      <c r="C37" t="s">
+        <v>338</v>
+      </c>
+      <c r="D37" t="s">
+        <v>223</v>
+      </c>
+      <c r="E37">
+        <v>0.63793794210092503</v>
+      </c>
+      <c r="F37">
+        <v>2.6345502446367998E-3</v>
+      </c>
+      <c r="G37">
+        <v>5.6580102872914262E-2</v>
+      </c>
+      <c r="H37">
+        <v>7</v>
+      </c>
+      <c r="I37">
+        <v>148.74853801169499</v>
+      </c>
+      <c r="J37">
+        <v>0.83684606699284902</v>
+      </c>
+      <c r="K37">
+        <v>0.151486639066616</v>
+      </c>
+      <c r="L37">
+        <v>3.76364320662401E-4</v>
+      </c>
+      <c r="M37">
+        <v>8.6563793752352201E-3</v>
+      </c>
+      <c r="N37">
+        <v>0</v>
+      </c>
+      <c r="O37">
+        <v>1.8818216033120001E-4</v>
+      </c>
+      <c r="P37">
+        <v>2.4463680843055998E-3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A38">
         <v>240</v>
       </c>
-      <c r="B26" t="s">
-        <v>337</v>
-      </c>
-      <c r="C26" t="s">
-        <v>338</v>
-      </c>
-      <c r="D26" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A27">
+      <c r="B38" t="s">
+        <v>339</v>
+      </c>
+      <c r="C38" t="s">
+        <v>338</v>
+      </c>
+      <c r="D38" t="s">
+        <v>223</v>
+      </c>
+      <c r="E38">
+        <v>0.71801256972518501</v>
+      </c>
+      <c r="F38">
+        <v>1.36632200886262E-2</v>
+      </c>
+      <c r="G38">
+        <v>7.4901526341703425E-2</v>
+      </c>
+      <c r="H38">
+        <v>6</v>
+      </c>
+      <c r="I38">
+        <v>143.25054466230901</v>
+      </c>
+      <c r="J38">
+        <v>0.76440177252584895</v>
+      </c>
+      <c r="K38">
+        <v>0.22064254062038399</v>
+      </c>
+      <c r="L38">
+        <v>5.5391432791728195E-4</v>
+      </c>
+      <c r="M38">
+        <v>7.3855243722304202E-4</v>
+      </c>
+      <c r="N38">
+        <v>0</v>
+      </c>
+      <c r="O38">
+        <v>1.4771048744460799E-3</v>
+      </c>
+      <c r="P38">
+        <v>1.21861152141802E-2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A39">
         <v>300</v>
       </c>
-      <c r="B27" t="s">
-        <v>337</v>
-      </c>
-      <c r="C27" t="s">
-        <v>338</v>
-      </c>
-      <c r="D27" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A28">
+      <c r="B39" t="s">
+        <v>339</v>
+      </c>
+      <c r="C39" t="s">
+        <v>338</v>
+      </c>
+      <c r="D39" t="s">
+        <v>223</v>
+      </c>
+      <c r="E39">
+        <v>0.68767058399472203</v>
+      </c>
+      <c r="F39">
+        <v>1.68823860438942E-2</v>
+      </c>
+      <c r="G39">
+        <v>0.18289251547552032</v>
+      </c>
+      <c r="H39">
+        <v>8</v>
+      </c>
+      <c r="I39">
+        <v>163.06709956709901</v>
+      </c>
+      <c r="J39">
+        <v>0.513787281935846</v>
+      </c>
+      <c r="K39">
+        <v>0.39317201275558</v>
+      </c>
+      <c r="L39">
+        <v>7.1468767585818799E-2</v>
+      </c>
+      <c r="M39">
+        <v>4.6895516788595E-3</v>
+      </c>
+      <c r="N39">
+        <v>0</v>
+      </c>
+      <c r="O39">
+        <v>3.1888951416244602E-3</v>
+      </c>
+      <c r="P39">
+        <v>1.3693490902269701E-2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A40">
         <v>360</v>
       </c>
-      <c r="B28" t="s">
-        <v>337</v>
-      </c>
-      <c r="C28" t="s">
-        <v>338</v>
-      </c>
-      <c r="D28" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A29">
+      <c r="B40" t="s">
+        <v>339</v>
+      </c>
+      <c r="C40" t="s">
+        <v>338</v>
+      </c>
+      <c r="D40" t="s">
+        <v>223</v>
+      </c>
+      <c r="E40">
+        <v>0.29922529292703698</v>
+      </c>
+      <c r="F40">
+        <v>0</v>
+      </c>
+      <c r="G40">
+        <v>4.1041626079615499E-2</v>
+      </c>
+      <c r="H40">
+        <v>4.5</v>
+      </c>
+      <c r="I40">
+        <v>145.66865079364999</v>
+      </c>
+      <c r="J40">
+        <v>0.87901811805961405</v>
+      </c>
+      <c r="K40">
+        <v>0.11883888564192401</v>
+      </c>
+      <c r="L40">
+        <v>2.1429962984609299E-3</v>
+      </c>
+      <c r="M40">
+        <v>0</v>
+      </c>
+      <c r="N40">
+        <v>0</v>
+      </c>
+      <c r="O40">
+        <v>0</v>
+      </c>
+      <c r="P40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A41">
         <v>420</v>
       </c>
-      <c r="B29" t="s">
-        <v>337</v>
-      </c>
-      <c r="C29" t="s">
-        <v>338</v>
-      </c>
-      <c r="D29" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A30">
+      <c r="B41" t="s">
+        <v>339</v>
+      </c>
+      <c r="C41" t="s">
+        <v>338</v>
+      </c>
+      <c r="D41" t="s">
+        <v>223</v>
+      </c>
+      <c r="E41">
+        <v>0.64020429773009202</v>
+      </c>
+      <c r="F41">
+        <v>4.1766109785202803E-3</v>
+      </c>
+      <c r="G41">
+        <v>5.018562715460087E-2</v>
+      </c>
+      <c r="H41">
+        <v>11.5</v>
+      </c>
+      <c r="I41">
+        <v>178.324603174603</v>
+      </c>
+      <c r="J41">
+        <v>0.84626093874303898</v>
+      </c>
+      <c r="K41">
+        <v>0.14856801909307801</v>
+      </c>
+      <c r="L41">
+        <v>9.94431185361973E-4</v>
+      </c>
+      <c r="M41">
+        <v>0</v>
+      </c>
+      <c r="N41">
+        <v>0</v>
+      </c>
+      <c r="O41">
+        <v>0</v>
+      </c>
+      <c r="P41">
+        <v>4.1766109785202803E-3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A42">
         <v>480</v>
       </c>
-      <c r="B30" t="s">
-        <v>337</v>
-      </c>
-      <c r="C30" t="s">
-        <v>338</v>
-      </c>
-      <c r="D30" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A31">
+      <c r="B42" t="s">
+        <v>339</v>
+      </c>
+      <c r="C42" t="s">
+        <v>338</v>
+      </c>
+      <c r="D42" t="s">
+        <v>223</v>
+      </c>
+      <c r="E42">
+        <v>0.34961695278388799</v>
+      </c>
+      <c r="F42">
+        <v>8.4115805946791793E-3</v>
+      </c>
+      <c r="G42">
+        <v>0.1169144496609283</v>
+      </c>
+      <c r="H42">
+        <v>6.5</v>
+      </c>
+      <c r="I42">
+        <v>191.89807692307647</v>
+      </c>
+      <c r="J42">
+        <v>0.66392801251956102</v>
+      </c>
+      <c r="K42">
+        <v>0.30457746478873199</v>
+      </c>
+      <c r="L42">
+        <v>2.0735524256651001E-2</v>
+      </c>
+      <c r="M42">
+        <v>2.34741784037558E-3</v>
+      </c>
+      <c r="N42">
+        <v>0</v>
+      </c>
+      <c r="O42">
+        <v>0</v>
+      </c>
+      <c r="P42">
+        <v>8.4115805946791793E-3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A43">
         <v>540</v>
       </c>
-      <c r="B31" t="s">
-        <v>337</v>
-      </c>
-      <c r="C31" t="s">
-        <v>338</v>
-      </c>
-      <c r="D31" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A32">
+      <c r="B43" t="s">
+        <v>339</v>
+      </c>
+      <c r="C43" t="s">
+        <v>338</v>
+      </c>
+      <c r="D43" t="s">
+        <v>223</v>
+      </c>
+      <c r="E43">
+        <v>0.53847550232407404</v>
+      </c>
+      <c r="F43">
+        <v>7.22797421371361E-3</v>
+      </c>
+      <c r="G43">
+        <v>9.5786937552907125E-2</v>
+      </c>
+      <c r="H43">
+        <v>5</v>
+      </c>
+      <c r="I43">
+        <v>172.68</v>
+      </c>
+      <c r="J43">
+        <v>0.709318226216057</v>
+      </c>
+      <c r="K43">
+        <v>0.27993748779058403</v>
+      </c>
+      <c r="L43">
+        <v>0</v>
+      </c>
+      <c r="M43">
+        <v>3.5163117796444599E-3</v>
+      </c>
+      <c r="N43">
+        <v>0</v>
+      </c>
+      <c r="O43">
+        <v>3.9070130884938397E-4</v>
+      </c>
+      <c r="P43">
+        <v>6.8372729048642297E-3</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A44">
         <v>600</v>
       </c>
-      <c r="B32" t="s">
-        <v>337</v>
-      </c>
-      <c r="C32" t="s">
-        <v>338</v>
-      </c>
-      <c r="D32" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A33">
+      <c r="B44" t="s">
+        <v>339</v>
+      </c>
+      <c r="C44" t="s">
+        <v>338</v>
+      </c>
+      <c r="D44" t="s">
+        <v>223</v>
+      </c>
+      <c r="E44">
+        <v>0.42700513578083299</v>
+      </c>
+      <c r="F44">
+        <v>4.99246420497362E-2</v>
+      </c>
+      <c r="G44">
+        <v>9.9535292640039907E-2</v>
+      </c>
+      <c r="H44">
+        <v>6</v>
+      </c>
+      <c r="I44">
+        <v>164.388888888888</v>
+      </c>
+      <c r="J44">
+        <v>0.67558402411454399</v>
+      </c>
+      <c r="K44">
+        <v>0.25263752825923103</v>
+      </c>
+      <c r="L44">
+        <v>9.0429540316503392E-3</v>
+      </c>
+      <c r="M44">
+        <v>1.28108515448379E-2</v>
+      </c>
+      <c r="N44">
+        <v>0</v>
+      </c>
+      <c r="O44">
+        <v>2.26073850791258E-3</v>
+      </c>
+      <c r="P44">
+        <v>4.76639035418236E-2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A45">
         <v>660</v>
       </c>
-      <c r="B33" t="s">
-        <v>337</v>
-      </c>
-      <c r="C33" t="s">
-        <v>338</v>
-      </c>
-      <c r="D33" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A35">
-        <v>0</v>
-      </c>
-      <c r="B35" t="s">
-        <v>337</v>
-      </c>
-      <c r="C35" t="s">
-        <v>338</v>
-      </c>
-      <c r="D35" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A36">
-        <v>60</v>
-      </c>
-      <c r="B36" t="s">
-        <v>337</v>
-      </c>
-      <c r="C36" t="s">
-        <v>338</v>
-      </c>
-      <c r="D36" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A37">
-        <v>120</v>
-      </c>
-      <c r="B37" t="s">
-        <v>337</v>
-      </c>
-      <c r="C37" t="s">
-        <v>338</v>
-      </c>
-      <c r="D37" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A38">
-        <v>180</v>
-      </c>
-      <c r="B38" t="s">
-        <v>337</v>
-      </c>
-      <c r="C38" t="s">
-        <v>338</v>
-      </c>
-      <c r="D38" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A39">
-        <v>240</v>
-      </c>
-      <c r="B39" t="s">
-        <v>337</v>
-      </c>
-      <c r="C39" t="s">
-        <v>338</v>
-      </c>
-      <c r="D39" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A40">
-        <v>300</v>
-      </c>
-      <c r="B40" t="s">
-        <v>337</v>
-      </c>
-      <c r="C40" t="s">
-        <v>338</v>
-      </c>
-      <c r="D40" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A41">
-        <v>360</v>
-      </c>
-      <c r="B41" t="s">
-        <v>337</v>
-      </c>
-      <c r="C41" t="s">
-        <v>338</v>
-      </c>
-      <c r="D41" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A42">
-        <v>420</v>
-      </c>
-      <c r="B42" t="s">
-        <v>337</v>
-      </c>
-      <c r="C42" t="s">
-        <v>338</v>
-      </c>
-      <c r="D42" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A43">
-        <v>480</v>
-      </c>
-      <c r="B43" t="s">
-        <v>337</v>
-      </c>
-      <c r="C43" t="s">
-        <v>338</v>
-      </c>
-      <c r="D43" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A44">
-        <v>540</v>
-      </c>
-      <c r="B44" t="s">
-        <v>337</v>
-      </c>
-      <c r="C44" t="s">
-        <v>338</v>
-      </c>
-      <c r="D44" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A45">
-        <v>600</v>
-      </c>
       <c r="B45" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C45" t="s">
         <v>338</v>
       </c>
       <c r="D45" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+        <v>223</v>
+      </c>
+      <c r="E45">
+        <v>0.73556960692111095</v>
+      </c>
+      <c r="F45">
+        <v>0</v>
+      </c>
+      <c r="G45">
+        <v>2.1791767554479386E-2</v>
+      </c>
+      <c r="H45">
+        <v>8</v>
+      </c>
+      <c r="I45">
+        <v>141.768115942029</v>
+      </c>
+      <c r="J45">
+        <v>0.98238426874231799</v>
+      </c>
+      <c r="K45">
+        <v>1.7615731257681198E-2</v>
+      </c>
+      <c r="L45">
+        <v>0</v>
+      </c>
+      <c r="M45">
+        <v>0</v>
+      </c>
+      <c r="N45">
+        <v>0</v>
+      </c>
+      <c r="O45">
+        <v>0</v>
+      </c>
+      <c r="P45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A46">
-        <v>660</v>
+        <v>720</v>
       </c>
       <c r="B46" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C46" t="s">
         <v>338</v>
       </c>
       <c r="D46" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+        <v>223</v>
+      </c>
+      <c r="E46">
+        <v>0.50929059167584401</v>
+      </c>
+      <c r="F46">
+        <v>0</v>
+      </c>
+      <c r="G46">
+        <v>7.6849183477425481E-3</v>
+      </c>
+      <c r="H46">
+        <v>6.5</v>
+      </c>
+      <c r="I46">
+        <v>163.21568627450901</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>0</v>
       </c>
       <c r="B47" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C47" t="s">
         <v>338</v>
       </c>
       <c r="D47" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+        <v>237</v>
+      </c>
+      <c r="E47">
+        <v>0.31731714131464001</v>
+      </c>
+      <c r="F47">
+        <v>8.5040983606557305E-2</v>
+      </c>
+      <c r="G47">
+        <v>0.29935109289617468</v>
+      </c>
+      <c r="H47">
+        <v>4.5</v>
+      </c>
+      <c r="I47">
+        <v>150.305555555555</v>
+      </c>
+      <c r="J47">
+        <v>0.25665983606557302</v>
+      </c>
+      <c r="K47">
+        <v>0.45824795081967201</v>
+      </c>
+      <c r="L47">
+        <v>4.3801229508196697E-2</v>
+      </c>
+      <c r="M47">
+        <v>0.14497950819672101</v>
+      </c>
+      <c r="N47">
+        <v>1.12704918032786E-2</v>
+      </c>
+      <c r="O47">
+        <v>2.84323770491803E-2</v>
+      </c>
+      <c r="P47">
+        <v>5.6608606557376998E-2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>60</v>
       </c>
       <c r="B48" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C48" t="s">
         <v>338</v>
       </c>
       <c r="D48" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+        <v>237</v>
+      </c>
+      <c r="E48">
+        <v>0.29703657802815397</v>
+      </c>
+      <c r="F48">
+        <v>2.8032619775738999E-2</v>
+      </c>
+      <c r="G48">
+        <v>0.34633027522935733</v>
+      </c>
+      <c r="H48">
+        <v>13.5</v>
+      </c>
+      <c r="I48">
+        <v>168.58899868247599</v>
+      </c>
+      <c r="J48">
+        <v>0.22426095820591199</v>
+      </c>
+      <c r="K48">
+        <v>0.48037716615698201</v>
+      </c>
+      <c r="L48">
+        <v>5.8613659531090698E-2</v>
+      </c>
+      <c r="M48">
+        <v>0.18960244648318</v>
+      </c>
+      <c r="N48">
+        <v>1.91131498470948E-2</v>
+      </c>
+      <c r="O48">
+        <v>4.84199796126401E-3</v>
+      </c>
+      <c r="P48">
+        <v>2.3190621814474999E-2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>120</v>
       </c>
       <c r="B49" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C49" t="s">
         <v>338</v>
       </c>
       <c r="D49" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+        <v>237</v>
+      </c>
+      <c r="E49">
+        <v>0.31888492293589898</v>
+      </c>
+      <c r="F49">
+        <v>7.6530612244897905E-2</v>
+      </c>
+      <c r="G49">
+        <v>0.3721088435374143</v>
+      </c>
+      <c r="H49">
+        <v>19.5</v>
+      </c>
+      <c r="I49">
+        <v>177.28396854204399</v>
+      </c>
+      <c r="J49">
+        <v>0.15076530612244801</v>
+      </c>
+      <c r="K49">
+        <v>0.50408163265306105</v>
+      </c>
+      <c r="L49">
+        <v>7.6530612244897897E-3</v>
+      </c>
+      <c r="M49">
+        <v>0.23010204081632599</v>
+      </c>
+      <c r="N49">
+        <v>3.0867346938775499E-2</v>
+      </c>
+      <c r="O49">
+        <v>4.4132653061224401E-2</v>
+      </c>
+      <c r="P49">
+        <v>3.23979591836734E-2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>180</v>
       </c>
       <c r="B50" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C50" t="s">
         <v>338</v>
       </c>
       <c r="D50" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+        <v>237</v>
+      </c>
+      <c r="E50">
+        <v>0.55081228552069905</v>
+      </c>
+      <c r="F50">
+        <v>4.6620046620046603E-2</v>
+      </c>
+      <c r="G50">
+        <v>0.24492791159457802</v>
+      </c>
+      <c r="H50">
+        <v>19</v>
+      </c>
+      <c r="I50">
+        <v>178.680518035912</v>
+      </c>
+      <c r="J50">
+        <v>0.34032634032634002</v>
+      </c>
+      <c r="K50">
+        <v>0.49987049987049897</v>
+      </c>
+      <c r="L50">
+        <v>2.0461020461020399E-2</v>
+      </c>
+      <c r="M50">
+        <v>8.7283087283087202E-2</v>
+      </c>
+      <c r="N50">
+        <v>5.4390054390054303E-3</v>
+      </c>
+      <c r="O50">
+        <v>3.1080031080031002E-3</v>
+      </c>
+      <c r="P50">
+        <v>4.3512043512043498E-2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>240</v>
       </c>
       <c r="B51" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C51" t="s">
         <v>338</v>
       </c>
       <c r="D51" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+        <v>237</v>
+      </c>
+      <c r="E51">
+        <v>0.50703826768083804</v>
+      </c>
+      <c r="F51">
+        <v>2.1119592875318002E-2</v>
+      </c>
+      <c r="G51">
+        <v>0.14766751484308707</v>
+      </c>
+      <c r="H51">
+        <v>16.5</v>
+      </c>
+      <c r="I51">
+        <v>168.73543417366901</v>
+      </c>
+      <c r="J51">
+        <v>0.60839694656488497</v>
+      </c>
+      <c r="K51">
+        <v>0.29949109414758202</v>
+      </c>
+      <c r="L51">
+        <v>1.04325699745547E-2</v>
+      </c>
+      <c r="M51">
+        <v>5.9033078880407097E-2</v>
+      </c>
+      <c r="N51">
+        <v>1.5267175572518999E-3</v>
+      </c>
+      <c r="O51">
+        <v>0</v>
+      </c>
+      <c r="P51">
+        <v>2.1119592875318002E-2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>300</v>
       </c>
       <c r="B52" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C52" t="s">
         <v>338</v>
       </c>
       <c r="D52" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+        <v>237</v>
+      </c>
+      <c r="E52">
+        <v>0.61625846222013902</v>
+      </c>
+      <c r="F52">
+        <v>0.106893880712625</v>
+      </c>
+      <c r="G52">
+        <v>0.31198898356140764</v>
+      </c>
+      <c r="H52">
+        <v>12</v>
+      </c>
+      <c r="I52">
+        <v>164.15695203400099</v>
+      </c>
+      <c r="J52">
+        <v>0.22334107926671801</v>
+      </c>
+      <c r="K52">
+        <v>0.47017815646785399</v>
+      </c>
+      <c r="L52">
+        <v>3.2532920216886099E-2</v>
+      </c>
+      <c r="M52">
+        <v>0.13400464756003</v>
+      </c>
+      <c r="N52">
+        <v>3.3049315775884297E-2</v>
+      </c>
+      <c r="O52">
+        <v>3.3565711334882502E-2</v>
+      </c>
+      <c r="P52">
+        <v>7.3328169377743294E-2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>360</v>
       </c>
       <c r="B53" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C53" t="s">
         <v>338</v>
       </c>
       <c r="D53" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+        <v>237</v>
+      </c>
+      <c r="E53">
+        <v>0.65810231732073698</v>
+      </c>
+      <c r="F53">
+        <v>3.0028475278281098E-2</v>
+      </c>
+      <c r="G53">
+        <v>0.400379670377081</v>
+      </c>
+      <c r="H53">
+        <v>13</v>
+      </c>
+      <c r="I53">
+        <v>168.531746031746</v>
+      </c>
+      <c r="J53">
+        <v>0.19777375097074801</v>
+      </c>
+      <c r="K53">
+        <v>0.441366813357494</v>
+      </c>
+      <c r="L53">
+        <v>4.7631374579342398E-2</v>
+      </c>
+      <c r="M53">
+        <v>0.20683406678746999</v>
+      </c>
+      <c r="N53">
+        <v>7.6365519026663206E-2</v>
+      </c>
+      <c r="O53">
+        <v>2.17447579601346E-2</v>
+      </c>
+      <c r="P53">
+        <v>8.2837173181465103E-3</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>420</v>
       </c>
       <c r="B54" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C54" t="s">
         <v>338</v>
       </c>
       <c r="D54" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+        <v>237</v>
+      </c>
+      <c r="E54">
+        <v>0.455995785185764</v>
+      </c>
+      <c r="F54">
+        <v>2.4127310061601601E-2</v>
+      </c>
+      <c r="G54">
+        <v>0.26480150581793233</v>
+      </c>
+      <c r="H54">
+        <v>12.5</v>
+      </c>
+      <c r="I54">
+        <v>168.17728758169901</v>
+      </c>
+      <c r="J54">
+        <v>0.35164271047227902</v>
+      </c>
+      <c r="K54">
+        <v>0.45559548254620102</v>
+      </c>
+      <c r="L54">
+        <v>4.9024640657084097E-2</v>
+      </c>
+      <c r="M54">
+        <v>0.11960985626283301</v>
+      </c>
+      <c r="N54">
+        <v>0</v>
+      </c>
+      <c r="O54">
+        <v>1.5400410677618001E-3</v>
+      </c>
+      <c r="P54">
+        <v>2.2587268993839799E-2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>480</v>
       </c>
       <c r="B55" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C55" t="s">
         <v>338</v>
       </c>
       <c r="D55" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+        <v>237</v>
+      </c>
+      <c r="E55">
+        <v>0.39795908671019697</v>
+      </c>
+      <c r="F55">
+        <v>1.8970893970893899E-2</v>
+      </c>
+      <c r="G55">
+        <v>0.30258142758142753</v>
+      </c>
+      <c r="H55">
+        <v>16.5</v>
+      </c>
+      <c r="I55">
+        <v>159.708333333333</v>
+      </c>
+      <c r="J55">
+        <v>0.26481288981288897</v>
+      </c>
+      <c r="K55">
+        <v>0.52754677754677703</v>
+      </c>
+      <c r="L55">
+        <v>8.8877338877338799E-2</v>
+      </c>
+      <c r="M55">
+        <v>9.9792099792099798E-2</v>
+      </c>
+      <c r="N55">
+        <v>0</v>
+      </c>
+      <c r="O55">
+        <v>2.8586278586278501E-3</v>
+      </c>
+      <c r="P55">
+        <v>1.6112266112266099E-2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>540</v>
       </c>
       <c r="B56" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C56" t="s">
         <v>338</v>
       </c>
       <c r="D56" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+        <v>237</v>
+      </c>
+      <c r="E56">
+        <v>0.29419940858772697</v>
+      </c>
+      <c r="F56">
+        <v>0.10214083053907599</v>
+      </c>
+      <c r="G56">
+        <v>0.17393173415871299</v>
+      </c>
+      <c r="H56">
+        <v>14</v>
+      </c>
+      <c r="I56">
+        <v>166.91174603174599</v>
+      </c>
+      <c r="J56">
+        <v>0.42197575444931601</v>
+      </c>
+      <c r="K56">
+        <v>0.430487490327572</v>
+      </c>
+      <c r="L56">
+        <v>1.1864843951508899E-2</v>
+      </c>
+      <c r="M56">
+        <v>3.3531080732525101E-2</v>
+      </c>
+      <c r="N56">
+        <v>0</v>
+      </c>
+      <c r="O56">
+        <v>5.1586278050038596E-4</v>
+      </c>
+      <c r="P56">
+        <v>0.101624967758576</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>600</v>
       </c>
       <c r="B57" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C57" t="s">
         <v>338</v>
       </c>
       <c r="D57" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+        <v>237</v>
+      </c>
+      <c r="E57">
+        <v>0.18776899615559101</v>
+      </c>
+      <c r="F57">
+        <v>7.0093457943925198E-3</v>
+      </c>
+      <c r="G57">
+        <v>0.16536863966770476</v>
+      </c>
+      <c r="H57">
+        <v>20.5</v>
+      </c>
+      <c r="I57">
+        <v>173.35542929292899</v>
+      </c>
+      <c r="J57">
+        <v>0.56970404984423595</v>
+      </c>
+      <c r="K57">
+        <v>0.35046728971962599</v>
+      </c>
+      <c r="L57">
+        <v>0</v>
+      </c>
+      <c r="M57">
+        <v>7.2819314641744501E-2</v>
+      </c>
+      <c r="N57">
+        <v>0</v>
+      </c>
+      <c r="O57">
+        <v>0</v>
+      </c>
+      <c r="P57">
+        <v>7.0093457943925198E-3</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>0</v>
       </c>
       <c r="B58" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C58" t="s">
         <v>338</v>
       </c>
       <c r="D58" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
+        <v>238</v>
+      </c>
+      <c r="E58">
+        <v>0.168137887747214</v>
+      </c>
+      <c r="F58">
+        <v>1.3274336283185801E-2</v>
+      </c>
+      <c r="G58">
+        <v>0.26889749262536833</v>
+      </c>
+      <c r="H58">
+        <v>7.5</v>
+      </c>
+      <c r="I58">
+        <v>194</v>
+      </c>
+      <c r="J58">
+        <v>0.328263274336283</v>
+      </c>
+      <c r="K58">
+        <v>0.51438053097345104</v>
+      </c>
+      <c r="L58">
+        <v>5.1438053097345102E-2</v>
+      </c>
+      <c r="M58">
+        <v>9.2643805309734498E-2</v>
+      </c>
+      <c r="N58">
+        <v>0</v>
+      </c>
+      <c r="O58">
+        <v>4.1482300884955704E-3</v>
+      </c>
+      <c r="P58">
+        <v>9.1261061946902606E-3</v>
+      </c>
+    </row>
+    <row r="59" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>60</v>
       </c>
       <c r="B59" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C59" t="s">
         <v>338</v>
       </c>
       <c r="D59" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
+        <v>238</v>
+      </c>
+      <c r="E59">
+        <v>0.56846135687966404</v>
+      </c>
+      <c r="F59">
+        <v>7.6754385964912198E-3</v>
+      </c>
+      <c r="G59">
+        <v>0.17900219298245579</v>
+      </c>
+      <c r="H59">
+        <v>12</v>
+      </c>
+      <c r="I59">
+        <v>183.786231884057</v>
+      </c>
+      <c r="J59">
+        <v>0.48739035087719201</v>
+      </c>
+      <c r="K59">
+        <v>0.472861842105263</v>
+      </c>
+      <c r="L59">
+        <v>6.5789473684210497E-3</v>
+      </c>
+      <c r="M59">
+        <v>2.5493421052631499E-2</v>
+      </c>
+      <c r="N59">
+        <v>0</v>
+      </c>
+      <c r="O59">
+        <v>0</v>
+      </c>
+      <c r="P59">
+        <v>7.6754385964912198E-3</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>120</v>
       </c>
       <c r="B60" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C60" t="s">
         <v>338</v>
       </c>
       <c r="D60" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
+        <v>238</v>
+      </c>
+      <c r="E60">
+        <v>0.548642562466374</v>
+      </c>
+      <c r="F60">
+        <v>7.0992789794786404E-2</v>
+      </c>
+      <c r="G60">
+        <v>0.286282122388611</v>
+      </c>
+      <c r="H60">
+        <v>8</v>
+      </c>
+      <c r="I60">
+        <v>171.868055555555</v>
+      </c>
+      <c r="J60">
+        <v>0.32002218524680998</v>
+      </c>
+      <c r="K60">
+        <v>0.39961175818080902</v>
+      </c>
+      <c r="L60">
+        <v>6.5723793677204601E-2</v>
+      </c>
+      <c r="M60">
+        <v>0.143649473100388</v>
+      </c>
+      <c r="N60">
+        <v>0</v>
+      </c>
+      <c r="O60">
+        <v>4.04880754298391E-2</v>
+      </c>
+      <c r="P60">
+        <v>3.05047143649473E-2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>180</v>
       </c>
       <c r="B61" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C61" t="s">
         <v>338</v>
       </c>
       <c r="D61" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
+        <v>238</v>
+      </c>
+      <c r="E61">
+        <v>0.69017060098391803</v>
+      </c>
+      <c r="F61">
+        <v>7.6901950013732404E-3</v>
+      </c>
+      <c r="G61">
+        <v>0.18895907717659957</v>
+      </c>
+      <c r="H61">
+        <v>9.5</v>
+      </c>
+      <c r="I61">
+        <v>184.25063131313101</v>
+      </c>
+      <c r="J61">
+        <v>0.47761603954957399</v>
+      </c>
+      <c r="K61">
+        <v>0.46251029936830501</v>
+      </c>
+      <c r="L61">
+        <v>3.7352375720955698E-2</v>
+      </c>
+      <c r="M61">
+        <v>1.48310903597912E-2</v>
+      </c>
+      <c r="N61">
+        <v>0</v>
+      </c>
+      <c r="O61">
+        <v>0</v>
+      </c>
+      <c r="P61">
+        <v>7.6901950013732404E-3</v>
+      </c>
+    </row>
+    <row r="62" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>240</v>
       </c>
       <c r="B62" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C62" t="s">
         <v>338</v>
       </c>
       <c r="D62" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
+        <v>238</v>
+      </c>
+      <c r="E62">
+        <v>0.70074495207290499</v>
+      </c>
+      <c r="F62">
+        <v>0.121046892039258</v>
+      </c>
+      <c r="G62">
+        <v>0.14640130861504871</v>
+      </c>
+      <c r="H62">
+        <v>5</v>
+      </c>
+      <c r="I62">
+        <v>173.638888888888</v>
+      </c>
+      <c r="J62">
+        <v>0.44083969465648798</v>
+      </c>
+      <c r="K62">
+        <v>0.43729552889858198</v>
+      </c>
+      <c r="L62">
+        <v>5.4525627044710995E-4</v>
+      </c>
+      <c r="M62">
+        <v>2.7262813522355498E-4</v>
+      </c>
+      <c r="N62">
+        <v>0</v>
+      </c>
+      <c r="O62">
+        <v>2.7262813522355498E-4</v>
+      </c>
+      <c r="P62">
+        <v>0.12077426390403399</v>
+      </c>
+    </row>
+    <row r="63" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>300</v>
       </c>
       <c r="B63" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C63" t="s">
         <v>338</v>
       </c>
       <c r="D63" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
+        <v>238</v>
+      </c>
+      <c r="E63">
+        <v>0.63517578209749903</v>
+      </c>
+      <c r="F63">
+        <v>5.2401746724890799E-2</v>
+      </c>
+      <c r="G63">
+        <v>0.17530931586608409</v>
+      </c>
+      <c r="H63">
+        <v>13.5</v>
+      </c>
+      <c r="I63">
+        <v>182.00643939393899</v>
+      </c>
+      <c r="J63">
+        <v>0.455786026200873</v>
+      </c>
+      <c r="K63">
+        <v>0.47188864628820898</v>
+      </c>
+      <c r="L63">
+        <v>9.2794759825327502E-3</v>
+      </c>
+      <c r="M63">
+        <v>1.03711790393013E-2</v>
+      </c>
+      <c r="N63">
+        <v>2.7292576419213902E-4</v>
+      </c>
+      <c r="O63">
+        <v>1.39192139737991E-2</v>
+      </c>
+      <c r="P63">
+        <v>3.8482532751091703E-2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>360</v>
       </c>
       <c r="B64" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C64" t="s">
         <v>338</v>
       </c>
       <c r="D64" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
+        <v>238</v>
+      </c>
+      <c r="E64">
+        <v>0.57327463620416796</v>
+      </c>
+      <c r="F64">
+        <v>2.75996654586005E-2</v>
+      </c>
+      <c r="G64">
+        <v>0.17563423473654838</v>
+      </c>
+      <c r="H64">
+        <v>13</v>
+      </c>
+      <c r="I64">
+        <v>182.64652014652</v>
+      </c>
+      <c r="J64">
+        <v>0.510175634234736</v>
+      </c>
+      <c r="K64">
+        <v>0.414552550878171</v>
+      </c>
+      <c r="L64">
+        <v>3.0945079453582301E-2</v>
+      </c>
+      <c r="M64">
+        <v>1.67270699749093E-2</v>
+      </c>
+      <c r="N64">
+        <v>0</v>
+      </c>
+      <c r="O64">
+        <v>1.7005854474491201E-2</v>
+      </c>
+      <c r="P64">
+        <v>1.0593810984109201E-2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>420</v>
       </c>
       <c r="B65" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C65" t="s">
         <v>338</v>
       </c>
       <c r="D65" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
+        <v>238</v>
+      </c>
+      <c r="E65">
+        <v>0.628198098617194</v>
+      </c>
+      <c r="F65">
+        <v>8.8716384807319103E-3</v>
+      </c>
+      <c r="G65">
+        <v>0.12919323537565819</v>
+      </c>
+      <c r="H65">
+        <v>15.5</v>
+      </c>
+      <c r="I65">
+        <v>189.98085901027</v>
+      </c>
+      <c r="J65">
+        <v>0.62572775159412197</v>
+      </c>
+      <c r="K65">
+        <v>0.34433046853340699</v>
+      </c>
+      <c r="L65">
+        <v>0</v>
+      </c>
+      <c r="M65">
+        <v>2.0515663986692498E-2</v>
+      </c>
+      <c r="N65">
+        <v>5.5447740504574396E-4</v>
+      </c>
+      <c r="O65">
+        <v>5.5447740504574396E-4</v>
+      </c>
+      <c r="P65">
+        <v>8.3171610756861605E-3</v>
+      </c>
+    </row>
+    <row r="66" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>480</v>
       </c>
       <c r="B66" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C66" t="s">
         <v>338</v>
       </c>
       <c r="D66" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
+        <v>238</v>
+      </c>
+      <c r="E66">
+        <v>0.69186944480755797</v>
+      </c>
+      <c r="F66">
+        <v>6.0354374307862599E-2</v>
+      </c>
+      <c r="G66">
+        <v>0.19592100406053861</v>
+      </c>
+      <c r="H66">
+        <v>11.5</v>
+      </c>
+      <c r="I66">
+        <v>176.39434523809501</v>
+      </c>
+      <c r="J66">
+        <v>0.40808416389811702</v>
+      </c>
+      <c r="K66">
+        <v>0.47535991140642297</v>
+      </c>
+      <c r="L66">
+        <v>1.77187153931339E-2</v>
+      </c>
+      <c r="M66">
+        <v>3.8482834994462901E-2</v>
+      </c>
+      <c r="N66">
+        <v>0</v>
+      </c>
+      <c r="O66">
+        <v>0</v>
+      </c>
+      <c r="P66">
+        <v>6.0354374307862599E-2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A67">
+        <v>540</v>
+      </c>
+      <c r="B67" t="s">
+        <v>339</v>
+      </c>
+      <c r="C67" t="s">
+        <v>338</v>
+      </c>
+      <c r="D67" t="s">
+        <v>238</v>
+      </c>
+      <c r="E67">
+        <v>0.39664642829528302</v>
+      </c>
+      <c r="F67">
+        <v>7.4833702882483302E-3</v>
+      </c>
+      <c r="G67">
+        <v>0.1482815964523278</v>
+      </c>
+      <c r="H67">
+        <v>11.5</v>
+      </c>
+      <c r="I67">
+        <v>180.69612794612701</v>
+      </c>
+      <c r="J67">
+        <v>0.604490022172949</v>
+      </c>
+      <c r="K67">
+        <v>0.33564301552106401</v>
+      </c>
+      <c r="L67">
+        <v>3.7694013303769397E-2</v>
+      </c>
+      <c r="M67">
+        <v>1.46895787139689E-2</v>
+      </c>
+      <c r="N67">
+        <v>0</v>
+      </c>
+      <c r="O67">
+        <v>4.4345898004434503E-3</v>
+      </c>
+      <c r="P67">
+        <v>3.0487804878048699E-3</v>
+      </c>
+    </row>
+    <row r="68" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A68">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="B68" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C68" t="s">
         <v>338</v>
       </c>
       <c r="D68" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
+        <v>238</v>
+      </c>
+      <c r="E68">
+        <v>0.19008077652147001</v>
+      </c>
+      <c r="F68">
+        <v>2.1723388848660301E-2</v>
+      </c>
+      <c r="G68">
+        <v>6.9032102341298474E-2</v>
+      </c>
+      <c r="H68">
+        <v>7</v>
+      </c>
+      <c r="I68">
+        <v>174.87285714285701</v>
+      </c>
+      <c r="J68">
+        <v>0.775524981897176</v>
+      </c>
+      <c r="K68">
+        <v>0.19840695148443099</v>
+      </c>
+      <c r="L68">
+        <v>0</v>
+      </c>
+      <c r="M68">
+        <v>4.3446777697320697E-3</v>
+      </c>
+      <c r="N68">
+        <v>0</v>
+      </c>
+      <c r="O68">
+        <v>0</v>
+      </c>
+      <c r="P68">
+        <v>2.1723388848660301E-2</v>
+      </c>
+    </row>
+    <row r="69" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A69">
+        <v>0</v>
+      </c>
+      <c r="B69" t="s">
+        <v>339</v>
+      </c>
+      <c r="C69" t="s">
+        <v>340</v>
+      </c>
+      <c r="D69" t="s">
+        <v>240</v>
+      </c>
+      <c r="E69">
+        <v>7.7726147668412003E-4</v>
+      </c>
+      <c r="F69">
+        <v>6.7944673622907003E-3</v>
+      </c>
+      <c r="G69">
+        <v>8.4445522931327024E-2</v>
+      </c>
+      <c r="H69">
+        <v>7</v>
+      </c>
+      <c r="I69">
+        <v>189.34632034632</v>
+      </c>
+      <c r="J69">
+        <v>0.74108226158699297</v>
+      </c>
+      <c r="K69">
+        <v>0.25090997330744902</v>
+      </c>
+      <c r="L69">
+        <v>7.2797864595971801E-4</v>
+      </c>
+      <c r="M69">
+        <v>4.8531909730647902E-4</v>
+      </c>
+      <c r="N69">
+        <v>0</v>
+      </c>
+      <c r="O69">
+        <v>0</v>
+      </c>
+      <c r="P69">
+        <v>6.7944673622907003E-3</v>
+      </c>
+    </row>
+    <row r="70" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A70">
         <v>60</v>
       </c>
-      <c r="B69" t="s">
-        <v>337</v>
-      </c>
-      <c r="C69" t="s">
-        <v>338</v>
-      </c>
-      <c r="D69" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A70">
+      <c r="B70" t="s">
+        <v>339</v>
+      </c>
+      <c r="C70" t="s">
+        <v>340</v>
+      </c>
+      <c r="D70" t="s">
+        <v>240</v>
+      </c>
+      <c r="E70">
+        <v>0.25565519319152302</v>
+      </c>
+      <c r="F70">
+        <v>2.2922636103151799E-2</v>
+      </c>
+      <c r="G70">
+        <v>8.1423113658070492E-2</v>
+      </c>
+      <c r="H70">
+        <v>14.5</v>
+      </c>
+      <c r="I70">
+        <v>189.12843137254899</v>
+      </c>
+      <c r="J70">
+        <v>0.73280802292263603</v>
+      </c>
+      <c r="K70">
+        <v>0.24426934097421199</v>
+      </c>
+      <c r="L70">
+        <v>0</v>
+      </c>
+      <c r="M70">
+        <v>0</v>
+      </c>
+      <c r="N70">
+        <v>0</v>
+      </c>
+      <c r="O70">
+        <v>0</v>
+      </c>
+      <c r="P70">
+        <v>2.2922636103151799E-2</v>
+      </c>
+    </row>
+    <row r="71" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A71">
         <v>120</v>
       </c>
-      <c r="B70" t="s">
-        <v>337</v>
-      </c>
-      <c r="C70" t="s">
-        <v>338</v>
-      </c>
-      <c r="D70" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A71">
+      <c r="B71" t="s">
+        <v>339</v>
+      </c>
+      <c r="C71" t="s">
+        <v>340</v>
+      </c>
+      <c r="D71" t="s">
+        <v>240</v>
+      </c>
+      <c r="E71">
+        <v>0.38137068276304698</v>
+      </c>
+      <c r="F71">
+        <v>6.98290392487358E-3</v>
+      </c>
+      <c r="G71">
+        <v>5.8672445621638626E-2</v>
+      </c>
+      <c r="H71">
+        <v>11.5</v>
+      </c>
+      <c r="I71">
+        <v>175.02564102564099</v>
+      </c>
+      <c r="J71">
+        <v>0.81699975921020895</v>
+      </c>
+      <c r="K71">
+        <v>0.176017336864916</v>
+      </c>
+      <c r="L71">
+        <v>0</v>
+      </c>
+      <c r="M71">
+        <v>0</v>
+      </c>
+      <c r="N71">
+        <v>0</v>
+      </c>
+      <c r="O71">
+        <v>0</v>
+      </c>
+      <c r="P71">
+        <v>6.98290392487358E-3</v>
+      </c>
+    </row>
+    <row r="72" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A72">
         <v>180</v>
       </c>
-      <c r="B71" t="s">
-        <v>337</v>
-      </c>
-      <c r="C71" t="s">
-        <v>338</v>
-      </c>
-      <c r="D71" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A72">
+      <c r="B72" t="s">
+        <v>339</v>
+      </c>
+      <c r="C72" t="s">
+        <v>340</v>
+      </c>
+      <c r="D72" t="s">
         <v>240</v>
       </c>
-      <c r="B72" t="s">
-        <v>337</v>
-      </c>
-      <c r="C72" t="s">
-        <v>338</v>
-      </c>
-      <c r="D72" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E72">
+        <v>0.18325886630416799</v>
+      </c>
+      <c r="F72">
+        <v>0</v>
+      </c>
+      <c r="G72">
+        <v>5.3150553150552844E-2</v>
+      </c>
+      <c r="H72">
+        <v>12</v>
+      </c>
+      <c r="I72">
+        <v>173.56736596736499</v>
+      </c>
+      <c r="J72">
+        <v>0.84800384800384798</v>
+      </c>
+      <c r="K72">
+        <v>0.144540644540644</v>
+      </c>
+      <c r="L72">
+        <v>6.01250601250601E-3</v>
+      </c>
+      <c r="M72">
+        <v>1.44300144300144E-3</v>
+      </c>
+      <c r="N72">
+        <v>0</v>
+      </c>
+      <c r="O72">
+        <v>0</v>
+      </c>
+      <c r="P72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A73">
+        <v>240</v>
+      </c>
+      <c r="B73" t="s">
+        <v>339</v>
+      </c>
+      <c r="C73" t="s">
+        <v>340</v>
+      </c>
+      <c r="D73" t="s">
+        <v>240</v>
+      </c>
+      <c r="E73">
+        <v>0.51938085054891703</v>
+      </c>
+      <c r="F73">
+        <v>0</v>
+      </c>
+      <c r="G73">
+        <v>3.65307753796962E-2</v>
+      </c>
+      <c r="H73">
+        <v>11.5</v>
+      </c>
+      <c r="I73">
+        <v>199.128205128205</v>
+      </c>
+      <c r="J73">
+        <v>0.89544364508393204</v>
+      </c>
+      <c r="K73">
+        <v>9.95203836930455E-2</v>
+      </c>
+      <c r="L73">
+        <v>5.0359712230215797E-3</v>
+      </c>
+      <c r="M73">
+        <v>0</v>
+      </c>
+      <c r="N73">
+        <v>0</v>
+      </c>
+      <c r="O73">
+        <v>0</v>
+      </c>
+      <c r="P73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A74">
         <v>300</v>
       </c>
-      <c r="B73" t="s">
-        <v>337</v>
-      </c>
-      <c r="C73" t="s">
-        <v>338</v>
-      </c>
-      <c r="D73" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A74">
+      <c r="B74" t="s">
+        <v>339</v>
+      </c>
+      <c r="C74" t="s">
+        <v>340</v>
+      </c>
+      <c r="D74" t="s">
+        <v>240</v>
+      </c>
+      <c r="E74">
+        <v>0.152042432066269</v>
+      </c>
+      <c r="F74">
+        <v>0</v>
+      </c>
+      <c r="G74">
+        <v>1.9070321811680546E-3</v>
+      </c>
+      <c r="H74">
+        <v>6.5</v>
+      </c>
+      <c r="I74">
+        <v>182.655555555555</v>
+      </c>
+      <c r="J74">
+        <v>0.99427890345649494</v>
+      </c>
+      <c r="K74">
+        <v>5.7210965435041698E-3</v>
+      </c>
+      <c r="L74">
+        <v>0</v>
+      </c>
+      <c r="M74">
+        <v>0</v>
+      </c>
+      <c r="N74">
+        <v>0</v>
+      </c>
+      <c r="O74">
+        <v>0</v>
+      </c>
+      <c r="P74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A75">
         <v>360</v>
       </c>
-      <c r="B74" t="s">
-        <v>337</v>
-      </c>
-      <c r="C74" t="s">
-        <v>338</v>
-      </c>
-      <c r="D74" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A75">
+      <c r="B75" t="s">
+        <v>339</v>
+      </c>
+      <c r="C75" t="s">
+        <v>340</v>
+      </c>
+      <c r="D75" t="s">
+        <v>240</v>
+      </c>
+      <c r="E75">
+        <v>0.60259193515821796</v>
+      </c>
+      <c r="F75">
+        <v>0</v>
+      </c>
+      <c r="G75">
+        <v>2.5281803542673103E-2</v>
+      </c>
+      <c r="H75">
+        <v>8.5</v>
+      </c>
+      <c r="I75">
+        <v>208.39047619047599</v>
+      </c>
+      <c r="J75">
+        <v>0.92415458937198003</v>
+      </c>
+      <c r="K75">
+        <v>7.5845410628019305E-2</v>
+      </c>
+      <c r="L75">
+        <v>0</v>
+      </c>
+      <c r="M75">
+        <v>0</v>
+      </c>
+      <c r="N75">
+        <v>0</v>
+      </c>
+      <c r="O75">
+        <v>0</v>
+      </c>
+      <c r="P75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A76">
         <v>420</v>
       </c>
-      <c r="B75" t="s">
-        <v>337</v>
-      </c>
-      <c r="C75" t="s">
-        <v>338</v>
-      </c>
-      <c r="D75" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A76">
+      <c r="B76" t="s">
+        <v>339</v>
+      </c>
+      <c r="C76" t="s">
+        <v>340</v>
+      </c>
+      <c r="D76" t="s">
+        <v>240</v>
+      </c>
+      <c r="E76">
+        <v>0.525178168861549</v>
+      </c>
+      <c r="F76">
+        <v>0</v>
+      </c>
+      <c r="G76">
+        <v>1.9798766634209666E-2</v>
+      </c>
+      <c r="H76">
+        <v>1.5</v>
+      </c>
+      <c r="I76">
+        <v>168.666666666666</v>
+      </c>
+      <c r="J76">
+        <v>0.94060370009737004</v>
+      </c>
+      <c r="K76">
+        <v>5.9396299902628999E-2</v>
+      </c>
+      <c r="L76">
+        <v>0</v>
+      </c>
+      <c r="M76">
+        <v>0</v>
+      </c>
+      <c r="N76">
+        <v>0</v>
+      </c>
+      <c r="O76">
+        <v>0</v>
+      </c>
+      <c r="P76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A77">
+        <v>0</v>
+      </c>
+      <c r="B77" t="s">
+        <v>339</v>
+      </c>
+      <c r="C77" t="s">
+        <v>338</v>
+      </c>
+      <c r="D77" t="s">
+        <v>248</v>
+      </c>
+      <c r="E77">
+        <v>2.6845976548976299E-2</v>
+      </c>
+      <c r="F77">
+        <v>5.5504727050930097E-2</v>
+      </c>
+      <c r="G77">
+        <v>0.16651418115279029</v>
+      </c>
+      <c r="H77">
+        <v>18.5</v>
+      </c>
+      <c r="I77">
+        <v>199.37797619047601</v>
+      </c>
+      <c r="J77">
+        <v>0.51113144251296105</v>
+      </c>
+      <c r="K77">
+        <v>0.37907898749618701</v>
+      </c>
+      <c r="L77">
+        <v>3.3546813052759898E-3</v>
+      </c>
+      <c r="M77">
+        <v>4.6965538273863898E-2</v>
+      </c>
+      <c r="N77">
+        <v>3.96462336078072E-3</v>
+      </c>
+      <c r="O77">
+        <v>7.9292467215614504E-3</v>
+      </c>
+      <c r="P77">
+        <v>4.7575480329368702E-2</v>
+      </c>
+    </row>
+    <row r="78" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A78">
+        <v>60</v>
+      </c>
+      <c r="B78" t="s">
+        <v>339</v>
+      </c>
+      <c r="C78" t="s">
+        <v>338</v>
+      </c>
+      <c r="D78" t="s">
+        <v>248</v>
+      </c>
+      <c r="E78">
+        <v>0.15590583921322199</v>
+      </c>
+      <c r="F78">
+        <v>0.206938900828983</v>
+      </c>
+      <c r="G78">
+        <v>0.30314195067035049</v>
+      </c>
+      <c r="H78">
+        <v>31</v>
+      </c>
+      <c r="I78">
+        <v>190.980263157894</v>
+      </c>
+      <c r="J78">
+        <v>0.16334049739023601</v>
+      </c>
+      <c r="K78">
+        <v>0.41940435984034302</v>
+      </c>
+      <c r="L78">
+        <v>6.5704636168252895E-2</v>
+      </c>
+      <c r="M78">
+        <v>0.14461160577218299</v>
+      </c>
+      <c r="N78">
+        <v>0</v>
+      </c>
+      <c r="O78">
+        <v>6.9389008289837198E-2</v>
+      </c>
+      <c r="P78">
+        <v>0.13754989253914601</v>
+      </c>
+    </row>
+    <row r="79" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A79">
+        <v>120</v>
+      </c>
+      <c r="B79" t="s">
+        <v>339</v>
+      </c>
+      <c r="C79" t="s">
+        <v>338</v>
+      </c>
+      <c r="D79" t="s">
+        <v>248</v>
+      </c>
+      <c r="E79">
+        <v>0.38064711605557999</v>
+      </c>
+      <c r="F79">
+        <v>3.5312024353120197E-2</v>
+      </c>
+      <c r="G79">
+        <v>0.10126839167935027</v>
+      </c>
+      <c r="H79">
+        <v>15</v>
+      </c>
+      <c r="I79">
+        <v>165.890540831717</v>
+      </c>
+      <c r="J79">
+        <v>0.68371385083713798</v>
+      </c>
+      <c r="K79">
+        <v>0.25936073059360698</v>
+      </c>
+      <c r="L79">
+        <v>2.7397260273972599E-3</v>
+      </c>
+      <c r="M79">
+        <v>1.8873668188736599E-2</v>
+      </c>
+      <c r="N79">
+        <v>0</v>
+      </c>
+      <c r="O79">
+        <v>1.21765601217656E-3</v>
+      </c>
+      <c r="P79">
+        <v>3.40943683409436E-2</v>
+      </c>
+    </row>
+    <row r="80" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A80">
+        <v>180</v>
+      </c>
+      <c r="B80" t="s">
+        <v>339</v>
+      </c>
+      <c r="C80" t="s">
+        <v>338</v>
+      </c>
+      <c r="D80" t="s">
+        <v>248</v>
+      </c>
+      <c r="E80">
+        <v>5.8379269512182398E-3</v>
+      </c>
+      <c r="F80">
+        <v>6.1462814996926804E-3</v>
+      </c>
+      <c r="G80">
+        <v>9.7725875845113511E-2</v>
+      </c>
+      <c r="H80">
+        <v>12.5</v>
+      </c>
+      <c r="I80">
+        <v>166.091269841269</v>
+      </c>
+      <c r="J80">
+        <v>0.73110018438844504</v>
+      </c>
+      <c r="K80">
+        <v>0.23478795328825999</v>
+      </c>
+      <c r="L80">
+        <v>1.2292562999385299E-3</v>
+      </c>
+      <c r="M80">
+        <v>2.6736324523663101E-2</v>
+      </c>
+      <c r="N80">
+        <v>0</v>
+      </c>
+      <c r="O80">
+        <v>2.4585125998770698E-3</v>
+      </c>
+      <c r="P80">
+        <v>3.6877688998156102E-3</v>
+      </c>
+    </row>
+    <row r="81" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A81">
+        <v>240</v>
+      </c>
+      <c r="B81" t="s">
+        <v>339</v>
+      </c>
+      <c r="C81" t="s">
+        <v>338</v>
+      </c>
+      <c r="D81" t="s">
+        <v>248</v>
+      </c>
+      <c r="E81">
+        <v>5.5942607186828001E-3</v>
+      </c>
+      <c r="F81">
+        <v>4.4090630740967501E-2</v>
+      </c>
+      <c r="G81">
+        <v>0.13329250867523948</v>
+      </c>
+      <c r="H81">
+        <v>12</v>
+      </c>
+      <c r="I81">
+        <v>190.29523809523801</v>
+      </c>
+      <c r="J81">
+        <v>0.60532761788120004</v>
+      </c>
+      <c r="K81">
+        <v>0.30312308634415103</v>
+      </c>
+      <c r="L81">
+        <v>2.14329454990814E-2</v>
+      </c>
+      <c r="M81">
+        <v>2.6025719534598899E-2</v>
+      </c>
+      <c r="N81">
+        <v>0</v>
+      </c>
+      <c r="O81">
+        <v>1.8371096142069799E-3</v>
+      </c>
+      <c r="P81">
+        <v>4.22535211267605E-2</v>
+      </c>
+    </row>
+    <row r="82" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A82">
+        <v>300</v>
+      </c>
+      <c r="B82" t="s">
+        <v>339</v>
+      </c>
+      <c r="C82" t="s">
+        <v>338</v>
+      </c>
+      <c r="D82" t="s">
+        <v>248</v>
+      </c>
+      <c r="E82">
+        <v>3.91016939234596E-2</v>
+      </c>
+      <c r="F82">
+        <v>9.62434026699782E-3</v>
+      </c>
+      <c r="G82">
+        <v>7.3786608713649934E-2</v>
+      </c>
+      <c r="H82">
+        <v>8.5</v>
+      </c>
+      <c r="I82">
+        <v>188.77248677248599</v>
+      </c>
+      <c r="J82">
+        <v>0.77460416019869605</v>
+      </c>
+      <c r="K82">
+        <v>0.210183172927662</v>
+      </c>
+      <c r="L82">
+        <v>1.86277553554796E-3</v>
+      </c>
+      <c r="M82">
+        <v>3.72555107109593E-3</v>
+      </c>
+      <c r="N82">
+        <v>0</v>
+      </c>
+      <c r="O82">
+        <v>0</v>
+      </c>
+      <c r="P82">
+        <v>9.62434026699782E-3</v>
+      </c>
+    </row>
+    <row r="83" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A83">
+        <v>360</v>
+      </c>
+      <c r="B83" t="s">
+        <v>339</v>
+      </c>
+      <c r="C83" t="s">
+        <v>338</v>
+      </c>
+      <c r="D83" t="s">
+        <v>248</v>
+      </c>
+      <c r="E83">
+        <v>7.4597583401735E-3</v>
+      </c>
+      <c r="F83">
+        <v>0</v>
+      </c>
+      <c r="G83">
+        <v>3.3301916431039899E-2</v>
+      </c>
+      <c r="H83">
+        <v>7</v>
+      </c>
+      <c r="I83">
+        <v>165.738888888888</v>
+      </c>
+      <c r="J83">
+        <v>0.90009425070687998</v>
+      </c>
+      <c r="K83">
+        <v>9.9905749293119697E-2</v>
+      </c>
+      <c r="L83">
+        <v>0</v>
+      </c>
+      <c r="M83">
+        <v>0</v>
+      </c>
+      <c r="N83">
+        <v>0</v>
+      </c>
+      <c r="O83">
+        <v>0</v>
+      </c>
+      <c r="P83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A84">
+        <v>0</v>
+      </c>
+      <c r="B84" t="s">
+        <v>339</v>
+      </c>
+      <c r="C84" t="s">
+        <v>338</v>
+      </c>
+      <c r="D84" t="s">
+        <v>250</v>
+      </c>
+      <c r="E84">
+        <v>1.298815E-2</v>
+      </c>
+      <c r="F84">
+        <v>0.24102393617021201</v>
+      </c>
+      <c r="G84">
+        <v>0.21797429078014149</v>
+      </c>
+      <c r="H84">
+        <v>9</v>
+      </c>
+      <c r="I84">
+        <v>173.70238095238</v>
+      </c>
+      <c r="J84">
+        <v>0.22340425531914801</v>
+      </c>
+      <c r="K84">
+        <v>0.44481382978723399</v>
+      </c>
+      <c r="L84">
+        <v>3.0252659574467999E-2</v>
+      </c>
+      <c r="M84">
+        <v>5.9175531914893602E-2</v>
+      </c>
+      <c r="N84">
+        <v>1.3297872340425499E-3</v>
+      </c>
+      <c r="O84">
+        <v>2.6263297872340399E-2</v>
+      </c>
+      <c r="P84">
+        <v>0.21476063829787201</v>
+      </c>
+    </row>
+    <row r="85" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A85">
+        <v>60</v>
+      </c>
+      <c r="B85" t="s">
+        <v>339</v>
+      </c>
+      <c r="C85" t="s">
+        <v>338</v>
+      </c>
+      <c r="D85" t="s">
+        <v>250</v>
+      </c>
+      <c r="E85">
+        <v>8.6380630147276899E-2</v>
+      </c>
+      <c r="F85">
+        <v>0.34243837441705499</v>
+      </c>
+      <c r="G85">
+        <v>0.2043082389518098</v>
+      </c>
+      <c r="H85">
+        <v>17</v>
+      </c>
+      <c r="I85">
+        <v>193.73853955375199</v>
+      </c>
+      <c r="J85">
+        <v>0.13157894736842099</v>
+      </c>
+      <c r="K85">
+        <v>0.45936042638241098</v>
+      </c>
+      <c r="L85">
+        <v>3.5309793471019299E-2</v>
+      </c>
+      <c r="M85">
+        <v>3.1312458361092602E-2</v>
+      </c>
+      <c r="N85">
+        <v>0</v>
+      </c>
+      <c r="O85">
+        <v>2.0319786808794101E-2</v>
+      </c>
+      <c r="P85">
+        <v>0.32211858760826101</v>
+      </c>
+    </row>
+    <row r="86" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A86">
+        <v>120</v>
+      </c>
+      <c r="B86" t="s">
+        <v>339</v>
+      </c>
+      <c r="C86" t="s">
+        <v>338</v>
+      </c>
+      <c r="D86" t="s">
+        <v>250</v>
+      </c>
+      <c r="E86">
+        <v>0.50891327902564498</v>
+      </c>
+      <c r="F86">
+        <v>0.119879113498992</v>
+      </c>
+      <c r="G86">
+        <v>0.23102753525856268</v>
+      </c>
+      <c r="H86">
+        <v>17</v>
+      </c>
+      <c r="I86">
+        <v>206.77167060677601</v>
+      </c>
+      <c r="J86">
+        <v>0.33143049026192001</v>
+      </c>
+      <c r="K86">
+        <v>0.41269308260577497</v>
+      </c>
+      <c r="L86">
+        <v>3.3579583613163101E-3</v>
+      </c>
+      <c r="M86">
+        <v>0.13129617192746801</v>
+      </c>
+      <c r="N86">
+        <v>1.3431833445265199E-3</v>
+      </c>
+      <c r="O86">
+        <v>7.05171255876427E-3</v>
+      </c>
+      <c r="P86">
+        <v>0.112827400940228</v>
+      </c>
+    </row>
+    <row r="87" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A87">
+        <v>180</v>
+      </c>
+      <c r="B87" t="s">
+        <v>339</v>
+      </c>
+      <c r="C87" t="s">
+        <v>338</v>
+      </c>
+      <c r="D87" t="s">
+        <v>250</v>
+      </c>
+      <c r="E87">
+        <v>0.64543073730122602</v>
+      </c>
+      <c r="F87">
+        <v>0.253925826929502</v>
+      </c>
+      <c r="G87">
+        <v>0.26439469874150734</v>
+      </c>
+      <c r="H87">
+        <v>21</v>
+      </c>
+      <c r="I87">
+        <v>189.34114353079801</v>
+      </c>
+      <c r="J87">
+        <v>0.132976946207818</v>
+      </c>
+      <c r="K87">
+        <v>0.49114600735048403</v>
+      </c>
+      <c r="L87">
+        <v>2.1383227530905401E-2</v>
+      </c>
+      <c r="M87">
+        <v>9.9231540260608E-2</v>
+      </c>
+      <c r="N87">
+        <v>1.3364517206815899E-3</v>
+      </c>
+      <c r="O87">
+        <v>5.6799198128967499E-2</v>
+      </c>
+      <c r="P87">
+        <v>0.197126628800534</v>
+      </c>
+    </row>
+    <row r="88" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A88">
+        <v>240</v>
+      </c>
+      <c r="B88" t="s">
+        <v>339</v>
+      </c>
+      <c r="C88" t="s">
+        <v>338</v>
+      </c>
+      <c r="D88" t="s">
+        <v>250</v>
+      </c>
+      <c r="E88">
+        <v>0.58476796003334197</v>
+      </c>
+      <c r="F88">
+        <v>0.16066576086956499</v>
+      </c>
+      <c r="G88">
+        <v>0.24581068840579701</v>
+      </c>
+      <c r="H88">
+        <v>24</v>
+      </c>
+      <c r="I88">
+        <v>211.33152578415701</v>
+      </c>
+      <c r="J88">
+        <v>0.2265625</v>
+      </c>
+      <c r="K88">
+        <v>0.50645380434782605</v>
+      </c>
+      <c r="L88">
+        <v>6.7934782608695607E-2</v>
+      </c>
+      <c r="M88">
+        <v>3.8383152173912999E-2</v>
+      </c>
+      <c r="N88">
+        <v>0</v>
+      </c>
+      <c r="O88">
+        <v>1.83423913043478E-2</v>
+      </c>
+      <c r="P88">
+        <v>0.14232336956521699</v>
+      </c>
+    </row>
+    <row r="89" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A89">
+        <v>300</v>
+      </c>
+      <c r="B89" t="s">
+        <v>339</v>
+      </c>
+      <c r="C89" t="s">
+        <v>338</v>
+      </c>
+      <c r="D89" t="s">
+        <v>250</v>
+      </c>
+      <c r="E89">
+        <v>0.49290088380730901</v>
+      </c>
+      <c r="F89">
+        <v>0.24824824824824801</v>
+      </c>
+      <c r="G89">
+        <v>0.26103881659437167</v>
+      </c>
+      <c r="H89">
+        <v>21</v>
+      </c>
+      <c r="I89">
+        <v>207.09851953601901</v>
+      </c>
+      <c r="J89">
+        <v>0.190523857190523</v>
+      </c>
+      <c r="K89">
+        <v>0.40840840840840797</v>
+      </c>
+      <c r="L89">
+        <v>6.3396730063396703E-2</v>
+      </c>
+      <c r="M89">
+        <v>8.8421755088421705E-2</v>
+      </c>
+      <c r="N89">
+        <v>1.0010010010009999E-3</v>
+      </c>
+      <c r="O89">
+        <v>6.8068068068068005E-2</v>
+      </c>
+      <c r="P89">
+        <v>0.18018018018018001</v>
+      </c>
+    </row>
+    <row r="90" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A90">
+        <v>360</v>
+      </c>
+      <c r="B90" t="s">
+        <v>339</v>
+      </c>
+      <c r="C90" t="s">
+        <v>338</v>
+      </c>
+      <c r="D90" t="s">
+        <v>250</v>
+      </c>
+      <c r="E90">
+        <v>0.72263426956574595</v>
+      </c>
+      <c r="F90">
+        <v>0.114907872696817</v>
+      </c>
+      <c r="G90">
+        <v>0.26130653266331599</v>
+      </c>
+      <c r="H90">
+        <v>25.5</v>
+      </c>
+      <c r="I90">
+        <v>209.70634920634899</v>
+      </c>
+      <c r="J90">
+        <v>0.267001675041876</v>
+      </c>
+      <c r="K90">
+        <v>0.47303182579564401</v>
+      </c>
+      <c r="L90">
+        <v>2.1105527638190898E-2</v>
+      </c>
+      <c r="M90">
+        <v>0.121608040201005</v>
+      </c>
+      <c r="N90">
+        <v>2.3450586264656599E-3</v>
+      </c>
+      <c r="O90">
+        <v>1.84254606365159E-2</v>
+      </c>
+      <c r="P90">
+        <v>9.6482412060301503E-2</v>
+      </c>
+    </row>
+    <row r="91" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A91">
+        <v>420</v>
+      </c>
+      <c r="B91" t="s">
+        <v>339</v>
+      </c>
+      <c r="C91" t="s">
+        <v>338</v>
+      </c>
+      <c r="D91" t="s">
+        <v>250</v>
+      </c>
+      <c r="E91">
+        <v>0.66162406265535001</v>
+      </c>
+      <c r="F91">
+        <v>7.0949185043144694E-2</v>
+      </c>
+      <c r="G91">
+        <v>0.30712687759667562</v>
+      </c>
+      <c r="H91">
+        <v>14.5</v>
+      </c>
+      <c r="I91">
+        <v>194.69576719576699</v>
+      </c>
+      <c r="J91">
+        <v>0.24640460210930001</v>
+      </c>
+      <c r="K91">
+        <v>0.49185043144774598</v>
+      </c>
+      <c r="L91">
+        <v>2.8763183125599199E-2</v>
+      </c>
+      <c r="M91">
+        <v>0.16203259827420899</v>
+      </c>
+      <c r="N91">
+        <v>0</v>
+      </c>
+      <c r="O91">
+        <v>4.79386385426653E-2</v>
+      </c>
+      <c r="P91">
+        <v>2.30105465004793E-2</v>
+      </c>
+    </row>
+    <row r="92" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A92">
+        <v>0</v>
+      </c>
+      <c r="B92" t="s">
+        <v>339</v>
+      </c>
+      <c r="C92" t="s">
+        <v>338</v>
+      </c>
+      <c r="D92" t="s">
+        <v>267</v>
+      </c>
+      <c r="E92">
+        <v>0.35298730526017003</v>
+      </c>
+      <c r="F92">
+        <v>1.6170212765957401E-2</v>
+      </c>
+      <c r="G92">
+        <v>0.11971631205673729</v>
+      </c>
+      <c r="H92">
+        <v>2</v>
+      </c>
+      <c r="I92">
+        <v>138.166666666666</v>
+      </c>
+      <c r="J92">
+        <v>0.62496453900709203</v>
+      </c>
+      <c r="K92">
+        <v>0.35858156028368698</v>
+      </c>
+      <c r="L92">
+        <v>0</v>
+      </c>
+      <c r="M92">
+        <v>2.8368794326241102E-4</v>
+      </c>
+      <c r="N92">
+        <v>0</v>
+      </c>
+      <c r="O92">
+        <v>0</v>
+      </c>
+      <c r="P92">
+        <v>1.6170212765957401E-2</v>
+      </c>
+    </row>
+    <row r="93" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A93">
+        <v>60</v>
+      </c>
+      <c r="B93" t="s">
+        <v>339</v>
+      </c>
+      <c r="C93" t="s">
+        <v>338</v>
+      </c>
+      <c r="D93" t="s">
+        <v>267</v>
+      </c>
+      <c r="E93">
+        <v>0.60128346662981902</v>
+      </c>
+      <c r="F93">
+        <v>1.92535545023696E-2</v>
+      </c>
+      <c r="G93">
+        <v>0.15560821484992085</v>
+      </c>
+      <c r="H93">
+        <v>15</v>
+      </c>
+      <c r="I93">
+        <v>170.64831573655101</v>
+      </c>
+      <c r="J93">
+        <v>0.59212085308056805</v>
+      </c>
+      <c r="K93">
+        <v>0.31783175355450199</v>
+      </c>
+      <c r="L93">
+        <v>2.8436018957345901E-2</v>
+      </c>
+      <c r="M93">
+        <v>4.2357819905213201E-2</v>
+      </c>
+      <c r="N93">
+        <v>0</v>
+      </c>
+      <c r="O93">
+        <v>7.4052132701421802E-3</v>
+      </c>
+      <c r="P93">
+        <v>1.1848341232227401E-2</v>
+      </c>
+    </row>
+    <row r="94" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A94">
+        <v>120</v>
+      </c>
+      <c r="B94" t="s">
+        <v>339</v>
+      </c>
+      <c r="C94" t="s">
+        <v>338</v>
+      </c>
+      <c r="D94" t="s">
+        <v>267</v>
+      </c>
+      <c r="E94">
+        <v>0.26039519435201502</v>
+      </c>
+      <c r="F94">
+        <v>1.48003351019268E-2</v>
+      </c>
+      <c r="G94">
+        <v>0.21269663967234465</v>
+      </c>
+      <c r="H94">
+        <v>16.5</v>
+      </c>
+      <c r="I94">
+        <v>170.40178571428501</v>
+      </c>
+      <c r="J94">
+        <v>0.43283998882993502</v>
+      </c>
+      <c r="K94">
+        <v>0.46746718793633002</v>
+      </c>
+      <c r="L94">
+        <v>1.1170064227869301E-3</v>
+      </c>
+      <c r="M94">
+        <v>8.3216978497626298E-2</v>
+      </c>
+      <c r="N94">
+        <v>5.5850321139346503E-4</v>
+      </c>
+      <c r="O94">
+        <v>2.7925160569673197E-4</v>
+      </c>
+      <c r="P94">
+        <v>1.4521083496230099E-2</v>
+      </c>
+    </row>
+    <row r="95" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A95">
+        <v>180</v>
+      </c>
+      <c r="B95" t="s">
+        <v>339</v>
+      </c>
+      <c r="C95" t="s">
+        <v>338</v>
+      </c>
+      <c r="D95" t="s">
+        <v>267</v>
+      </c>
+      <c r="E95">
+        <v>0.39483742216684897</v>
+      </c>
+      <c r="F95">
+        <v>1.6292134831460602E-2</v>
+      </c>
+      <c r="G95">
+        <v>0.15449438202247159</v>
+      </c>
+      <c r="H95">
+        <v>19.5</v>
+      </c>
+      <c r="I95">
+        <v>177.958759590792</v>
+      </c>
+      <c r="J95">
+        <v>0.57668539325842605</v>
+      </c>
+      <c r="K95">
+        <v>0.35056179775280899</v>
+      </c>
+      <c r="L95">
+        <v>4.7752808988764002E-3</v>
+      </c>
+      <c r="M95">
+        <v>5.1685393258426901E-2</v>
+      </c>
+      <c r="N95">
+        <v>0</v>
+      </c>
+      <c r="O95">
+        <v>0</v>
+      </c>
+      <c r="P95">
+        <v>1.6292134831460602E-2</v>
+      </c>
+    </row>
+    <row r="96" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A96">
+        <v>240</v>
+      </c>
+      <c r="B96" t="s">
+        <v>339</v>
+      </c>
+      <c r="C96" t="s">
+        <v>338</v>
+      </c>
+      <c r="D96" t="s">
+        <v>267</v>
+      </c>
+      <c r="E96">
+        <v>0.35745647982400902</v>
+      </c>
+      <c r="F96">
+        <v>2.1883098186006301E-2</v>
+      </c>
+      <c r="G96">
+        <v>0.17295325847010201</v>
+      </c>
+      <c r="H96">
+        <v>18</v>
+      </c>
+      <c r="I96">
+        <v>177.40159221583301</v>
+      </c>
+      <c r="J96">
+        <v>0.53095306651310104</v>
+      </c>
+      <c r="K96">
+        <v>0.381514540742873</v>
+      </c>
+      <c r="L96">
+        <v>2.7353872732507899E-2</v>
+      </c>
+      <c r="M96">
+        <v>3.4552260293694202E-2</v>
+      </c>
+      <c r="N96">
+        <v>3.7431615318168701E-3</v>
+      </c>
+      <c r="O96">
+        <v>2.3034840195796098E-3</v>
+      </c>
+      <c r="P96">
+        <v>1.9579614166426701E-2</v>
+      </c>
+    </row>
+    <row r="97" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A97">
+        <v>300</v>
+      </c>
+      <c r="B97" t="s">
+        <v>339</v>
+      </c>
+      <c r="C97" t="s">
+        <v>338</v>
+      </c>
+      <c r="D97" t="s">
+        <v>267</v>
+      </c>
+      <c r="E97">
+        <v>0.21325600349191501</v>
+      </c>
+      <c r="F97">
+        <v>3.7703513281919399E-2</v>
+      </c>
+      <c r="G97">
+        <v>0.18080548414738598</v>
+      </c>
+      <c r="H97">
+        <v>13.5</v>
+      </c>
+      <c r="I97">
+        <v>182.85138888888801</v>
+      </c>
+      <c r="J97">
+        <v>0.48728934590117101</v>
+      </c>
+      <c r="K97">
+        <v>0.41416738074835702</v>
+      </c>
+      <c r="L97">
+        <v>4.45586975149957E-2</v>
+      </c>
+      <c r="M97">
+        <v>1.6281062553556099E-2</v>
+      </c>
+      <c r="N97">
+        <v>0</v>
+      </c>
+      <c r="O97">
+        <v>6.5695515566980799E-3</v>
+      </c>
+      <c r="P97">
+        <v>3.1133961725221301E-2</v>
+      </c>
+    </row>
+    <row r="98" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A98">
+        <v>360</v>
+      </c>
+      <c r="B98" t="s">
+        <v>339</v>
+      </c>
+      <c r="C98" t="s">
+        <v>338</v>
+      </c>
+      <c r="D98" t="s">
+        <v>267</v>
+      </c>
+      <c r="E98">
+        <v>5.8791180971923002E-3</v>
+      </c>
+      <c r="F98">
+        <v>5.7430007178750899E-3</v>
+      </c>
+      <c r="G98">
+        <v>0.14046422589136112</v>
+      </c>
+      <c r="H98">
+        <v>19</v>
+      </c>
+      <c r="I98">
+        <v>148.953159041394</v>
+      </c>
+      <c r="J98">
+        <v>0.61162957645369698</v>
+      </c>
+      <c r="K98">
+        <v>0.34386216798276997</v>
+      </c>
+      <c r="L98">
+        <v>8.9734386216798207E-3</v>
+      </c>
+      <c r="M98">
+        <v>2.9791816223976999E-2</v>
+      </c>
+      <c r="N98">
+        <v>0</v>
+      </c>
+      <c r="O98">
+        <v>0</v>
+      </c>
+      <c r="P98">
+        <v>5.7430007178750899E-3</v>
+      </c>
+    </row>
+    <row r="99" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A99">
+        <v>0</v>
+      </c>
+      <c r="B99" t="s">
+        <v>339</v>
+      </c>
+      <c r="C99" t="s">
+        <v>340</v>
+      </c>
+      <c r="D99" t="s">
+        <v>262</v>
+      </c>
+      <c r="E99">
+        <v>0.38786652230396601</v>
+      </c>
+      <c r="F99">
+        <v>6.4724919093851099E-2</v>
+      </c>
+      <c r="G99">
+        <v>0.50755124056094891</v>
+      </c>
+      <c r="H99">
+        <v>10</v>
+      </c>
+      <c r="I99">
+        <v>155.106902356902</v>
+      </c>
+      <c r="J99">
+        <v>4.2394822006472398E-2</v>
+      </c>
+      <c r="K99">
+        <v>0.332362459546925</v>
+      </c>
+      <c r="L99">
+        <v>0.40355987055016102</v>
+      </c>
+      <c r="M99">
+        <v>0.13495145631067901</v>
+      </c>
+      <c r="N99">
+        <v>2.2006472491909301E-2</v>
+      </c>
+      <c r="O99">
+        <v>4.72491909385113E-2</v>
+      </c>
+      <c r="P99">
+        <v>1.7475728155339799E-2</v>
+      </c>
+    </row>
+    <row r="100" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A100">
+        <v>60</v>
+      </c>
+      <c r="B100" t="s">
+        <v>339</v>
+      </c>
+      <c r="C100" t="s">
+        <v>340</v>
+      </c>
+      <c r="D100" t="s">
+        <v>262</v>
+      </c>
+      <c r="E100">
+        <v>0.45318920134833801</v>
+      </c>
+      <c r="F100">
+        <v>6.8248293792655098E-3</v>
+      </c>
+      <c r="G100">
+        <v>0.51099555844437183</v>
+      </c>
+      <c r="H100">
+        <v>28.5</v>
+      </c>
+      <c r="I100">
+        <v>164.581082564778</v>
+      </c>
+      <c r="J100">
+        <v>4.0948976275593102E-2</v>
+      </c>
+      <c r="K100">
+        <v>0.39649008774780597</v>
+      </c>
+      <c r="L100">
+        <v>0.50048748781280405</v>
+      </c>
+      <c r="M100">
+        <v>3.6724081897952503E-2</v>
+      </c>
+      <c r="N100">
+        <v>1.8524536886577798E-2</v>
+      </c>
+      <c r="O100">
+        <v>6.4998375040623904E-3</v>
+      </c>
+      <c r="P100">
+        <v>3.2499187520311902E-4</v>
+      </c>
+    </row>
+    <row r="101" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A101">
+        <v>120</v>
+      </c>
+      <c r="B101" t="s">
+        <v>339</v>
+      </c>
+      <c r="C101" t="s">
+        <v>340</v>
+      </c>
+      <c r="D101" t="s">
+        <v>262</v>
+      </c>
+      <c r="E101">
+        <v>0.44779835712426802</v>
+      </c>
+      <c r="F101">
+        <v>3.64346128822381E-2</v>
+      </c>
+      <c r="G101">
+        <v>0.42463673823465581</v>
+      </c>
+      <c r="H101">
+        <v>24.5</v>
+      </c>
+      <c r="I101">
+        <v>180.74158249158199</v>
+      </c>
+      <c r="J101">
+        <v>2.7325959661678501E-2</v>
+      </c>
+      <c r="K101">
+        <v>0.61743656473649899</v>
+      </c>
+      <c r="L101">
+        <v>0.28887443070917301</v>
+      </c>
+      <c r="M101">
+        <v>2.9928432010409799E-2</v>
+      </c>
+      <c r="N101">
+        <v>0</v>
+      </c>
+      <c r="O101">
+        <v>1.8867924528301799E-2</v>
+      </c>
+      <c r="P101">
+        <v>1.75666883539362E-2</v>
+      </c>
+    </row>
+    <row r="102" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A102">
+        <v>180</v>
+      </c>
+      <c r="B102" t="s">
+        <v>339</v>
+      </c>
+      <c r="C102" t="s">
+        <v>340</v>
+      </c>
+      <c r="D102" t="s">
+        <v>262</v>
+      </c>
+      <c r="E102">
+        <v>0.354539076601396</v>
+      </c>
+      <c r="F102">
+        <v>5.6466302367941701E-2</v>
+      </c>
+      <c r="G102">
+        <v>0.35701275045537323</v>
+      </c>
+      <c r="H102">
+        <v>25</v>
+      </c>
+      <c r="I102">
+        <v>181.14135802469099</v>
+      </c>
+      <c r="J102">
+        <v>0.191621129326047</v>
+      </c>
+      <c r="K102">
+        <v>0.45719489981785</v>
+      </c>
+      <c r="L102">
+        <v>0.26448087431693901</v>
+      </c>
+      <c r="M102">
+        <v>3.02367941712204E-2</v>
+      </c>
+      <c r="N102">
+        <v>0</v>
+      </c>
+      <c r="O102">
+        <v>2.44080145719489E-2</v>
+      </c>
+      <c r="P102">
+        <v>3.20582877959927E-2</v>
+      </c>
+    </row>
+    <row r="103" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A103">
+        <v>0</v>
+      </c>
+      <c r="B103" t="s">
+        <v>339</v>
+      </c>
+      <c r="C103" t="s">
+        <v>340</v>
+      </c>
+      <c r="D103" t="s">
+        <v>284</v>
+      </c>
+      <c r="E103">
+        <v>0.27671749925544198</v>
+      </c>
+      <c r="F103">
+        <v>1.7214742882365901E-2</v>
+      </c>
+      <c r="G103">
+        <v>0.11550062532185666</v>
+      </c>
+      <c r="H103">
+        <v>10.5</v>
+      </c>
+      <c r="I103">
+        <v>191.45555555555501</v>
+      </c>
+      <c r="J103">
+        <v>0.637386890311189</v>
+      </c>
+      <c r="K103">
+        <v>0.34429485764731799</v>
+      </c>
+      <c r="L103">
+        <v>0</v>
+      </c>
+      <c r="M103">
+        <v>1.10350915912602E-3</v>
+      </c>
+      <c r="N103">
+        <v>0</v>
+      </c>
+      <c r="O103">
+        <v>0</v>
+      </c>
+      <c r="P103">
+        <v>1.7214742882365901E-2</v>
+      </c>
+    </row>
+    <row r="104" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A104">
+        <v>60</v>
+      </c>
+      <c r="B104" t="s">
+        <v>339</v>
+      </c>
+      <c r="C104" t="s">
+        <v>340</v>
+      </c>
+      <c r="D104" t="s">
+        <v>284</v>
+      </c>
+      <c r="E104">
+        <v>0.45683060018319099</v>
+      </c>
+      <c r="F104">
+        <v>0</v>
+      </c>
+      <c r="G104">
+        <v>7.0600322912079669E-2</v>
+      </c>
+      <c r="H104">
+        <v>24</v>
+      </c>
+      <c r="I104">
+        <v>186.00300300300299</v>
+      </c>
+      <c r="J104">
+        <v>0.78819903126376001</v>
+      </c>
+      <c r="K104">
+        <v>0.21180096873623899</v>
+      </c>
+      <c r="L104">
+        <v>0</v>
+      </c>
+      <c r="M104">
+        <v>0</v>
+      </c>
+      <c r="N104">
+        <v>0</v>
+      </c>
+      <c r="O104">
+        <v>0</v>
+      </c>
+      <c r="P104">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A105">
+        <v>120</v>
+      </c>
+      <c r="B105" t="s">
+        <v>339</v>
+      </c>
+      <c r="C105" t="s">
+        <v>340</v>
+      </c>
+      <c r="D105" t="s">
+        <v>284</v>
+      </c>
+      <c r="E105">
+        <v>0.30753190700452798</v>
+      </c>
+      <c r="F105">
+        <v>2.2036139268400098E-3</v>
+      </c>
+      <c r="G105">
+        <v>0.13177611282503301</v>
+      </c>
+      <c r="H105">
+        <v>18</v>
+      </c>
+      <c r="I105">
+        <v>193.86361283643799</v>
+      </c>
+      <c r="J105">
+        <v>0.61546936976641697</v>
+      </c>
+      <c r="K105">
+        <v>0.37152930806522699</v>
+      </c>
+      <c r="L105">
+        <v>1.0797708241516E-2</v>
+      </c>
+      <c r="M105">
+        <v>0</v>
+      </c>
+      <c r="N105">
+        <v>0</v>
+      </c>
+      <c r="O105">
+        <v>2.2036139268400098E-3</v>
+      </c>
+      <c r="P105">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A106">
+        <v>180</v>
+      </c>
+      <c r="B106" t="s">
+        <v>339</v>
+      </c>
+      <c r="C106" t="s">
+        <v>340</v>
+      </c>
+      <c r="D106" t="s">
+        <v>284</v>
+      </c>
+      <c r="E106">
+        <v>0.4811702597991</v>
+      </c>
+      <c r="F106">
+        <v>6.32083696599825E-3</v>
+      </c>
+      <c r="G106">
+        <v>0.13818657367044443</v>
+      </c>
+      <c r="H106">
+        <v>26.5</v>
+      </c>
+      <c r="I106">
+        <v>197.473316912972</v>
+      </c>
+      <c r="J106">
+        <v>0.59306887532693897</v>
+      </c>
+      <c r="K106">
+        <v>0.38666085440278902</v>
+      </c>
+      <c r="L106">
+        <v>3.26939843068875E-3</v>
+      </c>
+      <c r="M106">
+        <v>1.06800348735832E-2</v>
+      </c>
+      <c r="N106">
+        <v>0</v>
+      </c>
+      <c r="O106">
+        <v>0</v>
+      </c>
+      <c r="P106">
+        <v>6.32083696599825E-3</v>
+      </c>
+    </row>
+    <row r="107" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A107">
+        <v>240</v>
+      </c>
+      <c r="B107" t="s">
+        <v>339</v>
+      </c>
+      <c r="C107" t="s">
+        <v>340</v>
+      </c>
+      <c r="D107" t="s">
+        <v>284</v>
+      </c>
+      <c r="E107">
+        <v>0.289183274172095</v>
+      </c>
+      <c r="F107">
+        <v>2.68781669971359E-2</v>
+      </c>
+      <c r="G107">
+        <v>0.18043621943159249</v>
+      </c>
+      <c r="H107">
+        <v>21.5</v>
+      </c>
+      <c r="I107">
+        <v>195.775462962962</v>
+      </c>
+      <c r="J107">
+        <v>0.45362414628772801</v>
+      </c>
+      <c r="K107">
+        <v>0.49768671513549201</v>
+      </c>
+      <c r="L107">
+        <v>2.86406697510464E-3</v>
+      </c>
+      <c r="M107">
+        <v>1.8946904604538399E-2</v>
+      </c>
+      <c r="N107">
+        <v>0</v>
+      </c>
+      <c r="O107">
+        <v>0</v>
+      </c>
+      <c r="P107">
+        <v>2.68781669971359E-2</v>
+      </c>
+    </row>
+    <row r="108" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A108">
+        <v>300</v>
+      </c>
+      <c r="B108" t="s">
+        <v>339</v>
+      </c>
+      <c r="C108" t="s">
+        <v>340</v>
+      </c>
+      <c r="D108" t="s">
+        <v>284</v>
+      </c>
+      <c r="E108">
+        <v>0.651913821052023</v>
+      </c>
+      <c r="F108">
+        <v>6.6889632107023402E-3</v>
+      </c>
+      <c r="G108">
+        <v>0.16930509104422101</v>
+      </c>
+      <c r="H108">
+        <v>23.5</v>
+      </c>
+      <c r="I108">
+        <v>206.46812544180901</v>
+      </c>
+      <c r="J108">
+        <v>0.52441471571906295</v>
+      </c>
+      <c r="K108">
+        <v>0.42987736900780299</v>
+      </c>
+      <c r="L108">
+        <v>1.3377926421404599E-3</v>
+      </c>
+      <c r="M108">
+        <v>3.7681159420289802E-2</v>
+      </c>
+      <c r="N108">
+        <v>0</v>
+      </c>
+      <c r="O108">
+        <v>0</v>
+      </c>
+      <c r="P108">
+        <v>6.6889632107023402E-3</v>
+      </c>
+    </row>
+    <row r="109" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A109">
+        <v>360</v>
+      </c>
+      <c r="B109" t="s">
+        <v>339</v>
+      </c>
+      <c r="C109" t="s">
+        <v>340</v>
+      </c>
+      <c r="D109" t="s">
+        <v>284</v>
+      </c>
+      <c r="E109">
+        <v>0.605231404124566</v>
+      </c>
+      <c r="F109">
+        <v>1.16853932584269E-2</v>
+      </c>
+      <c r="G109">
+        <v>5.9026217228464239E-2</v>
+      </c>
+      <c r="H109">
+        <v>29</v>
+      </c>
+      <c r="I109">
+        <v>194.20634920634899</v>
+      </c>
+      <c r="J109">
+        <v>0.81662921348314599</v>
+      </c>
+      <c r="K109">
+        <v>0.16629213483145999</v>
+      </c>
+      <c r="L109">
+        <v>0</v>
+      </c>
+      <c r="M109">
+        <v>5.3932584269662902E-3</v>
+      </c>
+      <c r="N109">
+        <v>0</v>
+      </c>
+      <c r="O109">
+        <v>0</v>
+      </c>
+      <c r="P109">
+        <v>1.16853932584269E-2</v>
+      </c>
+    </row>
+    <row r="110" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A110">
+        <v>420</v>
+      </c>
+      <c r="B110" t="s">
+        <v>339</v>
+      </c>
+      <c r="C110" t="s">
+        <v>340</v>
+      </c>
+      <c r="D110" t="s">
+        <v>284</v>
+      </c>
+      <c r="E110">
+        <v>0.66842457022510304</v>
+      </c>
+      <c r="F110">
+        <v>8.6694308330192201E-3</v>
+      </c>
+      <c r="G110">
+        <v>5.3775599949742403E-2</v>
+      </c>
+      <c r="H110">
+        <v>27.5</v>
+      </c>
+      <c r="I110">
+        <v>203.59566250742699</v>
+      </c>
+      <c r="J110">
+        <v>0.83565774594798303</v>
+      </c>
+      <c r="K110">
+        <v>0.15001884658876699</v>
+      </c>
+      <c r="L110">
+        <v>1.50772710139464E-3</v>
+      </c>
+      <c r="M110">
+        <v>4.1462495288352797E-3</v>
+      </c>
+      <c r="N110">
+        <v>0</v>
+      </c>
+      <c r="O110">
+        <v>0</v>
+      </c>
+      <c r="P110">
+        <v>8.6694308330192201E-3</v>
+      </c>
+    </row>
+    <row r="111" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A111">
+        <v>0</v>
+      </c>
+      <c r="B111" t="s">
+        <v>339</v>
+      </c>
+      <c r="C111" t="s">
+        <v>338</v>
+      </c>
+      <c r="D111" t="s">
+        <v>294</v>
+      </c>
+      <c r="E111">
+        <v>0.16184115663017501</v>
+      </c>
+      <c r="F111">
+        <v>6.0357901122232299E-2</v>
+      </c>
+      <c r="G111" s="1">
+        <v>0.22768173086644392</v>
+      </c>
+      <c r="H111">
+        <v>11.5</v>
+      </c>
+      <c r="I111">
+        <v>150.797979797979</v>
+      </c>
+      <c r="J111">
+        <v>0.34334243251440699</v>
+      </c>
+      <c r="K111">
+        <v>0.520473157415832</v>
+      </c>
+      <c r="L111">
+        <v>1.6985138004246201E-2</v>
+      </c>
+      <c r="M111">
+        <v>5.4291780406429999E-2</v>
+      </c>
+      <c r="N111">
+        <v>4.5495905368516804E-3</v>
+      </c>
+      <c r="O111">
+        <v>6.3694267515923501E-3</v>
+      </c>
+      <c r="P111">
+        <v>5.3988474370639902E-2</v>
+      </c>
+    </row>
+    <row r="112" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A112">
+        <v>60</v>
+      </c>
+      <c r="B112" t="s">
+        <v>339</v>
+      </c>
+      <c r="C112" t="s">
+        <v>338</v>
+      </c>
+      <c r="D112" t="s">
+        <v>294</v>
+      </c>
+      <c r="E112">
+        <v>0.53171538953457598</v>
+      </c>
+      <c r="F112">
+        <v>6.6343532262950602E-2</v>
+      </c>
+      <c r="G112" s="1">
+        <v>0.20630112087246277</v>
+      </c>
+      <c r="H112">
+        <v>30.5</v>
+      </c>
+      <c r="I112">
+        <v>163.036733161733</v>
+      </c>
+      <c r="J112">
+        <v>0.336564677370493</v>
+      </c>
+      <c r="K112">
+        <v>0.57528021811572205</v>
+      </c>
+      <c r="L112">
+        <v>0</v>
+      </c>
+      <c r="M112">
+        <v>2.1811572250833001E-2</v>
+      </c>
+      <c r="N112">
+        <v>0</v>
+      </c>
+      <c r="O112">
+        <v>0</v>
+      </c>
+      <c r="P112">
+        <v>6.6343532262950602E-2</v>
+      </c>
+    </row>
+    <row r="113" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A113">
+        <v>120</v>
+      </c>
+      <c r="B113" t="s">
+        <v>339</v>
+      </c>
+      <c r="C113" t="s">
+        <v>338</v>
+      </c>
+      <c r="D113" t="s">
+        <v>294</v>
+      </c>
+      <c r="E113">
+        <v>0.67352368884810099</v>
+      </c>
+      <c r="F113">
+        <v>7.51357875678937E-2</v>
+      </c>
+      <c r="G113" s="1">
+        <v>0.14403540535103568</v>
+      </c>
+      <c r="H113">
+        <v>15.5</v>
+      </c>
+      <c r="I113">
+        <v>145.21618357487901</v>
+      </c>
+      <c r="J113">
+        <v>0.51327700663850295</v>
+      </c>
+      <c r="K113">
+        <v>0.391068195534097</v>
+      </c>
+      <c r="L113">
+        <v>0</v>
+      </c>
+      <c r="M113">
+        <v>2.0519010259505099E-2</v>
+      </c>
+      <c r="N113">
+        <v>0</v>
+      </c>
+      <c r="O113">
+        <v>0</v>
+      </c>
+      <c r="P113">
+        <v>7.51357875678937E-2</v>
+      </c>
+    </row>
+    <row r="114" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A114">
+        <v>180</v>
+      </c>
+      <c r="B114" t="s">
+        <v>339</v>
+      </c>
+      <c r="C114" t="s">
+        <v>338</v>
+      </c>
+      <c r="D114" t="s">
+        <v>294</v>
+      </c>
+      <c r="E114">
+        <v>0.64443376410332798</v>
+      </c>
+      <c r="F114">
+        <v>3.3393501805054099E-2</v>
+      </c>
+      <c r="G114" s="1">
+        <v>0.24107501002807849</v>
+      </c>
+      <c r="H114">
+        <v>31</v>
+      </c>
+      <c r="I114">
+        <v>168.892361111111</v>
+      </c>
+      <c r="J114">
+        <v>0.383273164861612</v>
+      </c>
+      <c r="K114">
+        <v>0.44374247894103402</v>
+      </c>
+      <c r="L114">
+        <v>2.7075812274368199E-3</v>
+      </c>
+      <c r="M114">
+        <v>0.13688327316486101</v>
+      </c>
+      <c r="N114">
+        <v>0</v>
+      </c>
+      <c r="O114">
+        <v>3.0084235860409098E-4</v>
+      </c>
+      <c r="P114">
+        <v>3.3092659446449998E-2</v>
+      </c>
+    </row>
+    <row r="115" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A115">
+        <v>240</v>
+      </c>
+      <c r="B115" t="s">
+        <v>339</v>
+      </c>
+      <c r="C115" t="s">
+        <v>338</v>
+      </c>
+      <c r="D115" t="s">
+        <v>294</v>
+      </c>
+      <c r="E115">
+        <v>0.57168590005764497</v>
+      </c>
+      <c r="F115">
+        <v>2.4736048265460001E-2</v>
+      </c>
+      <c r="G115" s="1">
+        <v>0.1524384112619406</v>
+      </c>
+      <c r="H115">
+        <v>29</v>
+      </c>
+      <c r="I115">
+        <v>169.029647435897</v>
+      </c>
+      <c r="J115">
+        <v>0.52549019607843095</v>
+      </c>
+      <c r="K115">
+        <v>0.44223227752639499</v>
+      </c>
+      <c r="L115">
+        <v>0</v>
+      </c>
+      <c r="M115">
+        <v>7.5414781297134196E-3</v>
+      </c>
+      <c r="N115">
+        <v>0</v>
+      </c>
+      <c r="O115">
+        <v>0</v>
+      </c>
+      <c r="P115">
+        <v>2.4736048265460001E-2</v>
+      </c>
+    </row>
+    <row r="116" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A116">
+        <v>300</v>
+      </c>
+      <c r="B116" t="s">
+        <v>339</v>
+      </c>
+      <c r="C116" t="s">
+        <v>338</v>
+      </c>
+      <c r="D116" t="s">
+        <v>294</v>
+      </c>
+      <c r="E116">
+        <v>0.53089662327207598</v>
+      </c>
+      <c r="F116">
+        <v>0.136610373944511</v>
+      </c>
+      <c r="G116" s="1">
+        <v>0.19250100522718097</v>
+      </c>
+      <c r="H116">
+        <v>25</v>
+      </c>
+      <c r="I116">
+        <v>159.931746031746</v>
+      </c>
+      <c r="J116">
+        <v>0.33594692400482501</v>
+      </c>
+      <c r="K116">
+        <v>0.47738238841978198</v>
+      </c>
+      <c r="L116">
+        <v>3.0156815440289498E-4</v>
+      </c>
+      <c r="M116">
+        <v>4.97587454764776E-2</v>
+      </c>
+      <c r="N116">
+        <v>0</v>
+      </c>
+      <c r="O116">
+        <v>0</v>
+      </c>
+      <c r="P116">
+        <v>0.136610373944511</v>
+      </c>
+    </row>
+    <row r="117" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A117">
+        <v>360</v>
+      </c>
+      <c r="B117" t="s">
+        <v>339</v>
+      </c>
+      <c r="C117" t="s">
+        <v>338</v>
+      </c>
+      <c r="D117" t="s">
+        <v>294</v>
+      </c>
+      <c r="E117">
+        <v>0.63635469068351502</v>
+      </c>
+      <c r="F117">
+        <v>5.9178743961352601E-2</v>
+      </c>
+      <c r="G117" s="1">
+        <v>0.22473832528180315</v>
+      </c>
+      <c r="H117">
+        <v>19</v>
+      </c>
+      <c r="I117">
+        <v>163.392495126705</v>
+      </c>
+      <c r="J117">
+        <v>0.37167874396135198</v>
+      </c>
+      <c r="K117">
+        <v>0.46467391304347799</v>
+      </c>
+      <c r="L117">
+        <v>2.5362318840579701E-2</v>
+      </c>
+      <c r="M117">
+        <v>7.9106280193236705E-2</v>
+      </c>
+      <c r="N117">
+        <v>0</v>
+      </c>
+      <c r="O117">
+        <v>6.0386473429951601E-4</v>
+      </c>
+      <c r="P117">
+        <v>5.8574879227053102E-2</v>
+      </c>
+    </row>
+    <row r="118" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A118">
+        <v>420</v>
+      </c>
+      <c r="B118" t="s">
+        <v>339</v>
+      </c>
+      <c r="C118" t="s">
+        <v>338</v>
+      </c>
+      <c r="D118" t="s">
+        <v>294</v>
+      </c>
+      <c r="E118">
+        <v>0.50503204912103095</v>
+      </c>
+      <c r="F118">
+        <v>0.12041564792176</v>
+      </c>
+      <c r="G118" s="1">
+        <v>0.2150570497147509</v>
+      </c>
+      <c r="H118">
+        <v>31</v>
+      </c>
+      <c r="I118">
+        <v>157.90152359717499</v>
+      </c>
+      <c r="J118">
+        <v>0.33649144254278701</v>
+      </c>
+      <c r="K118">
+        <v>0.44376528117359398</v>
+      </c>
+      <c r="L118">
+        <v>9.4743276283618498E-3</v>
+      </c>
+      <c r="M118">
+        <v>8.9853300733496302E-2</v>
+      </c>
+      <c r="N118">
+        <v>0</v>
+      </c>
+      <c r="O118">
+        <v>2.7506112469437602E-3</v>
+      </c>
+      <c r="P118">
+        <v>0.117665036674816</v>
+      </c>
+    </row>
+    <row r="119" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A119">
         <v>480</v>
       </c>
-      <c r="B76" t="s">
-        <v>337</v>
-      </c>
-      <c r="C76" t="s">
-        <v>338</v>
-      </c>
-      <c r="D76" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A77">
+      <c r="B119" t="s">
+        <v>339</v>
+      </c>
+      <c r="C119" t="s">
+        <v>338</v>
+      </c>
+      <c r="D119" t="s">
+        <v>294</v>
+      </c>
+      <c r="E119">
+        <v>0.58210449283191401</v>
+      </c>
+      <c r="F119">
+        <v>0.14302957151478499</v>
+      </c>
+      <c r="G119" s="1">
+        <v>0.23375578354455839</v>
+      </c>
+      <c r="H119">
+        <v>21.5</v>
+      </c>
+      <c r="I119">
+        <v>153.097671957671</v>
+      </c>
+      <c r="J119">
+        <v>0.24954737477368699</v>
+      </c>
+      <c r="K119">
+        <v>0.52383826191913097</v>
+      </c>
+      <c r="L119">
+        <v>2.4140012070006001E-3</v>
+      </c>
+      <c r="M119">
+        <v>7.3928786964393395E-2</v>
+      </c>
+      <c r="N119">
+        <v>7.2420036210018102E-3</v>
+      </c>
+      <c r="O119">
+        <v>3.01750150875075E-3</v>
+      </c>
+      <c r="P119">
+        <v>0.14001207000603499</v>
+      </c>
+    </row>
+    <row r="120" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A120">
         <v>540</v>
       </c>
-      <c r="B77" t="s">
-        <v>337</v>
-      </c>
-      <c r="C77" t="s">
-        <v>338</v>
-      </c>
-      <c r="D77" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A78">
+      <c r="B120" t="s">
+        <v>339</v>
+      </c>
+      <c r="C120" t="s">
+        <v>338</v>
+      </c>
+      <c r="D120" t="s">
+        <v>294</v>
+      </c>
+      <c r="E120">
+        <v>0.669605968323287</v>
+      </c>
+      <c r="F120">
+        <v>0.14992412746585701</v>
+      </c>
+      <c r="G120" s="1">
+        <v>0.20384420839656001</v>
+      </c>
+      <c r="H120">
+        <v>24</v>
+      </c>
+      <c r="I120">
+        <v>156.23753623188401</v>
+      </c>
+      <c r="J120">
+        <v>0.31532625189681301</v>
+      </c>
+      <c r="K120">
+        <v>0.459180576631259</v>
+      </c>
+      <c r="L120">
+        <v>1.09256449165402E-2</v>
+      </c>
+      <c r="M120">
+        <v>6.4036418816388399E-2</v>
+      </c>
+      <c r="N120">
+        <v>6.0698027314112204E-4</v>
+      </c>
+      <c r="O120">
+        <v>6.0698027314112204E-4</v>
+      </c>
+      <c r="P120">
+        <v>0.14931714719271599</v>
+      </c>
+    </row>
+    <row r="121" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A121">
         <v>600</v>
       </c>
-      <c r="B78" t="s">
-        <v>337</v>
-      </c>
-      <c r="C78" t="s">
-        <v>338</v>
-      </c>
-      <c r="D78" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A79">
-        <v>0</v>
-      </c>
-      <c r="B79" t="s">
-        <v>337</v>
-      </c>
-      <c r="C79" t="s">
-        <v>338</v>
-      </c>
-      <c r="D79" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A80">
+      <c r="B121" t="s">
+        <v>339</v>
+      </c>
+      <c r="C121" t="s">
+        <v>338</v>
+      </c>
+      <c r="D121" t="s">
+        <v>294</v>
+      </c>
+      <c r="E121">
+        <v>0.42875574825109503</v>
+      </c>
+      <c r="F121">
+        <v>4.5990566037735797E-2</v>
+      </c>
+      <c r="G121" s="1">
+        <v>0.20400943396226409</v>
+      </c>
+      <c r="H121">
+        <v>14.5</v>
+      </c>
+      <c r="I121">
+        <v>161.846671846671</v>
+      </c>
+      <c r="J121">
+        <v>0.43278301886792397</v>
+      </c>
+      <c r="K121">
+        <v>0.43042452830188599</v>
+      </c>
+      <c r="L121">
+        <v>1.2971698113207499E-2</v>
+      </c>
+      <c r="M121">
+        <v>7.7830188679245196E-2</v>
+      </c>
+      <c r="N121">
+        <v>0</v>
+      </c>
+      <c r="O121">
+        <v>0</v>
+      </c>
+      <c r="P121">
+        <v>4.5990566037735797E-2</v>
+      </c>
+    </row>
+    <row r="122" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A122">
+        <v>0</v>
+      </c>
+      <c r="B122" t="s">
+        <v>339</v>
+      </c>
+      <c r="C122" t="s">
+        <v>340</v>
+      </c>
+      <c r="D122" t="s">
+        <v>272</v>
+      </c>
+      <c r="E122">
+        <v>8.1788433723884293E-2</v>
+      </c>
+      <c r="F122">
+        <v>0</v>
+      </c>
+      <c r="G122">
+        <v>0.10152332292553677</v>
+      </c>
+      <c r="H122">
+        <v>2</v>
+      </c>
+      <c r="I122">
+        <v>195.5</v>
+      </c>
+      <c r="J122">
+        <v>0.69770082316207704</v>
+      </c>
+      <c r="K122">
+        <v>0.300028384899233</v>
+      </c>
+      <c r="L122">
+        <v>2.2707919386886098E-3</v>
+      </c>
+      <c r="M122">
+        <v>0</v>
+      </c>
+      <c r="N122">
+        <v>0</v>
+      </c>
+      <c r="O122">
+        <v>0</v>
+      </c>
+      <c r="P122">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A123">
         <v>60</v>
       </c>
-      <c r="B80" t="s">
-        <v>337</v>
-      </c>
-      <c r="C80" t="s">
-        <v>338</v>
-      </c>
-      <c r="D80" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A81">
+      <c r="B123" t="s">
+        <v>339</v>
+      </c>
+      <c r="C123" t="s">
+        <v>340</v>
+      </c>
+      <c r="D123" t="s">
+        <v>272</v>
+      </c>
+      <c r="E123">
+        <v>0.36184156270390599</v>
+      </c>
+      <c r="F123">
+        <v>0</v>
+      </c>
+      <c r="G123">
+        <v>1.1536643026004705E-2</v>
+      </c>
+      <c r="H123">
+        <v>17.5</v>
+      </c>
+      <c r="I123">
+        <v>173.122420020639</v>
+      </c>
+      <c r="J123">
+        <v>0.96539007092198503</v>
+      </c>
+      <c r="K123">
+        <v>3.46099290780141E-2</v>
+      </c>
+      <c r="L123">
+        <v>0</v>
+      </c>
+      <c r="M123">
+        <v>0</v>
+      </c>
+      <c r="N123">
+        <v>0</v>
+      </c>
+      <c r="O123">
+        <v>0</v>
+      </c>
+      <c r="P123">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A124">
         <v>120</v>
       </c>
-      <c r="B81" t="s">
-        <v>337</v>
-      </c>
-      <c r="C81" t="s">
-        <v>338</v>
-      </c>
-      <c r="D81" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A82">
+      <c r="B124" t="s">
+        <v>339</v>
+      </c>
+      <c r="C124" t="s">
+        <v>340</v>
+      </c>
+      <c r="D124" t="s">
+        <v>272</v>
+      </c>
+      <c r="E124">
+        <v>0.53748674094673898</v>
+      </c>
+      <c r="F124">
+        <v>0</v>
+      </c>
+      <c r="G124">
+        <v>9.6508657394265996E-3</v>
+      </c>
+      <c r="H124">
+        <v>20</v>
+      </c>
+      <c r="I124">
+        <v>178.60208866155099</v>
+      </c>
+      <c r="J124">
+        <v>0.97104740278171997</v>
+      </c>
+      <c r="K124">
+        <v>2.8952597218279801E-2</v>
+      </c>
+      <c r="L124">
+        <v>0</v>
+      </c>
+      <c r="M124">
+        <v>0</v>
+      </c>
+      <c r="N124">
+        <v>0</v>
+      </c>
+      <c r="O124">
+        <v>0</v>
+      </c>
+      <c r="P124">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A125">
         <v>180</v>
       </c>
-      <c r="B82" t="s">
-        <v>337</v>
-      </c>
-      <c r="C82" t="s">
-        <v>338</v>
-      </c>
-      <c r="D82" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A83">
+      <c r="B125" t="s">
+        <v>339</v>
+      </c>
+      <c r="C125" t="s">
+        <v>340</v>
+      </c>
+      <c r="D125" t="s">
+        <v>272</v>
+      </c>
+      <c r="E125">
+        <v>0.49228480705799799</v>
+      </c>
+      <c r="F125">
+        <v>0</v>
+      </c>
+      <c r="G125">
+        <v>9.6453900709219664E-3</v>
+      </c>
+      <c r="H125">
+        <v>14</v>
+      </c>
+      <c r="I125">
+        <v>167.701388888888</v>
+      </c>
+      <c r="J125">
+        <v>0.97106382978723405</v>
+      </c>
+      <c r="K125">
+        <v>2.8936170212765899E-2</v>
+      </c>
+      <c r="L125">
+        <v>0</v>
+      </c>
+      <c r="M125">
+        <v>0</v>
+      </c>
+      <c r="N125">
+        <v>0</v>
+      </c>
+      <c r="O125">
+        <v>0</v>
+      </c>
+      <c r="P125">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A126">
         <v>240</v>
       </c>
-      <c r="B83" t="s">
-        <v>337</v>
-      </c>
-      <c r="C83" t="s">
-        <v>338</v>
-      </c>
-      <c r="D83" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A84">
+      <c r="B126" t="s">
+        <v>339</v>
+      </c>
+      <c r="C126" t="s">
+        <v>340</v>
+      </c>
+      <c r="D126" t="s">
+        <v>272</v>
+      </c>
+      <c r="E126">
+        <v>0.511364671595682</v>
+      </c>
+      <c r="F126">
+        <v>0</v>
+      </c>
+      <c r="G126">
+        <v>7.6552310745676005E-3</v>
+      </c>
+      <c r="H126">
+        <v>15</v>
+      </c>
+      <c r="I126">
+        <v>162.39629629629599</v>
+      </c>
+      <c r="J126">
+        <v>0.97703430677629699</v>
+      </c>
+      <c r="K126">
+        <v>2.2965693223702802E-2</v>
+      </c>
+      <c r="L126">
+        <v>0</v>
+      </c>
+      <c r="M126">
+        <v>0</v>
+      </c>
+      <c r="N126">
+        <v>0</v>
+      </c>
+      <c r="O126">
+        <v>0</v>
+      </c>
+      <c r="P126">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A127">
         <v>300</v>
       </c>
-      <c r="B84" t="s">
-        <v>337</v>
-      </c>
-      <c r="C84" t="s">
-        <v>338</v>
-      </c>
-      <c r="D84" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A85">
+      <c r="B127" t="s">
+        <v>339</v>
+      </c>
+      <c r="C127" t="s">
+        <v>340</v>
+      </c>
+      <c r="D127" t="s">
+        <v>272</v>
+      </c>
+      <c r="E127">
+        <v>0.58956744484623103</v>
+      </c>
+      <c r="F127">
+        <v>0</v>
+      </c>
+      <c r="G127">
+        <v>1.8240241943105532E-2</v>
+      </c>
+      <c r="H127">
+        <v>23</v>
+      </c>
+      <c r="I127">
+        <v>173.79944960440301</v>
+      </c>
+      <c r="J127">
+        <v>0.94527927417068303</v>
+      </c>
+      <c r="K127">
+        <v>5.4720725829316599E-2</v>
+      </c>
+      <c r="L127">
+        <v>0</v>
+      </c>
+      <c r="M127">
+        <v>0</v>
+      </c>
+      <c r="N127">
+        <v>0</v>
+      </c>
+      <c r="O127">
+        <v>0</v>
+      </c>
+      <c r="P127">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A128">
         <v>360</v>
       </c>
-      <c r="B85" t="s">
-        <v>337</v>
-      </c>
-      <c r="C85" t="s">
-        <v>338</v>
-      </c>
-      <c r="D85" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A86">
+      <c r="B128" t="s">
+        <v>339</v>
+      </c>
+      <c r="C128" t="s">
+        <v>340</v>
+      </c>
+      <c r="D128" t="s">
+        <v>272</v>
+      </c>
+      <c r="E128">
+        <v>0.54170214338456601</v>
+      </c>
+      <c r="F128">
+        <v>0</v>
+      </c>
+      <c r="G128">
+        <v>3.3276611835885789E-2</v>
+      </c>
+      <c r="H128">
+        <v>25.5</v>
+      </c>
+      <c r="I128">
+        <v>182.871945488721</v>
+      </c>
+      <c r="J128">
+        <v>0.900170164492342</v>
+      </c>
+      <c r="K128">
+        <v>9.9829835507657394E-2</v>
+      </c>
+      <c r="L128">
+        <v>0</v>
+      </c>
+      <c r="M128">
+        <v>0</v>
+      </c>
+      <c r="N128">
+        <v>0</v>
+      </c>
+      <c r="O128">
+        <v>0</v>
+      </c>
+      <c r="P128">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A129">
         <v>420</v>
       </c>
-      <c r="B86" t="s">
-        <v>337</v>
-      </c>
-      <c r="C86" t="s">
-        <v>338</v>
-      </c>
-      <c r="D86" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A87">
+      <c r="B129" t="s">
+        <v>339</v>
+      </c>
+      <c r="C129" t="s">
+        <v>340</v>
+      </c>
+      <c r="D129" t="s">
+        <v>272</v>
+      </c>
+      <c r="E129">
+        <v>0.63096763620009999</v>
+      </c>
+      <c r="F129">
+        <v>0</v>
+      </c>
+      <c r="G129">
+        <v>1.0496453900709199E-2</v>
+      </c>
+      <c r="H129">
+        <v>17.5</v>
+      </c>
+      <c r="I129">
+        <v>181.112037037037</v>
+      </c>
+      <c r="J129">
+        <v>0.96851063829787198</v>
+      </c>
+      <c r="K129">
+        <v>3.14893617021276E-2</v>
+      </c>
+      <c r="L129">
+        <v>0</v>
+      </c>
+      <c r="M129">
+        <v>0</v>
+      </c>
+      <c r="N129">
+        <v>0</v>
+      </c>
+      <c r="O129">
+        <v>0</v>
+      </c>
+      <c r="P129">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A130">
         <v>480</v>
       </c>
-      <c r="B87" t="s">
-        <v>337</v>
-      </c>
-      <c r="C87" t="s">
-        <v>338</v>
-      </c>
-      <c r="D87" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A88">
+      <c r="B130" t="s">
+        <v>339</v>
+      </c>
+      <c r="C130" t="s">
+        <v>340</v>
+      </c>
+      <c r="D130" t="s">
+        <v>272</v>
+      </c>
+      <c r="E130">
+        <v>0.384927364246963</v>
+      </c>
+      <c r="F130">
+        <v>0</v>
+      </c>
+      <c r="G130">
+        <v>0</v>
+      </c>
+      <c r="H130">
+        <v>18</v>
+      </c>
+      <c r="I130">
+        <v>164.293452380952</v>
+      </c>
+      <c r="J130">
+        <v>1</v>
+      </c>
+      <c r="K130">
+        <v>0</v>
+      </c>
+      <c r="L130">
+        <v>0</v>
+      </c>
+      <c r="M130">
+        <v>0</v>
+      </c>
+      <c r="N130">
+        <v>0</v>
+      </c>
+      <c r="O130">
+        <v>0</v>
+      </c>
+      <c r="P130">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A131">
         <v>540</v>
       </c>
-      <c r="B88" t="s">
-        <v>337</v>
-      </c>
-      <c r="C88" t="s">
-        <v>338</v>
-      </c>
-      <c r="D88" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A89">
-        <v>600</v>
-      </c>
-      <c r="B89" t="s">
-        <v>337</v>
-      </c>
-      <c r="C89" t="s">
-        <v>338</v>
-      </c>
-      <c r="D89" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A90">
-        <v>660</v>
-      </c>
-      <c r="B90" t="s">
-        <v>337</v>
-      </c>
-      <c r="C90" t="s">
-        <v>338</v>
-      </c>
-      <c r="D90" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A91">
-        <v>720</v>
-      </c>
-      <c r="B91" t="s">
-        <v>337</v>
-      </c>
-      <c r="C91" t="s">
-        <v>338</v>
-      </c>
-      <c r="D91" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A92">
-        <v>780</v>
-      </c>
-      <c r="B92" t="s">
-        <v>337</v>
-      </c>
-      <c r="C92" t="s">
-        <v>338</v>
-      </c>
-      <c r="D92" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A93">
-        <v>0</v>
-      </c>
-      <c r="B93" t="s">
-        <v>337</v>
-      </c>
-      <c r="C93" t="s">
-        <v>338</v>
-      </c>
-      <c r="D93" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A94">
-        <v>60</v>
-      </c>
-      <c r="B94" t="s">
-        <v>337</v>
-      </c>
-      <c r="C94" t="s">
-        <v>338</v>
-      </c>
-      <c r="D94" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A95">
-        <v>120</v>
-      </c>
-      <c r="B95" t="s">
-        <v>337</v>
-      </c>
-      <c r="C95" t="s">
-        <v>338</v>
-      </c>
-      <c r="D95" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A96">
-        <v>180</v>
-      </c>
-      <c r="B96" t="s">
-        <v>337</v>
-      </c>
-      <c r="C96" t="s">
-        <v>338</v>
-      </c>
-      <c r="D96" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A97">
-        <v>240</v>
-      </c>
-      <c r="B97" t="s">
-        <v>337</v>
-      </c>
-      <c r="C97" t="s">
-        <v>338</v>
-      </c>
-      <c r="D97" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A98">
-        <v>300</v>
-      </c>
-      <c r="B98" t="s">
-        <v>337</v>
-      </c>
-      <c r="C98" t="s">
-        <v>338</v>
-      </c>
-      <c r="D98" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A99">
-        <v>360</v>
-      </c>
-      <c r="B99" t="s">
-        <v>337</v>
-      </c>
-      <c r="C99" t="s">
-        <v>338</v>
-      </c>
-      <c r="D99" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A100">
-        <v>0</v>
-      </c>
-      <c r="B100" t="s">
-        <v>337</v>
-      </c>
-      <c r="C100" t="s">
-        <v>338</v>
-      </c>
-      <c r="D100" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A101">
-        <v>60</v>
-      </c>
-      <c r="B101" t="s">
-        <v>337</v>
-      </c>
-      <c r="C101" t="s">
-        <v>338</v>
-      </c>
-      <c r="D101" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A102">
-        <v>120</v>
-      </c>
-      <c r="B102" t="s">
-        <v>337</v>
-      </c>
-      <c r="C102" t="s">
-        <v>338</v>
-      </c>
-      <c r="D102" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A103">
-        <v>180</v>
-      </c>
-      <c r="B103" t="s">
-        <v>337</v>
-      </c>
-      <c r="C103" t="s">
-        <v>338</v>
-      </c>
-      <c r="D103" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A104">
-        <v>240</v>
-      </c>
-      <c r="B104" t="s">
-        <v>337</v>
-      </c>
-      <c r="C104" t="s">
-        <v>338</v>
-      </c>
-      <c r="D104" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A105">
-        <v>300</v>
-      </c>
-      <c r="B105" t="s">
-        <v>337</v>
-      </c>
-      <c r="C105" t="s">
-        <v>338</v>
-      </c>
-      <c r="D105" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A106">
-        <v>360</v>
-      </c>
-      <c r="B106" t="s">
-        <v>337</v>
-      </c>
-      <c r="C106" t="s">
-        <v>338</v>
-      </c>
-      <c r="D106" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A107">
-        <v>420</v>
-      </c>
-      <c r="B107" t="s">
-        <v>337</v>
-      </c>
-      <c r="C107" t="s">
-        <v>338</v>
-      </c>
-      <c r="D107" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A108">
-        <v>480</v>
-      </c>
-      <c r="B108" t="s">
-        <v>337</v>
-      </c>
-      <c r="C108" t="s">
-        <v>338</v>
-      </c>
-      <c r="D108" t="s">
-        <v>197</v>
+      <c r="B131" t="s">
+        <v>339</v>
+      </c>
+      <c r="C131" t="s">
+        <v>340</v>
+      </c>
+      <c r="D131" t="s">
+        <v>272</v>
+      </c>
+      <c r="E131">
+        <v>0.63126847607571801</v>
+      </c>
+      <c r="F131">
+        <v>0</v>
+      </c>
+      <c r="G131">
+        <v>0</v>
+      </c>
+      <c r="H131">
+        <v>15</v>
+      </c>
+      <c r="I131">
+        <v>177.03748006379499</v>
+      </c>
+      <c r="J131">
+        <v>1</v>
+      </c>
+      <c r="K131">
+        <v>0</v>
+      </c>
+      <c r="L131">
+        <v>0</v>
+      </c>
+      <c r="M131">
+        <v>0</v>
+      </c>
+      <c r="N131">
+        <v>0</v>
+      </c>
+      <c r="O131">
+        <v>0</v>
+      </c>
+      <c r="P131">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -9825,6 +14850,2112 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F126CFC9-BE8B-4DAF-AADB-1B89D72E9205}">
+  <dimension ref="A1:W108"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>305</v>
+      </c>
+      <c r="C1" t="s">
+        <v>306</v>
+      </c>
+      <c r="D1" t="s">
+        <v>307</v>
+      </c>
+      <c r="E1" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>337</v>
+      </c>
+      <c r="C2" t="s">
+        <v>338</v>
+      </c>
+      <c r="D2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E2">
+        <v>0.87554664723032005</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>343</v>
+      </c>
+      <c r="R2" t="s">
+        <v>344</v>
+      </c>
+      <c r="S2" t="s">
+        <v>345</v>
+      </c>
+      <c r="T2" t="s">
+        <v>346</v>
+      </c>
+      <c r="U2" t="s">
+        <v>347</v>
+      </c>
+      <c r="V2" t="s">
+        <v>348</v>
+      </c>
+      <c r="W2" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>60</v>
+      </c>
+      <c r="B3" t="s">
+        <v>337</v>
+      </c>
+      <c r="C3" t="s">
+        <v>338</v>
+      </c>
+      <c r="D3" t="s">
+        <v>110</v>
+      </c>
+      <c r="E3">
+        <v>0.93689936536717999</v>
+      </c>
+      <c r="Q3">
+        <v>0.17376981675931599</v>
+      </c>
+      <c r="R3">
+        <v>0.391187976116944</v>
+      </c>
+      <c r="S3">
+        <v>4.9619106444307101E-2</v>
+      </c>
+      <c r="T3">
+        <v>6.9384393658636995E-2</v>
+      </c>
+      <c r="U3">
+        <v>0</v>
+      </c>
+      <c r="V3">
+        <v>8.8532015647519002E-2</v>
+      </c>
+      <c r="W3">
+        <v>0.22750669137327501</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>120</v>
+      </c>
+      <c r="B4" t="s">
+        <v>337</v>
+      </c>
+      <c r="C4" t="s">
+        <v>338</v>
+      </c>
+      <c r="D4" t="s">
+        <v>110</v>
+      </c>
+      <c r="E4">
+        <v>0.94897403304884698</v>
+      </c>
+      <c r="Q4">
+        <v>0.47136654951416102</v>
+      </c>
+      <c r="R4">
+        <v>0.40066156708703698</v>
+      </c>
+      <c r="S4">
+        <v>3.1631176348976602E-2</v>
+      </c>
+      <c r="T4">
+        <v>2.4808765763903201E-2</v>
+      </c>
+      <c r="U4">
+        <v>6.2021914409758096E-4</v>
+      </c>
+      <c r="V4">
+        <v>1.44717800289435E-2</v>
+      </c>
+      <c r="W4">
+        <v>5.6439942112879803E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>180</v>
+      </c>
+      <c r="B5" t="s">
+        <v>337</v>
+      </c>
+      <c r="C5" t="s">
+        <v>338</v>
+      </c>
+      <c r="D5" t="s">
+        <v>110</v>
+      </c>
+      <c r="E5">
+        <v>0.97681999275624698</v>
+      </c>
+      <c r="Q5">
+        <v>0.47531501755835498</v>
+      </c>
+      <c r="R5">
+        <v>0.37781450113612802</v>
+      </c>
+      <c r="S5">
+        <v>3.3051022516008999E-2</v>
+      </c>
+      <c r="T5">
+        <v>6.25903738896922E-2</v>
+      </c>
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5">
+        <v>9.5021689733526104E-3</v>
+      </c>
+      <c r="W5">
+        <v>4.1726915926461397E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>240</v>
+      </c>
+      <c r="B6" t="s">
+        <v>337</v>
+      </c>
+      <c r="C6" t="s">
+        <v>338</v>
+      </c>
+      <c r="D6" t="s">
+        <v>110</v>
+      </c>
+      <c r="E6">
+        <v>0.69329710144927503</v>
+      </c>
+      <c r="Q6">
+        <v>0.248264597795018</v>
+      </c>
+      <c r="R6">
+        <v>0.40955492037566299</v>
+      </c>
+      <c r="S6">
+        <v>0.111882400979991</v>
+      </c>
+      <c r="T6">
+        <v>7.9216006533278802E-2</v>
+      </c>
+      <c r="U6">
+        <v>4.2874642711310702E-3</v>
+      </c>
+      <c r="V6">
+        <v>6.6353613719885601E-2</v>
+      </c>
+      <c r="W6">
+        <v>8.04409963250306E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>300</v>
+      </c>
+      <c r="B7" t="s">
+        <v>337</v>
+      </c>
+      <c r="C7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D7" t="s">
+        <v>110</v>
+      </c>
+      <c r="E7">
+        <v>0.97549909255898304</v>
+      </c>
+      <c r="Q7">
+        <v>0.11491894110404199</v>
+      </c>
+      <c r="R7">
+        <v>0.460086189205828</v>
+      </c>
+      <c r="S7">
+        <v>0.12887338395239001</v>
+      </c>
+      <c r="T7">
+        <v>0.13400369382310601</v>
+      </c>
+      <c r="U7">
+        <v>2.2573363431151201E-3</v>
+      </c>
+      <c r="V7">
+        <v>5.2329160681305102E-2</v>
+      </c>
+      <c r="W7">
+        <v>0.107531294890211</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>360</v>
+      </c>
+      <c r="B8" t="s">
+        <v>337</v>
+      </c>
+      <c r="C8" t="s">
+        <v>338</v>
+      </c>
+      <c r="D8" t="s">
+        <v>110</v>
+      </c>
+      <c r="E8">
+        <v>0.93922452660054101</v>
+      </c>
+      <c r="Q8">
+        <v>0.2790077900779</v>
+      </c>
+      <c r="R8">
+        <v>0.47437474374743699</v>
+      </c>
+      <c r="S8">
+        <v>0.170561705617056</v>
+      </c>
+      <c r="T8">
+        <v>4.8585485854858501E-2</v>
+      </c>
+      <c r="U8">
+        <v>2.0500205002049999E-3</v>
+      </c>
+      <c r="V8">
+        <v>6.7650676506765001E-3</v>
+      </c>
+      <c r="W8">
+        <v>1.8655186551865498E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>420</v>
+      </c>
+      <c r="B9" t="s">
+        <v>337</v>
+      </c>
+      <c r="C9" t="s">
+        <v>338</v>
+      </c>
+      <c r="D9" t="s">
+        <v>110</v>
+      </c>
+      <c r="E9">
+        <v>0.99460043196544201</v>
+      </c>
+      <c r="Q9">
+        <v>0.20678314491264099</v>
+      </c>
+      <c r="R9">
+        <v>0.41459403905447001</v>
+      </c>
+      <c r="S9">
+        <v>0.13299075025693699</v>
+      </c>
+      <c r="T9">
+        <v>0.132579650565262</v>
+      </c>
+      <c r="U9">
+        <v>9.6608427543679303E-3</v>
+      </c>
+      <c r="V9">
+        <v>4.1521068859198297E-2</v>
+      </c>
+      <c r="W9">
+        <v>6.1870503597122303E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>480</v>
+      </c>
+      <c r="B10" t="s">
+        <v>337</v>
+      </c>
+      <c r="C10" t="s">
+        <v>338</v>
+      </c>
+      <c r="D10" t="s">
+        <v>110</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="Q10">
+        <v>0.496917385943279</v>
+      </c>
+      <c r="R10">
+        <v>0.35717221537196803</v>
+      </c>
+      <c r="S10">
+        <v>1.5824085491163101E-2</v>
+      </c>
+      <c r="T10">
+        <v>4.3773119605425397E-2</v>
+      </c>
+      <c r="U10">
+        <v>0</v>
+      </c>
+      <c r="V10">
+        <v>6.57624332100287E-3</v>
+      </c>
+      <c r="W10">
+        <v>7.9736950267159795E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>540</v>
+      </c>
+      <c r="B11" t="s">
+        <v>337</v>
+      </c>
+      <c r="C11" t="s">
+        <v>338</v>
+      </c>
+      <c r="D11" t="s">
+        <v>110</v>
+      </c>
+      <c r="E11">
+        <v>0.93255184851217299</v>
+      </c>
+      <c r="Q11">
+        <v>0.20157384987893401</v>
+      </c>
+      <c r="R11">
+        <v>0.39164648910411598</v>
+      </c>
+      <c r="S11">
+        <v>0.107949959644874</v>
+      </c>
+      <c r="T11">
+        <v>0.135189669087974</v>
+      </c>
+      <c r="U11">
+        <v>3.1275221953188E-2</v>
+      </c>
+      <c r="V11">
+        <v>5.95238095238095E-2</v>
+      </c>
+      <c r="W11">
+        <v>7.2841000807102499E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>600</v>
+      </c>
+      <c r="B12" t="s">
+        <v>337</v>
+      </c>
+      <c r="C12" t="s">
+        <v>338</v>
+      </c>
+      <c r="D12" t="s">
+        <v>110</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
+      <c r="Q12">
+        <v>0.37734693877551001</v>
+      </c>
+      <c r="R12">
+        <v>0.43244897959183598</v>
+      </c>
+      <c r="S12">
+        <v>4.8571428571428502E-2</v>
+      </c>
+      <c r="T12">
+        <v>0.09</v>
+      </c>
+      <c r="U12">
+        <v>1.6326530612244801E-3</v>
+      </c>
+      <c r="V12">
+        <v>2.9591836734693799E-2</v>
+      </c>
+      <c r="W12">
+        <v>2.04081632653061E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>0</v>
+      </c>
+      <c r="B13" t="s">
+        <v>337</v>
+      </c>
+      <c r="C13" t="s">
+        <v>338</v>
+      </c>
+      <c r="D13" t="s">
+        <v>122</v>
+      </c>
+      <c r="E13">
+        <v>0.75100461378181205</v>
+      </c>
+      <c r="Q13">
+        <v>0.193581567578687</v>
+      </c>
+      <c r="R13">
+        <v>0.43715284920798098</v>
+      </c>
+      <c r="S13">
+        <v>2.0160460810532799E-2</v>
+      </c>
+      <c r="T13">
+        <v>9.8539395186175605E-2</v>
+      </c>
+      <c r="U13">
+        <v>0</v>
+      </c>
+      <c r="V13">
+        <v>5.5955564698621597E-2</v>
+      </c>
+      <c r="W13">
+        <v>0.19461016251800001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>60</v>
+      </c>
+      <c r="B14" t="s">
+        <v>337</v>
+      </c>
+      <c r="C14" t="s">
+        <v>338</v>
+      </c>
+      <c r="D14" t="s">
+        <v>122</v>
+      </c>
+      <c r="E14">
+        <v>0.85975975975975905</v>
+      </c>
+      <c r="Q14">
+        <v>5.3209109730848803E-2</v>
+      </c>
+      <c r="R14">
+        <v>0.45548654244306402</v>
+      </c>
+      <c r="S14">
+        <v>0.125465838509316</v>
+      </c>
+      <c r="T14">
+        <v>5.6521739130434699E-2</v>
+      </c>
+      <c r="U14">
+        <v>0</v>
+      </c>
+      <c r="V14">
+        <v>2.7122153209109701E-2</v>
+      </c>
+      <c r="W14">
+        <v>0.28219461697722498</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>120</v>
+      </c>
+      <c r="B15" t="s">
+        <v>337</v>
+      </c>
+      <c r="C15" t="s">
+        <v>338</v>
+      </c>
+      <c r="D15" t="s">
+        <v>122</v>
+      </c>
+      <c r="E15">
+        <v>0.93885542168674696</v>
+      </c>
+      <c r="Q15">
+        <v>0.50118203309692599</v>
+      </c>
+      <c r="R15">
+        <v>0.32505910165484603</v>
+      </c>
+      <c r="S15">
+        <v>1.5957446808510599E-2</v>
+      </c>
+      <c r="T15">
+        <v>5.9692671394799002E-2</v>
+      </c>
+      <c r="U15">
+        <v>7.09219858156028E-3</v>
+      </c>
+      <c r="V15">
+        <v>3.0141843971631201E-2</v>
+      </c>
+      <c r="W15">
+        <v>6.0874704491725697E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>180</v>
+      </c>
+      <c r="B16" t="s">
+        <v>337</v>
+      </c>
+      <c r="C16" t="s">
+        <v>338</v>
+      </c>
+      <c r="D16" t="s">
+        <v>122</v>
+      </c>
+      <c r="E16">
+        <v>0.78962278216788395</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>240</v>
+      </c>
+      <c r="B17" t="s">
+        <v>337</v>
+      </c>
+      <c r="C17" t="s">
+        <v>338</v>
+      </c>
+      <c r="D17" t="s">
+        <v>122</v>
+      </c>
+      <c r="E17">
+        <v>0.93130799161927502</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>300</v>
+      </c>
+      <c r="B18" t="s">
+        <v>337</v>
+      </c>
+      <c r="C18" t="s">
+        <v>338</v>
+      </c>
+      <c r="D18" t="s">
+        <v>122</v>
+      </c>
+      <c r="E18">
+        <v>0.88182632050134202</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>360</v>
+      </c>
+      <c r="B19" t="s">
+        <v>337</v>
+      </c>
+      <c r="C19" t="s">
+        <v>338</v>
+      </c>
+      <c r="D19" t="s">
+        <v>122</v>
+      </c>
+      <c r="E19">
+        <v>0.65941043083900197</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>420</v>
+      </c>
+      <c r="B20" t="s">
+        <v>337</v>
+      </c>
+      <c r="C20" t="s">
+        <v>338</v>
+      </c>
+      <c r="D20" t="s">
+        <v>122</v>
+      </c>
+      <c r="E20">
+        <v>0.77470116507792397</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>480</v>
+      </c>
+      <c r="B21" t="s">
+        <v>337</v>
+      </c>
+      <c r="C21" t="s">
+        <v>338</v>
+      </c>
+      <c r="D21" t="s">
+        <v>122</v>
+      </c>
+      <c r="E21">
+        <v>0.77791718946047606</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>0</v>
+      </c>
+      <c r="B22" t="s">
+        <v>337</v>
+      </c>
+      <c r="C22" t="s">
+        <v>338</v>
+      </c>
+      <c r="D22" t="s">
+        <v>132</v>
+      </c>
+      <c r="E22">
+        <v>1.8529241459177701E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>60</v>
+      </c>
+      <c r="B23" t="s">
+        <v>337</v>
+      </c>
+      <c r="C23" t="s">
+        <v>338</v>
+      </c>
+      <c r="D23" t="s">
+        <v>132</v>
+      </c>
+      <c r="E23">
+        <v>3.4293552812071297E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A24">
+        <v>120</v>
+      </c>
+      <c r="B24" t="s">
+        <v>337</v>
+      </c>
+      <c r="C24" t="s">
+        <v>338</v>
+      </c>
+      <c r="D24" t="s">
+        <v>132</v>
+      </c>
+      <c r="E24">
+        <v>8.1666209920526103E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A25">
+        <v>180</v>
+      </c>
+      <c r="B25" t="s">
+        <v>337</v>
+      </c>
+      <c r="C25" t="s">
+        <v>338</v>
+      </c>
+      <c r="D25" t="s">
+        <v>132</v>
+      </c>
+      <c r="E25">
+        <v>7.21961972995315E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A26">
+        <v>240</v>
+      </c>
+      <c r="B26" t="s">
+        <v>337</v>
+      </c>
+      <c r="C26" t="s">
+        <v>338</v>
+      </c>
+      <c r="D26" t="s">
+        <v>132</v>
+      </c>
+      <c r="E26">
+        <v>5.1239209133945897E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A27">
+        <v>300</v>
+      </c>
+      <c r="B27" t="s">
+        <v>337</v>
+      </c>
+      <c r="C27" t="s">
+        <v>338</v>
+      </c>
+      <c r="D27" t="s">
+        <v>132</v>
+      </c>
+      <c r="E27">
+        <v>1.34578412524031E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A28">
+        <v>360</v>
+      </c>
+      <c r="B28" t="s">
+        <v>337</v>
+      </c>
+      <c r="C28" t="s">
+        <v>338</v>
+      </c>
+      <c r="D28" t="s">
+        <v>132</v>
+      </c>
+      <c r="E28">
+        <v>9.8238855255916302E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A29">
+        <v>420</v>
+      </c>
+      <c r="B29" t="s">
+        <v>337</v>
+      </c>
+      <c r="C29" t="s">
+        <v>338</v>
+      </c>
+      <c r="D29" t="s">
+        <v>132</v>
+      </c>
+      <c r="E29">
+        <v>5.7439824945295396E-3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A30">
+        <v>480</v>
+      </c>
+      <c r="B30" t="s">
+        <v>337</v>
+      </c>
+      <c r="C30" t="s">
+        <v>338</v>
+      </c>
+      <c r="D30" t="s">
+        <v>132</v>
+      </c>
+      <c r="E30">
+        <v>2.12413793103448E-2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A31">
+        <v>540</v>
+      </c>
+      <c r="B31" t="s">
+        <v>337</v>
+      </c>
+      <c r="C31" t="s">
+        <v>338</v>
+      </c>
+      <c r="D31" t="s">
+        <v>132</v>
+      </c>
+      <c r="E31">
+        <v>0.114861186717474</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A32">
+        <v>600</v>
+      </c>
+      <c r="B32" t="s">
+        <v>337</v>
+      </c>
+      <c r="C32" t="s">
+        <v>338</v>
+      </c>
+      <c r="D32" t="s">
+        <v>132</v>
+      </c>
+      <c r="E32">
+        <v>0.115631095012538</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A33">
+        <v>660</v>
+      </c>
+      <c r="B33" t="s">
+        <v>337</v>
+      </c>
+      <c r="C33" t="s">
+        <v>338</v>
+      </c>
+      <c r="D33" t="s">
+        <v>132</v>
+      </c>
+      <c r="E33">
+        <v>5.8085628579219999E-2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A35">
+        <v>0</v>
+      </c>
+      <c r="B35" t="s">
+        <v>337</v>
+      </c>
+      <c r="C35" t="s">
+        <v>338</v>
+      </c>
+      <c r="D35" t="s">
+        <v>145</v>
+      </c>
+      <c r="E35">
+        <v>0.35337278106508802</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A36">
+        <v>60</v>
+      </c>
+      <c r="B36" t="s">
+        <v>337</v>
+      </c>
+      <c r="C36" t="s">
+        <v>338</v>
+      </c>
+      <c r="D36" t="s">
+        <v>145</v>
+      </c>
+      <c r="E36">
+        <v>0.159283694627709</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A37">
+        <v>120</v>
+      </c>
+      <c r="B37" t="s">
+        <v>337</v>
+      </c>
+      <c r="C37" t="s">
+        <v>338</v>
+      </c>
+      <c r="D37" t="s">
+        <v>145</v>
+      </c>
+      <c r="E37">
+        <v>0.33317843866170999</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A38">
+        <v>180</v>
+      </c>
+      <c r="B38" t="s">
+        <v>337</v>
+      </c>
+      <c r="C38" t="s">
+        <v>338</v>
+      </c>
+      <c r="D38" t="s">
+        <v>145</v>
+      </c>
+      <c r="E38">
+        <v>0.34954619501978101</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A39">
+        <v>240</v>
+      </c>
+      <c r="B39" t="s">
+        <v>337</v>
+      </c>
+      <c r="C39" t="s">
+        <v>338</v>
+      </c>
+      <c r="D39" t="s">
+        <v>145</v>
+      </c>
+      <c r="E39">
+        <v>0.218181818181818</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A40">
+        <v>300</v>
+      </c>
+      <c r="B40" t="s">
+        <v>337</v>
+      </c>
+      <c r="C40" t="s">
+        <v>338</v>
+      </c>
+      <c r="D40" t="s">
+        <v>145</v>
+      </c>
+      <c r="E40">
+        <v>0.26981529109188601</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A41">
+        <v>360</v>
+      </c>
+      <c r="B41" t="s">
+        <v>337</v>
+      </c>
+      <c r="C41" t="s">
+        <v>338</v>
+      </c>
+      <c r="D41" t="s">
+        <v>145</v>
+      </c>
+      <c r="E41">
+        <v>0.22016651248843599</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A42">
+        <v>420</v>
+      </c>
+      <c r="B42" t="s">
+        <v>337</v>
+      </c>
+      <c r="C42" t="s">
+        <v>338</v>
+      </c>
+      <c r="D42" t="s">
+        <v>145</v>
+      </c>
+      <c r="E42">
+        <v>0.40415111940298498</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A43">
+        <v>480</v>
+      </c>
+      <c r="B43" t="s">
+        <v>337</v>
+      </c>
+      <c r="C43" t="s">
+        <v>338</v>
+      </c>
+      <c r="D43" t="s">
+        <v>145</v>
+      </c>
+      <c r="E43">
+        <v>0.12122608896058901</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A44">
+        <v>540</v>
+      </c>
+      <c r="B44" t="s">
+        <v>337</v>
+      </c>
+      <c r="C44" t="s">
+        <v>338</v>
+      </c>
+      <c r="D44" t="s">
+        <v>145</v>
+      </c>
+      <c r="E44">
+        <v>0.41359040677169001</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A45">
+        <v>600</v>
+      </c>
+      <c r="B45" t="s">
+        <v>337</v>
+      </c>
+      <c r="C45" t="s">
+        <v>338</v>
+      </c>
+      <c r="D45" t="s">
+        <v>145</v>
+      </c>
+      <c r="E45">
+        <v>0.55285714285714205</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A46">
+        <v>660</v>
+      </c>
+      <c r="B46" t="s">
+        <v>337</v>
+      </c>
+      <c r="C46" t="s">
+        <v>338</v>
+      </c>
+      <c r="D46" t="s">
+        <v>145</v>
+      </c>
+      <c r="E46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A47">
+        <v>0</v>
+      </c>
+      <c r="B47" t="s">
+        <v>337</v>
+      </c>
+      <c r="C47" t="s">
+        <v>338</v>
+      </c>
+      <c r="D47" t="s">
+        <v>147</v>
+      </c>
+      <c r="E47">
+        <v>7.9607187630589202E-2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A48">
+        <v>60</v>
+      </c>
+      <c r="B48" t="s">
+        <v>337</v>
+      </c>
+      <c r="C48" t="s">
+        <v>338</v>
+      </c>
+      <c r="D48" t="s">
+        <v>147</v>
+      </c>
+      <c r="E48">
+        <v>5.4048414023372203E-2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A49">
+        <v>120</v>
+      </c>
+      <c r="B49" t="s">
+        <v>337</v>
+      </c>
+      <c r="C49" t="s">
+        <v>338</v>
+      </c>
+      <c r="D49" t="s">
+        <v>147</v>
+      </c>
+      <c r="E49">
+        <v>1.3521947160391E-2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A50">
+        <v>180</v>
+      </c>
+      <c r="B50" t="s">
+        <v>337</v>
+      </c>
+      <c r="C50" t="s">
+        <v>338</v>
+      </c>
+      <c r="D50" t="s">
+        <v>147</v>
+      </c>
+      <c r="E50">
+        <v>1.39119601328903E-2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A51">
+        <v>240</v>
+      </c>
+      <c r="B51" t="s">
+        <v>337</v>
+      </c>
+      <c r="C51" t="s">
+        <v>338</v>
+      </c>
+      <c r="D51" t="s">
+        <v>147</v>
+      </c>
+      <c r="E51">
+        <v>0.389506172839506</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A52">
+        <v>300</v>
+      </c>
+      <c r="B52" t="s">
+        <v>337</v>
+      </c>
+      <c r="C52" t="s">
+        <v>338</v>
+      </c>
+      <c r="D52" t="s">
+        <v>147</v>
+      </c>
+      <c r="E52">
+        <v>3.52331606217616E-2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A53">
+        <v>360</v>
+      </c>
+      <c r="B53" t="s">
+        <v>337</v>
+      </c>
+      <c r="C53" t="s">
+        <v>338</v>
+      </c>
+      <c r="D53" t="s">
+        <v>147</v>
+      </c>
+      <c r="E53">
+        <v>4.8400498545907701E-2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A54">
+        <v>420</v>
+      </c>
+      <c r="B54" t="s">
+        <v>337</v>
+      </c>
+      <c r="C54" t="s">
+        <v>338</v>
+      </c>
+      <c r="D54" t="s">
+        <v>147</v>
+      </c>
+      <c r="E54">
+        <v>3.6055143160127201E-3</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A55">
+        <v>480</v>
+      </c>
+      <c r="B55" t="s">
+        <v>337</v>
+      </c>
+      <c r="C55" t="s">
+        <v>338</v>
+      </c>
+      <c r="D55" t="s">
+        <v>147</v>
+      </c>
+      <c r="E55">
+        <v>4.71293916023993E-3</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A56">
+        <v>540</v>
+      </c>
+      <c r="B56" t="s">
+        <v>337</v>
+      </c>
+      <c r="C56" t="s">
+        <v>338</v>
+      </c>
+      <c r="D56" t="s">
+        <v>147</v>
+      </c>
+      <c r="E56">
+        <v>6.3387746449014196E-2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A57">
+        <v>600</v>
+      </c>
+      <c r="B57" t="s">
+        <v>337</v>
+      </c>
+      <c r="C57" t="s">
+        <v>338</v>
+      </c>
+      <c r="D57" t="s">
+        <v>147</v>
+      </c>
+      <c r="E57">
+        <v>7.1082390953150207E-2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A58">
+        <v>0</v>
+      </c>
+      <c r="B58" t="s">
+        <v>337</v>
+      </c>
+      <c r="C58" t="s">
+        <v>338</v>
+      </c>
+      <c r="D58" t="s">
+        <v>159</v>
+      </c>
+      <c r="E58">
+        <v>0.114251497005988</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A59">
+        <v>60</v>
+      </c>
+      <c r="B59" t="s">
+        <v>337</v>
+      </c>
+      <c r="C59" t="s">
+        <v>338</v>
+      </c>
+      <c r="D59" t="s">
+        <v>159</v>
+      </c>
+      <c r="E59">
+        <v>7.0554355651547801E-2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A60">
+        <v>120</v>
+      </c>
+      <c r="B60" t="s">
+        <v>337</v>
+      </c>
+      <c r="C60" t="s">
+        <v>338</v>
+      </c>
+      <c r="D60" t="s">
+        <v>159</v>
+      </c>
+      <c r="E60">
+        <v>0.10111813320369401</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A61">
+        <v>180</v>
+      </c>
+      <c r="B61" t="s">
+        <v>337</v>
+      </c>
+      <c r="C61" t="s">
+        <v>338</v>
+      </c>
+      <c r="D61" t="s">
+        <v>159</v>
+      </c>
+      <c r="E61">
+        <v>0.28129531174480399</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A62">
+        <v>240</v>
+      </c>
+      <c r="B62" t="s">
+        <v>337</v>
+      </c>
+      <c r="C62" t="s">
+        <v>338</v>
+      </c>
+      <c r="D62" t="s">
+        <v>159</v>
+      </c>
+      <c r="E62">
+        <v>0.10924981791697</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A63">
+        <v>300</v>
+      </c>
+      <c r="B63" t="s">
+        <v>337</v>
+      </c>
+      <c r="C63" t="s">
+        <v>338</v>
+      </c>
+      <c r="D63" t="s">
+        <v>159</v>
+      </c>
+      <c r="E63">
+        <v>0.103984450923226</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A64">
+        <v>360</v>
+      </c>
+      <c r="B64" t="s">
+        <v>337</v>
+      </c>
+      <c r="C64" t="s">
+        <v>338</v>
+      </c>
+      <c r="D64" t="s">
+        <v>159</v>
+      </c>
+      <c r="E64">
+        <v>3.0456852791878101E-2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A65">
+        <v>420</v>
+      </c>
+      <c r="B65" t="s">
+        <v>337</v>
+      </c>
+      <c r="C65" t="s">
+        <v>338</v>
+      </c>
+      <c r="D65" t="s">
+        <v>159</v>
+      </c>
+      <c r="E65">
+        <v>0.134836852207293</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A66">
+        <v>480</v>
+      </c>
+      <c r="B66" t="s">
+        <v>337</v>
+      </c>
+      <c r="C66" t="s">
+        <v>338</v>
+      </c>
+      <c r="D66" t="s">
+        <v>159</v>
+      </c>
+      <c r="E66">
+        <v>0.16904474002418299</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A68">
+        <v>0</v>
+      </c>
+      <c r="B68" t="s">
+        <v>337</v>
+      </c>
+      <c r="C68" t="s">
+        <v>338</v>
+      </c>
+      <c r="D68" t="s">
+        <v>160</v>
+      </c>
+      <c r="E68">
+        <v>0.27981109799291598</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A69">
+        <v>60</v>
+      </c>
+      <c r="B69" t="s">
+        <v>337</v>
+      </c>
+      <c r="C69" t="s">
+        <v>338</v>
+      </c>
+      <c r="D69" t="s">
+        <v>160</v>
+      </c>
+      <c r="E69">
+        <v>0.31361085126286198</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A70">
+        <v>120</v>
+      </c>
+      <c r="B70" t="s">
+        <v>337</v>
+      </c>
+      <c r="C70" t="s">
+        <v>338</v>
+      </c>
+      <c r="D70" t="s">
+        <v>160</v>
+      </c>
+      <c r="E70">
+        <v>0.211024367163472</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A71">
+        <v>180</v>
+      </c>
+      <c r="B71" t="s">
+        <v>337</v>
+      </c>
+      <c r="C71" t="s">
+        <v>338</v>
+      </c>
+      <c r="D71" t="s">
+        <v>160</v>
+      </c>
+      <c r="E71">
+        <v>0.21717530163236301</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A72">
+        <v>240</v>
+      </c>
+      <c r="B72" t="s">
+        <v>337</v>
+      </c>
+      <c r="C72" t="s">
+        <v>338</v>
+      </c>
+      <c r="D72" t="s">
+        <v>160</v>
+      </c>
+      <c r="E72">
+        <v>0.27283399859121799</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A73">
+        <v>300</v>
+      </c>
+      <c r="B73" t="s">
+        <v>337</v>
+      </c>
+      <c r="C73" t="s">
+        <v>338</v>
+      </c>
+      <c r="D73" t="s">
+        <v>160</v>
+      </c>
+      <c r="E73">
+        <v>0.25887363937529501</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A74">
+        <v>360</v>
+      </c>
+      <c r="B74" t="s">
+        <v>337</v>
+      </c>
+      <c r="C74" t="s">
+        <v>338</v>
+      </c>
+      <c r="D74" t="s">
+        <v>160</v>
+      </c>
+      <c r="E74">
+        <v>0.48583569405099097</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A75">
+        <v>420</v>
+      </c>
+      <c r="B75" t="s">
+        <v>337</v>
+      </c>
+      <c r="C75" t="s">
+        <v>338</v>
+      </c>
+      <c r="D75" t="s">
+        <v>160</v>
+      </c>
+      <c r="E75">
+        <v>0.33801827125790501</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A76">
+        <v>480</v>
+      </c>
+      <c r="B76" t="s">
+        <v>337</v>
+      </c>
+      <c r="C76" t="s">
+        <v>338</v>
+      </c>
+      <c r="D76" t="s">
+        <v>160</v>
+      </c>
+      <c r="E76">
+        <v>0.31094992980814201</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A77">
+        <v>540</v>
+      </c>
+      <c r="B77" t="s">
+        <v>337</v>
+      </c>
+      <c r="C77" t="s">
+        <v>338</v>
+      </c>
+      <c r="D77" t="s">
+        <v>160</v>
+      </c>
+      <c r="E77">
+        <v>0.26441631504922603</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A78">
+        <v>600</v>
+      </c>
+      <c r="B78" t="s">
+        <v>337</v>
+      </c>
+      <c r="C78" t="s">
+        <v>338</v>
+      </c>
+      <c r="D78" t="s">
+        <v>160</v>
+      </c>
+      <c r="E78">
+        <v>0.27671541057367799</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A79">
+        <v>0</v>
+      </c>
+      <c r="B79" t="s">
+        <v>337</v>
+      </c>
+      <c r="C79" t="s">
+        <v>338</v>
+      </c>
+      <c r="D79" t="s">
+        <v>162</v>
+      </c>
+      <c r="E79">
+        <v>0.81887824897400796</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A80">
+        <v>60</v>
+      </c>
+      <c r="B80" t="s">
+        <v>337</v>
+      </c>
+      <c r="C80" t="s">
+        <v>338</v>
+      </c>
+      <c r="D80" t="s">
+        <v>162</v>
+      </c>
+      <c r="E80">
+        <v>0.76575342465753404</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A81">
+        <v>120</v>
+      </c>
+      <c r="B81" t="s">
+        <v>337</v>
+      </c>
+      <c r="C81" t="s">
+        <v>338</v>
+      </c>
+      <c r="D81" t="s">
+        <v>162</v>
+      </c>
+      <c r="E81">
+        <v>0.87858719646799099</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A82">
+        <v>180</v>
+      </c>
+      <c r="B82" t="s">
+        <v>337</v>
+      </c>
+      <c r="C82" t="s">
+        <v>338</v>
+      </c>
+      <c r="D82" t="s">
+        <v>162</v>
+      </c>
+      <c r="E82">
+        <v>0.73089700996677698</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A83">
+        <v>240</v>
+      </c>
+      <c r="B83" t="s">
+        <v>337</v>
+      </c>
+      <c r="C83" t="s">
+        <v>338</v>
+      </c>
+      <c r="D83" t="s">
+        <v>162</v>
+      </c>
+      <c r="E83">
+        <v>0.82727521180650399</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A84">
+        <v>300</v>
+      </c>
+      <c r="B84" t="s">
+        <v>337</v>
+      </c>
+      <c r="C84" t="s">
+        <v>338</v>
+      </c>
+      <c r="D84" t="s">
+        <v>162</v>
+      </c>
+      <c r="E84">
+        <v>0.82029540481400398</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A85">
+        <v>360</v>
+      </c>
+      <c r="B85" t="s">
+        <v>337</v>
+      </c>
+      <c r="C85" t="s">
+        <v>338</v>
+      </c>
+      <c r="D85" t="s">
+        <v>162</v>
+      </c>
+      <c r="E85">
+        <v>0.78175895765472303</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A86">
+        <v>420</v>
+      </c>
+      <c r="B86" t="s">
+        <v>337</v>
+      </c>
+      <c r="C86" t="s">
+        <v>338</v>
+      </c>
+      <c r="D86" t="s">
+        <v>162</v>
+      </c>
+      <c r="E86">
+        <v>0.64850807555433798</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A87">
+        <v>480</v>
+      </c>
+      <c r="B87" t="s">
+        <v>337</v>
+      </c>
+      <c r="C87" t="s">
+        <v>338</v>
+      </c>
+      <c r="D87" t="s">
+        <v>162</v>
+      </c>
+      <c r="E87">
+        <v>0.82779456193353396</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A88">
+        <v>540</v>
+      </c>
+      <c r="B88" t="s">
+        <v>337</v>
+      </c>
+      <c r="C88" t="s">
+        <v>338</v>
+      </c>
+      <c r="D88" t="s">
+        <v>162</v>
+      </c>
+      <c r="E88">
+        <v>0.595726970033296</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A89">
+        <v>600</v>
+      </c>
+      <c r="B89" t="s">
+        <v>337</v>
+      </c>
+      <c r="C89" t="s">
+        <v>338</v>
+      </c>
+      <c r="D89" t="s">
+        <v>162</v>
+      </c>
+      <c r="E89">
+        <v>0.63472222222222197</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A90">
+        <v>660</v>
+      </c>
+      <c r="B90" t="s">
+        <v>337</v>
+      </c>
+      <c r="C90" t="s">
+        <v>338</v>
+      </c>
+      <c r="D90" t="s">
+        <v>162</v>
+      </c>
+      <c r="E90">
+        <v>0.39702581369248002</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A91">
+        <v>720</v>
+      </c>
+      <c r="B91" t="s">
+        <v>337</v>
+      </c>
+      <c r="C91" t="s">
+        <v>338</v>
+      </c>
+      <c r="D91" t="s">
+        <v>162</v>
+      </c>
+      <c r="E91">
+        <v>0.69961132704053297</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A92">
+        <v>780</v>
+      </c>
+      <c r="B92" t="s">
+        <v>337</v>
+      </c>
+      <c r="C92" t="s">
+        <v>338</v>
+      </c>
+      <c r="D92" t="s">
+        <v>162</v>
+      </c>
+      <c r="E92">
+        <v>0.96761720637989301</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A93">
+        <v>0</v>
+      </c>
+      <c r="B93" t="s">
+        <v>337</v>
+      </c>
+      <c r="C93" t="s">
+        <v>338</v>
+      </c>
+      <c r="D93" t="s">
+        <v>189</v>
+      </c>
+      <c r="E93">
+        <v>0.69836400817995903</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A94">
+        <v>60</v>
+      </c>
+      <c r="B94" t="s">
+        <v>337</v>
+      </c>
+      <c r="C94" t="s">
+        <v>338</v>
+      </c>
+      <c r="D94" t="s">
+        <v>189</v>
+      </c>
+      <c r="E94">
+        <v>0.70638153428377404</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A95">
+        <v>120</v>
+      </c>
+      <c r="B95" t="s">
+        <v>337</v>
+      </c>
+      <c r="C95" t="s">
+        <v>338</v>
+      </c>
+      <c r="D95" t="s">
+        <v>189</v>
+      </c>
+      <c r="E95">
+        <v>0.60672614962251203</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A96">
+        <v>180</v>
+      </c>
+      <c r="B96" t="s">
+        <v>337</v>
+      </c>
+      <c r="C96" t="s">
+        <v>338</v>
+      </c>
+      <c r="D96" t="s">
+        <v>189</v>
+      </c>
+      <c r="E96">
+        <v>0.40679711637487098</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A97">
+        <v>240</v>
+      </c>
+      <c r="B97" t="s">
+        <v>337</v>
+      </c>
+      <c r="C97" t="s">
+        <v>338</v>
+      </c>
+      <c r="D97" t="s">
+        <v>189</v>
+      </c>
+      <c r="E97">
+        <v>0.61838921534739</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A98">
+        <v>300</v>
+      </c>
+      <c r="B98" t="s">
+        <v>337</v>
+      </c>
+      <c r="C98" t="s">
+        <v>338</v>
+      </c>
+      <c r="D98" t="s">
+        <v>189</v>
+      </c>
+      <c r="E98">
+        <v>0.94111424541607902</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A99">
+        <v>360</v>
+      </c>
+      <c r="B99" t="s">
+        <v>337</v>
+      </c>
+      <c r="C99" t="s">
+        <v>338</v>
+      </c>
+      <c r="D99" t="s">
+        <v>189</v>
+      </c>
+      <c r="E99">
+        <v>0.69351851851851798</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A100">
+        <v>0</v>
+      </c>
+      <c r="B100" t="s">
+        <v>337</v>
+      </c>
+      <c r="C100" t="s">
+        <v>338</v>
+      </c>
+      <c r="D100" t="s">
+        <v>197</v>
+      </c>
+      <c r="E100">
+        <v>0.98492871690427697</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A101">
+        <v>60</v>
+      </c>
+      <c r="B101" t="s">
+        <v>337</v>
+      </c>
+      <c r="C101" t="s">
+        <v>338</v>
+      </c>
+      <c r="D101" t="s">
+        <v>197</v>
+      </c>
+      <c r="E101">
+        <v>0.99979508196721301</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A102">
+        <v>120</v>
+      </c>
+      <c r="B102" t="s">
+        <v>337</v>
+      </c>
+      <c r="C102" t="s">
+        <v>338</v>
+      </c>
+      <c r="D102" t="s">
+        <v>197</v>
+      </c>
+      <c r="E102">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A103">
+        <v>180</v>
+      </c>
+      <c r="B103" t="s">
+        <v>337</v>
+      </c>
+      <c r="C103" t="s">
+        <v>338</v>
+      </c>
+      <c r="D103" t="s">
+        <v>197</v>
+      </c>
+      <c r="E103">
+        <v>0.979808492922564</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A104">
+        <v>240</v>
+      </c>
+      <c r="B104" t="s">
+        <v>337</v>
+      </c>
+      <c r="C104" t="s">
+        <v>338</v>
+      </c>
+      <c r="D104" t="s">
+        <v>197</v>
+      </c>
+      <c r="E104">
+        <v>0.97539766702014796</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A105">
+        <v>300</v>
+      </c>
+      <c r="B105" t="s">
+        <v>337</v>
+      </c>
+      <c r="C105" t="s">
+        <v>338</v>
+      </c>
+      <c r="D105" t="s">
+        <v>197</v>
+      </c>
+      <c r="E105">
+        <v>0.99895615866388299</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A106">
+        <v>360</v>
+      </c>
+      <c r="B106" t="s">
+        <v>337</v>
+      </c>
+      <c r="C106" t="s">
+        <v>338</v>
+      </c>
+      <c r="D106" t="s">
+        <v>197</v>
+      </c>
+      <c r="E106">
+        <v>0.965182527959485</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A107">
+        <v>420</v>
+      </c>
+      <c r="B107" t="s">
+        <v>337</v>
+      </c>
+      <c r="C107" t="s">
+        <v>338</v>
+      </c>
+      <c r="D107" t="s">
+        <v>197</v>
+      </c>
+      <c r="E107">
+        <v>0.96608750261670495</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A108">
+        <v>480</v>
+      </c>
+      <c r="B108" t="s">
+        <v>337</v>
+      </c>
+      <c r="C108" t="s">
+        <v>338</v>
+      </c>
+      <c r="D108" t="s">
+        <v>197</v>
+      </c>
+      <c r="E108">
+        <v>0.94115183246073297</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:CL15"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -13038,7 +20169,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C79A2F0D-0642-4C0E-8D2C-134A58C1CED4}">
   <dimension ref="A1:O15"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -13555,7 +20686,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A29EEC2-1BB3-40E4-97B4-D8227D81F07F}">
   <dimension ref="A1:AD15"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -14627,7 +21758,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0222AAA1-4358-484C-B7F2-43704DA71319}">
   <dimension ref="A1:E259"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
